--- a/output/Bonus_Plan_FINAL.xlsx
+++ b/output/Bonus_Plan_FINAL.xlsx
@@ -98,7 +98,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -155,8 +155,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -178,11 +183,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -290,6 +339,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2071,39 +2125,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Collected % Kicker (applies to BOTH proposals)</t>
+          <t>Collected Incentive - per policy, flat dollars</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>The kicker is applied to the per-policy target BEFORE the safe-net cap. It rewards collecting cash, not just writing premium.</t>
+          <t>Per-policy flat dollar amount added to the base bonus. ONLY applies to policies with WRITTEN PREMIUM &gt; $1,200. A $800 policy does not earn the kicker, regardless of how much was collected.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Collected % of Premium</t>
+          <t>Collected % of premium</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Multiplier</t>
+          <t>Per-policy kicker</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -2113,16 +2167,16 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Example: $10 target</t>
+          <t>Example: $1,500 NB base $7</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Example after Kicker</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Final per-policy pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Below 15%</t>
@@ -2130,7 +2184,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>x 1.00 (none)</t>
+          <t>$0 (none)</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -2140,159 +2194,194 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$1,500 NB, 10% down</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>$10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>$7 (base only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>15% - 24%</t>
+          <t>15% - 19%</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>x 1.10 (+10%)</t>
+          <t>+$1</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Minimum down. Small kicker.</t>
+          <t>Minimum down. Small bump.</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$1,500 NB, 17% down</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>$11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>$7 + $1 = $8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>25% - 49%</t>
+          <t>20% - 24%</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>x 1.15 (+15%)</t>
+          <t>+$2</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Standard down. Standard kicker.</t>
+          <t>Standard down. Standard bump.</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$1,500 NB, 22% down</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>$11.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>$7 + $2 = $9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>50% - 99%</t>
+          <t>25% - 99%</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>x 1.20 (+20%)</t>
+          <t>+$5</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>High collection. Stronger kicker.</t>
+          <t>High collection. Big bump.</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$1,500 NB, 30% down</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>$12.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>$7 + $5 = $12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>100% (PIF)</t>
+          <t>100% PIF</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>x 1.25 (+25%)</t>
+          <t>+$8</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Paid in full. Top kicker.</t>
+          <t>Paid in full. Top kicker - zero chargeback risk.</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$1,500 NB PIF</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>$12.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Why use the collected % instead of the written premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>Written premium is the carrier number. Collected premium is the agency number - it is the cash that actually pays commission, rent, and payroll.</t>
+          <t>$7 + $8 = $15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Premium &lt;= $1,200</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>$0 (no kicker)</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Low-premium policies do not earn the incentive, no matter the collected %.</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>$800 NB, 50% down</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>$5 (base only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Why a per-policy flat kicker</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="42" t="inlineStr">
         <is>
-          <t>Without the kicker, a policy with a $50 down looks the same as one with a $500 down. With the kicker, the agent who pushes for a bigger down earns more.</t>
+          <t>Each policy earns its own kicker based on its own collected % - not the agent's total collected %. A $50 down on one policy and a PIF on another are rewarded separately.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>The kicker is INSIDE the cap. The cap is still 15% of safe net. So a high kicker on a low-collected policy cannot break ownership economics.</t>
+          <t>The $1,200 premium floor excludes the smallest policies. A $700 policy at 25% collected is still only $175 in cash - not enough to justify a $5 bump.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Flat dollars (not a multiplier) make the math easy to audit. Every policy line on the tracker shows: base + kicker = pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>PIF is the top tier at +$8 because PIF policies have zero chargeback risk - the carrier already has all the money.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="7">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2963,322 +3052,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monthly Manual Bonus Tracker - Template</t>
+          <t>Monthly Manual Bonus Tracker - The Bonus Plan</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>One copy per month per agent. Only verified rows get paid. Use this whether running Proposal A, B, or C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+          <t>Agents enter ONE ROW PER POLICY. Without an entry the policy does NOT get bonused. Manager verifies fields. Per-policy bonus columns auto-calculate from the formulas below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>THE BONUS PLAN FORMULAS (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>Per-policy BASE</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>NB: &lt;$1,200=$5 | $1,200-$1,799=$7 | $1,800-$2,499=$10 | $2,500-$2,999=$13 | $3,000+ = $13+$2/$1k cap $25</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+      <c r="F4" s="44" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="44" t="n"/>
+      <c r="I4" s="44" t="n"/>
+      <c r="J4" s="44" t="n"/>
+      <c r="K4" s="44" t="n"/>
+      <c r="L4" s="44" t="n"/>
+      <c r="M4" s="44" t="n"/>
+      <c r="N4" s="44" t="n"/>
+      <c r="O4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Per-policy BASE</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>RWR: &lt;$1,200=$2 | $1,200-$1,799=$3 | $1,800+=$4</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
+      <c r="I5" s="44" t="n"/>
+      <c r="J5" s="44" t="n"/>
+      <c r="K5" s="44" t="n"/>
+      <c r="L5" s="44" t="n"/>
+      <c r="M5" s="44" t="n"/>
+      <c r="N5" s="44" t="n"/>
+      <c r="O5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Per-policy BASE</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>REN: &lt;$1,200=$4 | $1,200-$1,799=$6 | $1,800-$2,499=$8 | $2,500+=$10</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
+      <c r="I6" s="44" t="n"/>
+      <c r="J6" s="44" t="n"/>
+      <c r="K6" s="44" t="n"/>
+      <c r="L6" s="44" t="n"/>
+      <c r="M6" s="44" t="n"/>
+      <c r="N6" s="44" t="n"/>
+      <c r="O6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Collected incentive</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Only on policies &gt; $1,200 premium. 15-19%=+$1 | 20-24%=+$2 | 25-99%=+$5 | 100% PIF=+$8</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+      <c r="I7" s="44" t="n"/>
+      <c r="J7" s="44" t="n"/>
+      <c r="K7" s="44" t="n"/>
+      <c r="L7" s="44" t="n"/>
+      <c r="M7" s="44" t="n"/>
+      <c r="N7" s="44" t="n"/>
+      <c r="O7" s="45" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Minimums (monthly)</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>NB premium &gt;= $45,000 | REN retention &gt;= 30% of book | RWR follows NB gate</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+      <c r="I8" s="44" t="n"/>
+      <c r="J8" s="44" t="n"/>
+      <c r="K8" s="44" t="n"/>
+      <c r="L8" s="44" t="n"/>
+      <c r="M8" s="44" t="n"/>
+      <c r="N8" s="44" t="n"/>
+      <c r="O8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Chargeback</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+      <c r="I9" s="44" t="n"/>
+      <c r="J9" s="44" t="n"/>
+      <c r="K9" s="44" t="n"/>
+      <c r="L9" s="44" t="n"/>
+      <c r="M9" s="44" t="n"/>
+      <c r="N9" s="44" t="n"/>
+      <c r="O9" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ONE ROW PER POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Policy #</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Carrier</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Type (NB/RWR/REN)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Eff Date</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Exp Date</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>90-Day Review Date</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Written Premium</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Carrier Comm %</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Collected $</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>BI?</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>UM?</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>BI+UM Bundle?</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Comp?</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Coll?</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Down Payment $</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Collected % (calc)</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>PIF?</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>90-Day Review Date</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Target Bonus</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>Cap</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>Final Paid</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>Chargeback?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr"/>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr"/>
-      <c r="D5" s="14" t="inlineStr"/>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="14" t="inlineStr"/>
-      <c r="G5" s="14" t="inlineStr"/>
-      <c r="H5" s="14" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
-      <c r="J5" s="14" t="inlineStr"/>
-      <c r="K5" s="14" t="inlineStr"/>
-      <c r="L5" s="14" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
-      <c r="N5" s="14" t="inlineStr"/>
-      <c r="O5" s="14" t="inlineStr"/>
-      <c r="P5" s="14" t="inlineStr"/>
-      <c r="Q5" s="14" t="inlineStr"/>
-      <c r="R5" s="14" t="inlineStr"/>
-      <c r="S5" s="14" t="inlineStr"/>
-      <c r="T5" s="14" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="14" t="inlineStr"/>
-      <c r="D6" s="14" t="inlineStr"/>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="14" t="inlineStr"/>
-      <c r="G6" s="14" t="inlineStr"/>
-      <c r="H6" s="14" t="inlineStr"/>
-      <c r="I6" s="14" t="inlineStr"/>
-      <c r="J6" s="14" t="inlineStr"/>
-      <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="14" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
-      <c r="N6" s="14" t="inlineStr"/>
-      <c r="O6" s="14" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr"/>
-      <c r="Q6" s="14" t="inlineStr"/>
-      <c r="R6" s="14" t="inlineStr"/>
-      <c r="S6" s="14" t="inlineStr"/>
-      <c r="T6" s="14" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr"/>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr"/>
-      <c r="J7" s="14" t="inlineStr"/>
-      <c r="K7" s="14" t="inlineStr"/>
-      <c r="L7" s="14" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
-      <c r="N7" s="14" t="inlineStr"/>
-      <c r="O7" s="14" t="inlineStr"/>
-      <c r="P7" s="14" t="inlineStr"/>
-      <c r="Q7" s="14" t="inlineStr"/>
-      <c r="R7" s="14" t="inlineStr"/>
-      <c r="S7" s="14" t="inlineStr"/>
-      <c r="T7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr"/>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="14" t="inlineStr"/>
-      <c r="D8" s="14" t="inlineStr"/>
-      <c r="E8" s="14" t="inlineStr"/>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr"/>
-      <c r="J8" s="14" t="inlineStr"/>
-      <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="14" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
-      <c r="N8" s="14" t="inlineStr"/>
-      <c r="O8" s="14" t="inlineStr"/>
-      <c r="P8" s="14" t="inlineStr"/>
-      <c r="Q8" s="14" t="inlineStr"/>
-      <c r="R8" s="14" t="inlineStr"/>
-      <c r="S8" s="14" t="inlineStr"/>
-      <c r="T8" s="14" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr"/>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
-      <c r="J9" s="14" t="inlineStr"/>
-      <c r="K9" s="14" t="inlineStr"/>
-      <c r="L9" s="14" t="inlineStr"/>
-      <c r="M9" s="14" t="inlineStr"/>
-      <c r="N9" s="14" t="inlineStr"/>
-      <c r="O9" s="14" t="inlineStr"/>
-      <c r="P9" s="14" t="inlineStr"/>
-      <c r="Q9" s="14" t="inlineStr"/>
-      <c r="R9" s="14" t="inlineStr"/>
-      <c r="S9" s="14" t="inlineStr"/>
-      <c r="T9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr"/>
-      <c r="J10" s="14" t="inlineStr"/>
-      <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="14" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
-      <c r="N10" s="14" t="inlineStr"/>
-      <c r="O10" s="14" t="inlineStr"/>
-      <c r="P10" s="14" t="inlineStr"/>
-      <c r="Q10" s="14" t="inlineStr"/>
-      <c r="R10" s="14" t="inlineStr"/>
-      <c r="S10" s="14" t="inlineStr"/>
-      <c r="T10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr"/>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr"/>
-      <c r="K11" s="14" t="inlineStr"/>
-      <c r="L11" s="14" t="inlineStr"/>
-      <c r="M11" s="14" t="inlineStr"/>
-      <c r="N11" s="14" t="inlineStr"/>
-      <c r="O11" s="14" t="inlineStr"/>
-      <c r="P11" s="14" t="inlineStr"/>
-      <c r="Q11" s="14" t="inlineStr"/>
-      <c r="R11" s="14" t="inlineStr"/>
-      <c r="S11" s="14" t="inlineStr"/>
-      <c r="T11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
-      <c r="J12" s="14" t="inlineStr"/>
-      <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="14" t="inlineStr"/>
-      <c r="M12" s="14" t="inlineStr"/>
-      <c r="N12" s="14" t="inlineStr"/>
-      <c r="O12" s="14" t="inlineStr"/>
-      <c r="P12" s="14" t="inlineStr"/>
-      <c r="Q12" s="14" t="inlineStr"/>
-      <c r="R12" s="14" t="inlineStr"/>
-      <c r="S12" s="14" t="inlineStr"/>
-      <c r="T12" s="14" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Per-Policy Base $</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Collected Incentive $</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Total Bonus $</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr"/>
@@ -3296,11 +3343,6 @@
       <c r="M13" s="14" t="inlineStr"/>
       <c r="N13" s="14" t="inlineStr"/>
       <c r="O13" s="14" t="inlineStr"/>
-      <c r="P13" s="14" t="inlineStr"/>
-      <c r="Q13" s="14" t="inlineStr"/>
-      <c r="R13" s="14" t="inlineStr"/>
-      <c r="S13" s="14" t="inlineStr"/>
-      <c r="T13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr"/>
@@ -3318,11 +3360,6 @@
       <c r="M14" s="14" t="inlineStr"/>
       <c r="N14" s="14" t="inlineStr"/>
       <c r="O14" s="14" t="inlineStr"/>
-      <c r="P14" s="14" t="inlineStr"/>
-      <c r="Q14" s="14" t="inlineStr"/>
-      <c r="R14" s="14" t="inlineStr"/>
-      <c r="S14" s="14" t="inlineStr"/>
-      <c r="T14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr"/>
@@ -3340,11 +3377,6 @@
       <c r="M15" s="14" t="inlineStr"/>
       <c r="N15" s="14" t="inlineStr"/>
       <c r="O15" s="14" t="inlineStr"/>
-      <c r="P15" s="14" t="inlineStr"/>
-      <c r="Q15" s="14" t="inlineStr"/>
-      <c r="R15" s="14" t="inlineStr"/>
-      <c r="S15" s="14" t="inlineStr"/>
-      <c r="T15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr"/>
@@ -3362,11 +3394,6 @@
       <c r="M16" s="14" t="inlineStr"/>
       <c r="N16" s="14" t="inlineStr"/>
       <c r="O16" s="14" t="inlineStr"/>
-      <c r="P16" s="14" t="inlineStr"/>
-      <c r="Q16" s="14" t="inlineStr"/>
-      <c r="R16" s="14" t="inlineStr"/>
-      <c r="S16" s="14" t="inlineStr"/>
-      <c r="T16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr"/>
@@ -3384,11 +3411,6 @@
       <c r="M17" s="14" t="inlineStr"/>
       <c r="N17" s="14" t="inlineStr"/>
       <c r="O17" s="14" t="inlineStr"/>
-      <c r="P17" s="14" t="inlineStr"/>
-      <c r="Q17" s="14" t="inlineStr"/>
-      <c r="R17" s="14" t="inlineStr"/>
-      <c r="S17" s="14" t="inlineStr"/>
-      <c r="T17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr"/>
@@ -3406,11 +3428,6 @@
       <c r="M18" s="14" t="inlineStr"/>
       <c r="N18" s="14" t="inlineStr"/>
       <c r="O18" s="14" t="inlineStr"/>
-      <c r="P18" s="14" t="inlineStr"/>
-      <c r="Q18" s="14" t="inlineStr"/>
-      <c r="R18" s="14" t="inlineStr"/>
-      <c r="S18" s="14" t="inlineStr"/>
-      <c r="T18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr"/>
@@ -3428,11 +3445,6 @@
       <c r="M19" s="14" t="inlineStr"/>
       <c r="N19" s="14" t="inlineStr"/>
       <c r="O19" s="14" t="inlineStr"/>
-      <c r="P19" s="14" t="inlineStr"/>
-      <c r="Q19" s="14" t="inlineStr"/>
-      <c r="R19" s="14" t="inlineStr"/>
-      <c r="S19" s="14" t="inlineStr"/>
-      <c r="T19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr"/>
@@ -3450,11 +3462,6 @@
       <c r="M20" s="14" t="inlineStr"/>
       <c r="N20" s="14" t="inlineStr"/>
       <c r="O20" s="14" t="inlineStr"/>
-      <c r="P20" s="14" t="inlineStr"/>
-      <c r="Q20" s="14" t="inlineStr"/>
-      <c r="R20" s="14" t="inlineStr"/>
-      <c r="S20" s="14" t="inlineStr"/>
-      <c r="T20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr"/>
@@ -3472,11 +3479,6 @@
       <c r="M21" s="14" t="inlineStr"/>
       <c r="N21" s="14" t="inlineStr"/>
       <c r="O21" s="14" t="inlineStr"/>
-      <c r="P21" s="14" t="inlineStr"/>
-      <c r="Q21" s="14" t="inlineStr"/>
-      <c r="R21" s="14" t="inlineStr"/>
-      <c r="S21" s="14" t="inlineStr"/>
-      <c r="T21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr"/>
@@ -3494,11 +3496,6 @@
       <c r="M22" s="14" t="inlineStr"/>
       <c r="N22" s="14" t="inlineStr"/>
       <c r="O22" s="14" t="inlineStr"/>
-      <c r="P22" s="14" t="inlineStr"/>
-      <c r="Q22" s="14" t="inlineStr"/>
-      <c r="R22" s="14" t="inlineStr"/>
-      <c r="S22" s="14" t="inlineStr"/>
-      <c r="T22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr"/>
@@ -3516,11 +3513,6 @@
       <c r="M23" s="14" t="inlineStr"/>
       <c r="N23" s="14" t="inlineStr"/>
       <c r="O23" s="14" t="inlineStr"/>
-      <c r="P23" s="14" t="inlineStr"/>
-      <c r="Q23" s="14" t="inlineStr"/>
-      <c r="R23" s="14" t="inlineStr"/>
-      <c r="S23" s="14" t="inlineStr"/>
-      <c r="T23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr"/>
@@ -3538,11 +3530,6 @@
       <c r="M24" s="14" t="inlineStr"/>
       <c r="N24" s="14" t="inlineStr"/>
       <c r="O24" s="14" t="inlineStr"/>
-      <c r="P24" s="14" t="inlineStr"/>
-      <c r="Q24" s="14" t="inlineStr"/>
-      <c r="R24" s="14" t="inlineStr"/>
-      <c r="S24" s="14" t="inlineStr"/>
-      <c r="T24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr"/>
@@ -3560,11 +3547,6 @@
       <c r="M25" s="14" t="inlineStr"/>
       <c r="N25" s="14" t="inlineStr"/>
       <c r="O25" s="14" t="inlineStr"/>
-      <c r="P25" s="14" t="inlineStr"/>
-      <c r="Q25" s="14" t="inlineStr"/>
-      <c r="R25" s="14" t="inlineStr"/>
-      <c r="S25" s="14" t="inlineStr"/>
-      <c r="T25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr"/>
@@ -3582,11 +3564,6 @@
       <c r="M26" s="14" t="inlineStr"/>
       <c r="N26" s="14" t="inlineStr"/>
       <c r="O26" s="14" t="inlineStr"/>
-      <c r="P26" s="14" t="inlineStr"/>
-      <c r="Q26" s="14" t="inlineStr"/>
-      <c r="R26" s="14" t="inlineStr"/>
-      <c r="S26" s="14" t="inlineStr"/>
-      <c r="T26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr"/>
@@ -3604,11 +3581,6 @@
       <c r="M27" s="14" t="inlineStr"/>
       <c r="N27" s="14" t="inlineStr"/>
       <c r="O27" s="14" t="inlineStr"/>
-      <c r="P27" s="14" t="inlineStr"/>
-      <c r="Q27" s="14" t="inlineStr"/>
-      <c r="R27" s="14" t="inlineStr"/>
-      <c r="S27" s="14" t="inlineStr"/>
-      <c r="T27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr"/>
@@ -3626,11 +3598,6 @@
       <c r="M28" s="14" t="inlineStr"/>
       <c r="N28" s="14" t="inlineStr"/>
       <c r="O28" s="14" t="inlineStr"/>
-      <c r="P28" s="14" t="inlineStr"/>
-      <c r="Q28" s="14" t="inlineStr"/>
-      <c r="R28" s="14" t="inlineStr"/>
-      <c r="S28" s="14" t="inlineStr"/>
-      <c r="T28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr"/>
@@ -3648,11 +3615,6 @@
       <c r="M29" s="14" t="inlineStr"/>
       <c r="N29" s="14" t="inlineStr"/>
       <c r="O29" s="14" t="inlineStr"/>
-      <c r="P29" s="14" t="inlineStr"/>
-      <c r="Q29" s="14" t="inlineStr"/>
-      <c r="R29" s="14" t="inlineStr"/>
-      <c r="S29" s="14" t="inlineStr"/>
-      <c r="T29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr"/>
@@ -3670,11 +3632,6 @@
       <c r="M30" s="14" t="inlineStr"/>
       <c r="N30" s="14" t="inlineStr"/>
       <c r="O30" s="14" t="inlineStr"/>
-      <c r="P30" s="14" t="inlineStr"/>
-      <c r="Q30" s="14" t="inlineStr"/>
-      <c r="R30" s="14" t="inlineStr"/>
-      <c r="S30" s="14" t="inlineStr"/>
-      <c r="T30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr"/>
@@ -3692,11 +3649,6 @@
       <c r="M31" s="14" t="inlineStr"/>
       <c r="N31" s="14" t="inlineStr"/>
       <c r="O31" s="14" t="inlineStr"/>
-      <c r="P31" s="14" t="inlineStr"/>
-      <c r="Q31" s="14" t="inlineStr"/>
-      <c r="R31" s="14" t="inlineStr"/>
-      <c r="S31" s="14" t="inlineStr"/>
-      <c r="T31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr"/>
@@ -3714,11 +3666,6 @@
       <c r="M32" s="14" t="inlineStr"/>
       <c r="N32" s="14" t="inlineStr"/>
       <c r="O32" s="14" t="inlineStr"/>
-      <c r="P32" s="14" t="inlineStr"/>
-      <c r="Q32" s="14" t="inlineStr"/>
-      <c r="R32" s="14" t="inlineStr"/>
-      <c r="S32" s="14" t="inlineStr"/>
-      <c r="T32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr"/>
@@ -3736,11 +3683,6 @@
       <c r="M33" s="14" t="inlineStr"/>
       <c r="N33" s="14" t="inlineStr"/>
       <c r="O33" s="14" t="inlineStr"/>
-      <c r="P33" s="14" t="inlineStr"/>
-      <c r="Q33" s="14" t="inlineStr"/>
-      <c r="R33" s="14" t="inlineStr"/>
-      <c r="S33" s="14" t="inlineStr"/>
-      <c r="T33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr"/>
@@ -3758,16 +3700,155 @@
       <c r="M34" s="14" t="inlineStr"/>
       <c r="N34" s="14" t="inlineStr"/>
       <c r="O34" s="14" t="inlineStr"/>
-      <c r="P34" s="14" t="inlineStr"/>
-      <c r="Q34" s="14" t="inlineStr"/>
-      <c r="R34" s="14" t="inlineStr"/>
-      <c r="S34" s="14" t="inlineStr"/>
-      <c r="T34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr"/>
+      <c r="B35" s="14" t="inlineStr"/>
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr"/>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+      <c r="N35" s="14" t="inlineStr"/>
+      <c r="O35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr"/>
+      <c r="B36" s="14" t="inlineStr"/>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr"/>
+      <c r="H36" s="14" t="inlineStr"/>
+      <c r="I36" s="14" t="inlineStr"/>
+      <c r="J36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="inlineStr"/>
+      <c r="L36" s="14" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+      <c r="N36" s="14" t="inlineStr"/>
+      <c r="O36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr"/>
+      <c r="B37" s="14" t="inlineStr"/>
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+      <c r="N37" s="14" t="inlineStr"/>
+      <c r="O37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr"/>
+      <c r="B38" s="14" t="inlineStr"/>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr"/>
+      <c r="I38" s="14" t="inlineStr"/>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+      <c r="N38" s="14" t="inlineStr"/>
+      <c r="O38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr"/>
+      <c r="B39" s="14" t="inlineStr"/>
+      <c r="C39" s="14" t="inlineStr"/>
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="14" t="inlineStr"/>
+      <c r="L39" s="14" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+      <c r="N39" s="14" t="inlineStr"/>
+      <c r="O39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr"/>
+      <c r="B40" s="14" t="inlineStr"/>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="inlineStr"/>
+      <c r="H40" s="14" t="inlineStr"/>
+      <c r="I40" s="14" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+      <c r="N40" s="14" t="inlineStr"/>
+      <c r="O40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr"/>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="14" t="inlineStr"/>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+      <c r="N41" s="14" t="inlineStr"/>
+      <c r="O41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr"/>
+      <c r="B42" s="14" t="inlineStr"/>
+      <c r="C42" s="14" t="inlineStr"/>
+      <c r="D42" s="14" t="inlineStr"/>
+      <c r="E42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr"/>
+      <c r="G42" s="14" t="inlineStr"/>
+      <c r="H42" s="14" t="inlineStr"/>
+      <c r="I42" s="14" t="inlineStr"/>
+      <c r="J42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="inlineStr"/>
+      <c r="L42" s="14" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+      <c r="N42" s="14" t="inlineStr"/>
+      <c r="O42" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
+  <mergeCells count="10">
+    <mergeCell ref="B9:O9"/>
+    <mergeCell ref="B8:O8"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="B7:O7"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4501,13 +4582,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>11841.91676666667</v>
+        <v>12644.66911666667</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13078.83037222222</v>
+        <v>13911.87745277778</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>13729.91676666667</v>
+        <v>14532.66911666667</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4522,13 +4603,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>7452.005044444445</v>
+        <v>7741.538411111112</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>9529.59023888889</v>
+        <v>10000.33225</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>10818.24337777778</v>
+        <v>11370.11997222222</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4621,13 +4702,13 @@
         <v>350</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>487</v>
+        <v>508.6927777777778</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>261</v>
+        <v>263.45</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>-89</v>
+        <v>-86.55000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4654,13 +4735,13 @@
         <v>660</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>580.5894111111111</v>
+        <v>610.95985</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>275.5894111111111</v>
+        <v>285.4735277777778</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>-384.4105888888889</v>
+        <v>-374.5264722222222</v>
       </c>
     </row>
     <row r="16">
@@ -4687,7 +4768,7 @@
         <v>740</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>524</v>
+        <v>563.6958333333333</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>225</v>
@@ -4720,13 +4801,13 @@
         <v>490</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>434</v>
+        <v>465.0943611111111</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>231</v>
+        <v>231.9603888888889</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>-259</v>
+        <v>-258.0396111111111</v>
       </c>
     </row>
     <row r="18">
@@ -4753,13 +4834,13 @@
         <v>350</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>367</v>
+        <v>376.7632944444445</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>241</v>
+        <v>241.7166666666667</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-109</v>
+        <v>-108.2833333333333</v>
       </c>
     </row>
     <row r="19">
@@ -4786,13 +4867,13 @@
         <v>550</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>521</v>
+        <v>555.3496444444445</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>249</v>
+        <v>252.2254555555556</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-301</v>
+        <v>-297.7745444444445</v>
       </c>
     </row>
     <row r="20">
@@ -4819,13 +4900,13 @@
         <v>250</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>440</v>
+        <v>441.8427777777778</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>253</v>
+        <v>254.8427777777778</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>3</v>
+        <v>4.842777777777769</v>
       </c>
     </row>
     <row r="21">
@@ -4852,13 +4933,13 @@
         <v>740</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>608</v>
+        <v>649.3512055555556</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>279</v>
+        <v>282.4609333333333</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-461</v>
+        <v>-457.5390666666667</v>
       </c>
     </row>
     <row r="22">
@@ -4918,13 +4999,13 @@
         <v>600</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>452.5416111111111</v>
+        <v>488.5466388888889</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>233</v>
+        <v>233.4994444444444</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>-367</v>
+        <v>-366.5005555555556</v>
       </c>
     </row>
     <row r="24">
@@ -4951,13 +5032,13 @@
         <v>350</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>405.94</v>
+        <v>427.1902277777777</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>259.94</v>
+        <v>267.35</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>-90.06</v>
+        <v>-82.64999999999998</v>
       </c>
     </row>
     <row r="25">
@@ -4984,7 +5065,7 @@
         <v>450</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>471</v>
+        <v>508.5900444444445</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>237</v>
@@ -5017,13 +5098,13 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>507.0011111111111</v>
+        <v>525.2001111111111</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>507.0011111111111</v>
+        <v>525.2001111111111</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>157.0011111111111</v>
+        <v>175.2001111111111</v>
       </c>
     </row>
     <row r="27">
@@ -5050,13 +5131,13 @@
         <v>1020</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>728.9375</v>
+        <v>824.7438888888889</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>728.9375</v>
+        <v>824.7438888888889</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>-291.0625</v>
+        <v>-195.2561111111111</v>
       </c>
     </row>
     <row r="28">
@@ -5083,13 +5164,13 @@
         <v>710</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>521</v>
+        <v>536.8303333333333</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>229</v>
+        <v>229.2411111111111</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>-481</v>
+        <v>-480.7588888888889</v>
       </c>
     </row>
     <row r="29">
@@ -5116,7 +5197,7 @@
         <v>490</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>438.8841111111111</v>
+        <v>476.2102777777778</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>225</v>
@@ -5149,13 +5230,13 @@
         <v>350</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>391.4306555555556</v>
+        <v>414.9553611111111</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>251.271</v>
+        <v>254.6775</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>-98.72899999999998</v>
+        <v>-95.32249999999999</v>
       </c>
     </row>
     <row r="31">
@@ -5182,13 +5263,13 @@
         <v>590</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>669</v>
+        <v>721.1624666666667</v>
       </c>
       <c r="H31" s="17" t="n">
-        <v>669</v>
+        <v>721.1624666666667</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>79</v>
+        <v>131.1624666666667</v>
       </c>
     </row>
     <row r="32">
@@ -5215,13 +5296,13 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>506.5532666666667</v>
+        <v>546.4119777777778</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>280.4844333333334</v>
+        <v>285.7110833333334</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>-69.51556666666664</v>
+        <v>-64.28891666666664</v>
       </c>
     </row>
     <row r="33">
@@ -5248,13 +5329,13 @@
         <v>720</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>649.9615888888889</v>
+        <v>731.5091666666667</v>
       </c>
       <c r="H33" s="17" t="n">
-        <v>649.9615888888889</v>
+        <v>731.5091666666667</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>-70.03841111111115</v>
+        <v>11.50916666666672</v>
       </c>
     </row>
     <row r="34">
@@ -5281,7 +5362,7 @@
         <v>470</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>404</v>
+        <v>427.2071666666667</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>225</v>
@@ -5314,13 +5395,13 @@
         <v>490</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>466.3836222222222</v>
+        <v>504.7810555555556</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>229.7916666666667</v>
+        <v>230.2666666666667</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>-260.2083333333334</v>
+        <v>-259.7333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -5347,13 +5428,13 @@
         <v>350</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>405.6938888888889</v>
+        <v>434.6524444444444</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>246.0283333333333</v>
+        <v>248.0472222222222</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>-103.9716666666667</v>
+        <v>-101.9527777777778</v>
       </c>
     </row>
     <row r="37">
@@ -5380,7 +5461,7 @@
         <v>350</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>457</v>
+        <v>499.9282111111111</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>237</v>
@@ -5399,13 +5480,13 @@
         <v>12220</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>11841.91676666667</v>
+        <v>12644.66911666667</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>7452.005044444445</v>
+        <v>7741.538411111112</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-4767.994955555555</v>
+        <v>-4478.461588888888</v>
       </c>
     </row>
     <row r="40">
@@ -5486,13 +5567,13 @@
         <v>250</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>529</v>
+        <v>550.6927777777778</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>327</v>
+        <v>339.4047222222222</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>77</v>
+        <v>89.40472222222223</v>
       </c>
     </row>
     <row r="43">
@@ -5519,13 +5600,13 @@
         <v>350</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>668</v>
+        <v>705.3188944444445</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>435</v>
+        <v>462.0757333333333</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>85</v>
+        <v>112.0757333333333</v>
       </c>
     </row>
     <row r="44">
@@ -5552,13 +5633,13 @@
         <v>500</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>596</v>
+        <v>635.6958333333333</v>
       </c>
       <c r="H44" s="17" t="n">
-        <v>369</v>
+        <v>378.6040277777778</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>-131</v>
+        <v>-121.3959722222222</v>
       </c>
     </row>
     <row r="45">
@@ -5585,13 +5666,13 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>468</v>
+        <v>499.0943611111111</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>301</v>
+        <v>311.9370833333334</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>-49</v>
+        <v>-38.06291666666664</v>
       </c>
     </row>
     <row r="46">
@@ -5618,13 +5699,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>395</v>
+        <v>404.7632944444445</v>
       </c>
       <c r="H46" s="17" t="n">
-        <v>297</v>
+        <v>302.2399805555556</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>297</v>
+        <v>302.2399805555556</v>
       </c>
     </row>
     <row r="47">
@@ -5651,13 +5732,13 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>587</v>
+        <v>619.7369166666666</v>
       </c>
       <c r="H47" s="17" t="n">
-        <v>369</v>
+        <v>378.1163277777778</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>19</v>
+        <v>28.11632777777777</v>
       </c>
     </row>
     <row r="48">
@@ -5684,13 +5765,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>484</v>
+        <v>491.0213888888889</v>
       </c>
       <c r="H48" s="17" t="n">
-        <v>327</v>
+        <v>334.0213888888889</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>327</v>
+        <v>334.0213888888889</v>
       </c>
     </row>
     <row r="49">
@@ -5717,13 +5798,13 @@
         <v>460</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>692</v>
+        <v>733.3512055555556</v>
       </c>
       <c r="H49" s="17" t="n">
-        <v>447</v>
+        <v>464.8899888888889</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>-13</v>
+        <v>4.889988888888865</v>
       </c>
     </row>
     <row r="50">
@@ -5783,13 +5864,13 @@
         <v>350</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>495.5405</v>
+        <v>532.5444166666666</v>
       </c>
       <c r="H51" s="17" t="n">
-        <v>328.2696944444444</v>
+        <v>345.1742361111111</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-21.73030555555556</v>
+        <v>-4.825763888888901</v>
       </c>
     </row>
     <row r="52">
@@ -5816,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>461.6612</v>
+        <v>490.6326277777778</v>
       </c>
       <c r="H52" s="17" t="n">
-        <v>339.6612</v>
+        <v>358.653</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>339.6612</v>
+        <v>358.653</v>
       </c>
     </row>
     <row r="53">
@@ -5849,7 +5930,7 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>513</v>
+        <v>542.1377722222222</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>321</v>
@@ -5882,13 +5963,13 @@
         <v>350</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>549.6831111111111</v>
+        <v>572.2231111111112</v>
       </c>
       <c r="H54" s="17" t="n">
-        <v>549.6831111111111</v>
+        <v>572.2231111111112</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>199.6831111111111</v>
+        <v>222.2231111111112</v>
       </c>
     </row>
     <row r="55">
@@ -5915,13 +5996,13 @@
         <v>680</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>842</v>
+        <v>937.8063888888889</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>842</v>
+        <v>937.8063888888889</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>162</v>
+        <v>257.8063888888889</v>
       </c>
     </row>
     <row r="56">
@@ -5948,13 +6029,13 @@
         <v>470</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>569</v>
+        <v>584.8303333333333</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>325</v>
+        <v>333.0357222222222</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>-145</v>
+        <v>-136.9642777777778</v>
       </c>
     </row>
     <row r="57">
@@ -5981,13 +6062,13 @@
         <v>350</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>466.8841111111111</v>
+        <v>504.2102777777778</v>
       </c>
       <c r="H57" s="17" t="n">
-        <v>284.7370555555556</v>
+        <v>290.3426388888889</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>-65.26294444444443</v>
+        <v>-59.65736111111113</v>
       </c>
     </row>
     <row r="58">
@@ -6014,13 +6095,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>409.1596555555556</v>
+        <v>431.5488611111111</v>
       </c>
       <c r="H58" s="17" t="n">
-        <v>289</v>
+        <v>295.6270277777778</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>289</v>
+        <v>295.6270277777778</v>
       </c>
     </row>
     <row r="59">
@@ -6047,13 +6128,13 @@
         <v>450</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>711</v>
+        <v>763.1624666666667</v>
       </c>
       <c r="H59" s="17" t="n">
-        <v>711</v>
+        <v>763.1624666666667</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>261</v>
+        <v>313.1624666666667</v>
       </c>
     </row>
     <row r="60">
@@ -6080,13 +6161,13 @@
         <v>250</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>522.5532666666667</v>
+        <v>562.4119777777778</v>
       </c>
       <c r="H60" s="17" t="n">
-        <v>315.6855166666667</v>
+        <v>325.7137916666667</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>65.68551666666667</v>
+        <v>75.71379166666668</v>
       </c>
     </row>
     <row r="61">
@@ -6113,13 +6194,13 @@
         <v>500</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>734.9807944444444</v>
+        <v>824.4546416666666</v>
       </c>
       <c r="H61" s="17" t="n">
-        <v>734.9807944444444</v>
+        <v>824.4546416666666</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>234.9807944444444</v>
+        <v>324.4546416666666</v>
       </c>
     </row>
     <row r="62">
@@ -6146,13 +6227,13 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>476</v>
+        <v>499.2071666666666</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>333</v>
+        <v>339.0545</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>83</v>
+        <v>89.05450000000002</v>
       </c>
     </row>
     <row r="63">
@@ -6179,13 +6260,13 @@
         <v>350</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>497.9086222222222</v>
+        <v>536.3060555555555</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>299.7793111111111</v>
+        <v>309.9482777777778</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v>-50.2206888888889</v>
+        <v>-40.05172222222222</v>
       </c>
     </row>
     <row r="64">
@@ -6212,13 +6293,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>459.4591111111111</v>
+        <v>502.2017777777778</v>
       </c>
       <c r="H64" s="17" t="n">
-        <v>341.7935555555555</v>
+        <v>363.9838888888889</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>341.7935555555555</v>
+        <v>363.9838888888889</v>
       </c>
     </row>
     <row r="65">
@@ -6245,13 +6326,13 @@
         <v>250</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>490</v>
+        <v>527.5249055555555</v>
       </c>
       <c r="H65" s="17" t="n">
-        <v>303</v>
+        <v>309.8633055555555</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v>53</v>
+        <v>59.86330555555554</v>
       </c>
     </row>
     <row r="66">
@@ -6264,13 +6345,13 @@
         <v>7110</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>13078.83037222222</v>
+        <v>13911.87745277778</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>9529.590238888888</v>
+        <v>10000.33225</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>2419.590238888888</v>
+        <v>2890.332249999999</v>
       </c>
     </row>
     <row r="69">
@@ -6283,14 +6364,14 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $7,452 (less, because few agents clear the $45k NB gate today).</t>
+          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $7,742 (less, because few agents clear the $45k NB gate today).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $10,818 (89% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,370 (93% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6567,7 +6648,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Below 25%</t>
+          <t>Below 15%</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -6582,58 +6663,58 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$1,500 policy, 15% down -&gt; $0 incentive</t>
+          <t>$1,500 policy, 10% down -&gt; $0 incentive</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>25% to 49%</t>
+          <t>15% to 19%</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>+$2 per policy</t>
+          <t>+$1 per policy</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Standard down. Small incentive.</t>
+          <t>Minimum down. Small bump.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>$1,500 policy, 30% down -&gt; +$2</t>
+          <t>$1,500 policy, 17% down -&gt; +$1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>50% to 99%</t>
+          <t>20% to 24%</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>+$3 per policy</t>
+          <t>+$2 per policy</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>High collection. Higher incentive.</t>
+          <t>Standard down. Standard bump.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$1,500 policy, 60% down -&gt; +$3</t>
+          <t>$1,500 policy, 22% down -&gt; +$2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>100% PIF</t>
+          <t>25% to 99%</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6643,308 +6724,317 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+          <t>High collection. Big bump.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>$1,500 policy PIF -&gt; +$5</t>
+          <t>$1,500 policy, 30% down -&gt; +$5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>100% PIF</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>+$8 per policy</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>$1,500 policy PIF -&gt; +$8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
           <t>Policy with premium &lt;= $1,200</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>$0 incentive</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Low-premium policies do not earn the incentive.</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>$800 policy at 50% -&gt; base only</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>3. BOOK RETENTION BONUS (separate, not gated by monthly minimums)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Math</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Retention Rate</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>% retained</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>(NB premium written 6 months ago that is STILL ACTIVE today) / (NB premium written 6 months ago)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Monthly Pool</t>
+          <t>Retention Rate</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>% retained</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Pool of bonus dollars at stake for retention.</t>
+          <t>(NB premium written 6 months ago that is STILL ACTIVE today) / (NB premium written 6 months ago)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Retention Bonus</t>
+          <t>Monthly Pool</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Rate x Pool</t>
+          <t>$300</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>e.g., 75% x $300 = $225/mo. 90% x $300 = $270/mo. 100% x $300 = $300/mo.</t>
+          <t>Pool of bonus dollars at stake for retention.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
+          <t>Retention Bonus</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Rate x Pool</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>e.g., 75% x $300 = $225/mo. 90% x $300 = $270/mo. 100% x $300 = $300/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
           <t>Modeling assumption</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>75% retention rate</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>For modeling in this workbook we use 75% (industry typical) = $225/mo. Actual is computed monthly from the agency's history.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>4. RULES THAT APPLY ON TOP</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>How it works</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - NB</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>$45,000 written premium</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Monthly Minimum - REN</t>
+          <t>Monthly Minimum - NB</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Retain &gt;= 30% of agent's book</t>
+          <t>$45,000 written premium</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>REN base + REN collected paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
+          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Monthly Minimum - RWR</t>
+          <t>Monthly Minimum - REN</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>NB gate met (or both)</t>
+          <t>Retain &gt;= 30% of agent's book</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
+          <t>REN base + REN collected paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Retention Bonus exception</t>
+          <t>Monthly Minimum - RWR</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Always paid</t>
+          <t>NB gate met (or both)</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
+          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Retention Bonus exception</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>3 months (90 days)</t>
+          <t>Always paid</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Excel Tracker</t>
+          <t>Chargeback</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Required for every policy</t>
+          <t>3 months (90 days)</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
+          <t>Excel Tracker</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Required for every policy</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
           <t>Renewal Book of Business</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Assigned per agent</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Each agent has an assigned renewal book. Newer agents who do not have their own renewals get a book reassigned from former employees. The agent is responsible for renewing that book.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
@@ -6954,7 +7044,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
+          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr"/>
@@ -6967,7 +7057,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr"/>
@@ -6975,165 +7065,161 @@
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>NB base (tier)</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>38 policies in tier "$1,200-$1,799" x $7</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>$266</t>
-        </is>
-      </c>
+          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>NB collected incentive</t>
+          <t>NB base (tier)</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$0/policy</t>
+          <t>38 policies in tier "$1,200-$1,799" x $7</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$266</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>REN base (tier)</t>
+          <t>NB collected incentive</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>7 policies in tier "Under $1,200" x $4</t>
+          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>$28</t>
+          <t>$33</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>REN collected incentive</t>
+          <t>REN base (tier)</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>~14% &gt;$1,200, collected 52% -&gt; +$3/policy</t>
+          <t>7 policies in tier "Under $1,200" x $4</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>$3</t>
+          <t>$28</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>RWR base (tier)</t>
+          <t>REN collected incentive</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>69 policies in tier "$1,200-$1,799" x $3</t>
+          <t>~14% &gt;$1,200, collected 52% -&gt; +$5/policy</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>$207</t>
+          <t>$5</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>RWR collected incentive</t>
+          <t>RWR base (tier)</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>~44% &gt;$1,200, collected 20% -&gt; +$0/policy</t>
+          <t>69 policies in tier "$1,200-$1,799" x $3</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$207</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus</t>
+          <t>RWR collected incentive</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>75% retention x $300 pool</t>
+          <t>~44% &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>$225</t>
+          <t>$61</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Subtotal target</t>
+          <t>Retention bonus</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>(everything before gates)</t>
+          <t>75% retention x $300 pool</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>$729</t>
+          <t>$225</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>NB gate ($45,000)</t>
+          <t>Subtotal target</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>NB written $52,435 vs $45,000</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>(everything before gates)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>$825</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>REN gate (&gt;= 30% retention)</t>
+          <t>NB gate ($45,000)</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Assumed retention 75% vs 30%</t>
+          <t>NB written $52,435 vs $45,000</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -7145,46 +7231,63 @@
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
+          <t>REN gate (&gt;= 30% retention)</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Assumed retention 75% vs 30%</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
           <t>RWR gate (both)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>Both NB and REN gates passed?</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>FINAL PAID</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B54" s="24" t="inlineStr">
         <is>
           <t>Pay only the lines whose gates passed + retention bonus</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>$728.94</t>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>$824.74</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7697,7 +7800,7 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>261</v>
+        <v>263.45</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>78.20999999999999</v>
@@ -7739,7 +7842,7 @@
         </is>
       </c>
       <c r="H31" s="16" t="n">
-        <v>253</v>
+        <v>254.8427777777778</v>
       </c>
       <c r="I31" s="16" t="n">
         <v>60.83</v>
@@ -7781,7 +7884,7 @@
         </is>
       </c>
       <c r="H32" s="16" t="n">
-        <v>507.0011111111111</v>
+        <v>525.2001111111111</v>
       </c>
       <c r="I32" s="16" t="n">
         <v>475.825</v>
@@ -7823,7 +7926,7 @@
         </is>
       </c>
       <c r="H33" s="16" t="n">
-        <v>280.4844333333334</v>
+        <v>285.7110833333334</v>
       </c>
       <c r="I33" s="16" t="n">
         <v>118.105</v>
@@ -7865,7 +7968,7 @@
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>275.5894111111111</v>
+        <v>285.4735277777778</v>
       </c>
       <c r="I34" s="16" t="n">
         <v>99.935</v>
@@ -7907,7 +8010,7 @@
         </is>
       </c>
       <c r="H35" s="16" t="n">
-        <v>279</v>
+        <v>282.4609333333333</v>
       </c>
       <c r="I35" s="16" t="n">
         <v>78.20999999999999</v>
@@ -7949,7 +8052,7 @@
         </is>
       </c>
       <c r="H36" s="16" t="n">
-        <v>728.9375</v>
+        <v>824.7438888888889</v>
       </c>
       <c r="I36" s="16" t="n">
         <v>765.74</v>
@@ -7991,7 +8094,7 @@
         </is>
       </c>
       <c r="H37" s="16" t="n">
-        <v>649.9615888888889</v>
+        <v>731.5091666666667</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>594.11</v>
@@ -8117,7 +8220,7 @@
         </is>
       </c>
       <c r="H40" s="16" t="n">
-        <v>229</v>
+        <v>229.2411111111111</v>
       </c>
       <c r="I40" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8201,7 +8304,7 @@
         </is>
       </c>
       <c r="H42" s="16" t="n">
-        <v>231</v>
+        <v>231.9603888888889</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8243,7 +8346,7 @@
         </is>
       </c>
       <c r="H43" s="16" t="n">
-        <v>233</v>
+        <v>233.4994444444444</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>17.38</v>
@@ -8327,7 +8430,7 @@
         </is>
       </c>
       <c r="H45" s="16" t="n">
-        <v>229.7916666666667</v>
+        <v>230.2666666666667</v>
       </c>
       <c r="I45" s="16" t="n">
         <v>9.875</v>
@@ -8369,7 +8472,7 @@
         </is>
       </c>
       <c r="H46" s="16" t="n">
-        <v>241</v>
+        <v>241.7166666666667</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>34.76000000000001</v>
@@ -8411,7 +8514,7 @@
         </is>
       </c>
       <c r="H47" s="16" t="n">
-        <v>259.94</v>
+        <v>267.35</v>
       </c>
       <c r="I47" s="16" t="n">
         <v>45.425</v>
@@ -8453,7 +8556,7 @@
         </is>
       </c>
       <c r="H48" s="16" t="n">
-        <v>251.271</v>
+        <v>254.6775</v>
       </c>
       <c r="I48" s="16" t="n">
         <v>54.50999999999999</v>
@@ -8495,7 +8598,7 @@
         </is>
       </c>
       <c r="H49" s="16" t="n">
-        <v>246.0283333333333</v>
+        <v>248.0472222222222</v>
       </c>
       <c r="I49" s="16" t="n">
         <v>28.44</v>
@@ -8537,7 +8640,7 @@
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>249</v>
+        <v>252.2254555555556</v>
       </c>
       <c r="I50" s="16" t="n">
         <v>52.14</v>
@@ -8621,7 +8724,7 @@
         </is>
       </c>
       <c r="H52" s="16" t="n">
-        <v>669</v>
+        <v>721.1624666666667</v>
       </c>
       <c r="I52" s="16" t="n">
         <v>574.7600000000001</v>
@@ -8764,7 +8867,7 @@
         </is>
       </c>
       <c r="H58" s="16" t="n">
-        <v>327</v>
+        <v>339.4047222222222</v>
       </c>
       <c r="I58" s="16" t="n">
         <v>147.73</v>
@@ -8806,7 +8909,7 @@
         </is>
       </c>
       <c r="H59" s="16" t="n">
-        <v>327</v>
+        <v>334.0213888888889</v>
       </c>
       <c r="I59" s="16" t="n">
         <v>147.73</v>
@@ -8848,7 +8951,7 @@
         </is>
       </c>
       <c r="H60" s="16" t="n">
-        <v>549.6831111111111</v>
+        <v>572.2231111111112</v>
       </c>
       <c r="I60" s="16" t="n">
         <v>530.905</v>
@@ -8890,7 +8993,7 @@
         </is>
       </c>
       <c r="H61" s="16" t="n">
-        <v>315.6855166666667</v>
+        <v>325.7137916666667</v>
       </c>
       <c r="I61" s="16" t="n">
         <v>190.785</v>
@@ -8932,7 +9035,7 @@
         </is>
       </c>
       <c r="H62" s="16" t="n">
-        <v>435</v>
+        <v>462.0757333333333</v>
       </c>
       <c r="I62" s="16" t="n">
         <v>304.15</v>
@@ -8974,7 +9077,7 @@
         </is>
       </c>
       <c r="H63" s="16" t="n">
-        <v>447</v>
+        <v>464.8899888888889</v>
       </c>
       <c r="I63" s="16" t="n">
         <v>321.53</v>
@@ -9016,7 +9119,7 @@
         </is>
       </c>
       <c r="H64" s="16" t="n">
-        <v>842</v>
+        <v>937.8063888888889</v>
       </c>
       <c r="I64" s="16" t="n">
         <v>980.8700000000001</v>
@@ -9058,7 +9161,7 @@
         </is>
       </c>
       <c r="H65" s="16" t="n">
-        <v>734.9807944444444</v>
+        <v>824.4546416666666</v>
       </c>
       <c r="I65" s="16" t="n">
         <v>734.6900000000001</v>
@@ -9100,7 +9203,7 @@
         </is>
       </c>
       <c r="H66" s="16" t="n">
-        <v>369</v>
+        <v>378.6040277777778</v>
       </c>
       <c r="I66" s="16" t="n">
         <v>208.56</v>
@@ -9184,7 +9287,7 @@
         </is>
       </c>
       <c r="H68" s="16" t="n">
-        <v>325</v>
+        <v>333.0357222222222</v>
       </c>
       <c r="I68" s="16" t="n">
         <v>217.25</v>
@@ -9226,7 +9329,7 @@
         </is>
       </c>
       <c r="H69" s="16" t="n">
-        <v>333</v>
+        <v>339.0545</v>
       </c>
       <c r="I69" s="16" t="n">
         <v>156.42</v>
@@ -9268,7 +9371,7 @@
         </is>
       </c>
       <c r="H70" s="16" t="n">
-        <v>301</v>
+        <v>311.9370833333334</v>
       </c>
       <c r="I70" s="16" t="n">
         <v>165.11</v>
@@ -9310,7 +9413,7 @@
         </is>
       </c>
       <c r="H71" s="16" t="n">
-        <v>328.2696944444444</v>
+        <v>345.1742361111111</v>
       </c>
       <c r="I71" s="16" t="n">
         <v>208.955</v>
@@ -9352,7 +9455,7 @@
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>284.7370555555556</v>
+        <v>290.3426388888889</v>
       </c>
       <c r="I72" s="16" t="n">
         <v>127.19</v>
@@ -9394,7 +9497,7 @@
         </is>
       </c>
       <c r="H73" s="16" t="n">
-        <v>299.7793111111111</v>
+        <v>309.9482777777778</v>
       </c>
       <c r="I73" s="16" t="n">
         <v>154.445</v>
@@ -9436,7 +9539,7 @@
         </is>
       </c>
       <c r="H74" s="16" t="n">
-        <v>297</v>
+        <v>302.2399805555556</v>
       </c>
       <c r="I74" s="16" t="n">
         <v>156.42</v>
@@ -9478,7 +9581,7 @@
         </is>
       </c>
       <c r="H75" s="16" t="n">
-        <v>339.6612</v>
+        <v>358.653</v>
       </c>
       <c r="I75" s="16" t="n">
         <v>154.445</v>
@@ -9520,7 +9623,7 @@
         </is>
       </c>
       <c r="H76" s="16" t="n">
-        <v>289</v>
+        <v>295.6270277777778</v>
       </c>
       <c r="I76" s="16" t="n">
         <v>139.04</v>
@@ -9562,7 +9665,7 @@
         </is>
       </c>
       <c r="H77" s="16" t="n">
-        <v>341.7935555555555</v>
+        <v>363.9838888888889</v>
       </c>
       <c r="I77" s="16" t="n">
         <v>154.445</v>
@@ -9604,7 +9707,7 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>369</v>
+        <v>378.1163277777778</v>
       </c>
       <c r="I78" s="16" t="n">
         <v>208.56</v>
@@ -9688,7 +9791,7 @@
         </is>
       </c>
       <c r="H80" s="16" t="n">
-        <v>711</v>
+        <v>763.1624666666667</v>
       </c>
       <c r="I80" s="16" t="n">
         <v>657.3600000000001</v>
@@ -9730,7 +9833,7 @@
         </is>
       </c>
       <c r="H81" s="16" t="n">
-        <v>303</v>
+        <v>309.8633055555555</v>
       </c>
       <c r="I81" s="16" t="n">
         <v>112.97</v>
@@ -10846,22 +10949,22 @@
         <v>36</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>36</v>
+        <v>38.45</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>51</v>
+        <v>70.24277777777777</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>487</v>
+        <v>508.6927777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>261</v>
+        <v>263.45</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -10872,7 +10975,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-89</v>
+        <v>-86.55000000000001</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>350</v>
@@ -10897,10 +11000,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0</v>
+        <v>1.842777777777778</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>28</v>
+        <v>29.84277777777778</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>57</v>
@@ -10909,10 +11012,10 @@
         <v>225</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>440</v>
+        <v>441.8427777777778</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>253</v>
+        <v>254.8427777777778</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -10923,7 +11026,7 @@
         <v>544.3810526</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>3</v>
+        <v>4.842777777777769</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>250</v>
@@ -10948,22 +11051,22 @@
         <v>20</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1.001111111111111</v>
+        <v>2.502777777777778</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>21.00111111111111</v>
+        <v>22.50277777777778</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>51</v>
+        <v>67.69733333333333</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>507.0011111111111</v>
+        <v>525.2001111111111</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>507.0011111111111</v>
+        <v>525.2001111111111</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -10974,7 +11077,7 @@
         <v>829.8586758</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>157.0011111111111</v>
+        <v>175.2001111111111</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -10990,31 +11093,31 @@
         <v>189</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>24.02881111111111</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>189</v>
+        <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>52</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3.484433333333333</v>
+        <v>8.711083333333335</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>55.48443333333334</v>
+        <v>60.71108333333333</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>37.06883333333334</v>
+        <v>47.67208333333333</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>506.5532666666667</v>
+        <v>546.4119777777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>280.4844333333334</v>
+        <v>285.7110833333334</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -11025,7 +11128,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-69.51556666666664</v>
+        <v>-64.28891666666664</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>350</v>
@@ -11045,16 +11148,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>1940.554377777778</v>
+        <v>2022.147644444444</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1301.485544444444</v>
+        <v>1329.203972222222</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>1.485544444444486</v>
+        <v>29.20397222222232</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>1300</v>
@@ -11811,22 +11914,22 @@
         <v>44</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6.58941111111111</v>
+        <v>16.47352777777778</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>50.58941111111111</v>
+        <v>60.47352777777778</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>144</v>
+        <v>164.4863222222222</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>580.5894111111111</v>
+        <v>610.95985</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>275.5894111111111</v>
+        <v>285.4735277777778</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -11837,7 +11940,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-384.4105888888889</v>
+        <v>-374.5264722222222</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>660</v>
@@ -11853,31 +11956,31 @@
         <v>161</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>0</v>
+        <v>9.03216111111111</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>161</v>
+        <v>170.0321611111111</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>54</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0</v>
+        <v>3.460933333333334</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>54</v>
+        <v>57.46093333333334</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>168</v>
+        <v>196.8581111111111</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>608</v>
+        <v>649.3512055555556</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>279</v>
+        <v>282.4609333333333</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -11888,7 +11991,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-461</v>
+        <v>-457.5390666666667</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>740</v>
@@ -11904,31 +12007,31 @@
         <v>266</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>0</v>
+        <v>32.92766666666667</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>266</v>
+        <v>298.9276666666667</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>28</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2.9375</v>
+        <v>4.895833333333334</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>30.9375</v>
+        <v>32.89583333333334</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>207</v>
+        <v>267.9203888888889</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>728.9375</v>
+        <v>824.7438888888889</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>728.9375</v>
+        <v>824.7438888888889</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -11939,7 +12042,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>-291.0625</v>
+        <v>-195.2561111111111</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>1020</v>
@@ -11955,31 +12058,31 @@
         <v>231</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>0</v>
+        <v>16.60519444444445</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>231</v>
+        <v>247.6051944444444</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>20</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>173.9615888888889</v>
+        <v>236.9039722222222</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>649.9615888888889</v>
+        <v>731.5091666666667</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>649.9615888888889</v>
+        <v>731.5091666666667</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -11990,7 +12093,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>-70.03841111111115</v>
+        <v>11.50916666666672</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>720</v>
@@ -12010,16 +12113,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>2567.4885</v>
+        <v>2816.564111111111</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1933.4885</v>
+        <v>2124.187516666667</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>-1206.5115</v>
+        <v>-1015.812483333333</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>3140</v>
@@ -12767,10 +12870,10 @@
         <v>155</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>0</v>
+        <v>20.48777777777778</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>155</v>
+        <v>175.4877777777778</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>0</v>
@@ -12782,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>144</v>
+        <v>163.2080555555555</v>
       </c>
       <c r="I61" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>524</v>
+        <v>563.6958333333333</v>
       </c>
       <c r="K61" s="17" t="n">
         <v>225</v>
@@ -12878,22 +12981,22 @@
         <v>4</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0</v>
+        <v>0.2411111111111111</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>4</v>
+        <v>4.241111111111111</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>96</v>
+        <v>111.5892222222222</v>
       </c>
       <c r="I63" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>521</v>
+        <v>536.8303333333333</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>229</v>
+        <v>229.2411111111111</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -12904,7 +13007,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-481</v>
+        <v>-480.7588888888889</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>710</v>
@@ -12920,10 +13023,10 @@
         <v>105</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>0</v>
+        <v>11.4315</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>105</v>
+        <v>116.4315</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>0</v>
@@ -12935,13 +13038,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>74</v>
+        <v>85.77566666666667</v>
       </c>
       <c r="I64" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>404</v>
+        <v>427.2071666666667</v>
       </c>
       <c r="K64" s="17" t="n">
         <v>225</v>
@@ -12975,16 +13078,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1854</v>
+        <v>1932.733333333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>908</v>
+        <v>908.2411111111111</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-1462</v>
+        <v>-1461.758888888889</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>2370</v>
@@ -13732,31 +13835,31 @@
         <v>133</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>0</v>
+        <v>9.513916666666665</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>133</v>
+        <v>142.5139166666667</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>6</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0</v>
+        <v>0.9603888888888887</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>6</v>
+        <v>6.960388888888889</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>70</v>
+        <v>90.62005555555555</v>
       </c>
       <c r="I85" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>434</v>
+        <v>465.0943611111111</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>231</v>
+        <v>231.9603888888889</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -13767,7 +13870,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-259</v>
+        <v>-258.0396111111111</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>490</v>
@@ -13783,31 +13886,31 @@
         <v>115</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>0</v>
+        <v>4.693166666666667</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>115</v>
+        <v>119.6931666666667</v>
       </c>
       <c r="E86" s="11" t="n">
         <v>8</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>0</v>
+        <v>0.4994444444444445</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>8</v>
+        <v>8.499444444444444</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>104.5416111111111</v>
+        <v>135.3540277777778</v>
       </c>
       <c r="I86" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>452.5416111111111</v>
+        <v>488.5466388888889</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>233</v>
+        <v>233.4994444444444</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -13818,7 +13921,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-367</v>
+        <v>-366.5005555555556</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>600</v>
@@ -13834,10 +13937,10 @@
         <v>135</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>16.74333333333333</v>
+        <v>41.85833333333333</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>151.7433333333333</v>
+        <v>176.8583333333333</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>0</v>
@@ -13849,13 +13952,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="11" t="n">
-        <v>62.14077777777778</v>
+        <v>74.35194444444444</v>
       </c>
       <c r="I87" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>438.8841111111111</v>
+        <v>476.2102777777778</v>
       </c>
       <c r="K87" s="17" t="n">
         <v>225</v>
@@ -13885,31 +13988,31 @@
         <v>161</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0</v>
+        <v>17.5345</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>161</v>
+        <v>178.5345</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>4</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.7916666666666666</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>4.791666666666667</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>75.59195555555556</v>
+        <v>95.97988888888888</v>
       </c>
       <c r="I88" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>466.3836222222222</v>
+        <v>504.7810555555556</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>229.7916666666667</v>
+        <v>230.2666666666667</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -13920,7 +14023,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-260.2083333333334</v>
+        <v>-259.7333333333333</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>490</v>
@@ -13940,16 +14043,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1791.809344444444</v>
+        <v>1934.632333333333</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>918.7916666666666</v>
+        <v>920.7265</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-1151.208333333333</v>
+        <v>-1149.2735</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>2070</v>
@@ -14706,22 +14809,22 @@
         <v>16</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>16</v>
+        <v>16.71666666666667</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>56</v>
+        <v>65.04662777777777</v>
       </c>
       <c r="I109" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>367</v>
+        <v>376.7632944444445</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>241</v>
+        <v>241.7166666666667</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -14732,7 +14835,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>-109</v>
+        <v>-108.2833333333333</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>350</v>
@@ -14748,31 +14851,31 @@
         <v>98</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>0</v>
+        <v>6.119027777777778</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>98</v>
+        <v>104.1190277777778</v>
       </c>
       <c r="E110" s="11" t="n">
         <v>30</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>4.94</v>
+        <v>12.35</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>34.94</v>
+        <v>42.35</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>48</v>
+        <v>55.7212</v>
       </c>
       <c r="I110" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>405.94</v>
+        <v>427.1902277777777</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>259.94</v>
+        <v>267.35</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -14783,7 +14886,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>-90.06</v>
+        <v>-82.64999999999998</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>350</v>
@@ -14799,31 +14902,31 @@
         <v>95</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7.159655555555553</v>
+        <v>17.89913888888888</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>102.1596555555556</v>
+        <v>112.8991388888889</v>
       </c>
       <c r="E111" s="11" t="n">
         <v>24</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>2.271</v>
+        <v>5.6775</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>26.271</v>
+        <v>29.6775</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>38</v>
+        <v>47.37872222222222</v>
       </c>
       <c r="I111" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>391.4306555555556</v>
+        <v>414.9553611111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>251.271</v>
+        <v>254.6775</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -14834,7 +14937,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>-98.72899999999998</v>
+        <v>-95.32249999999999</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>350</v>
@@ -14850,31 +14953,31 @@
         <v>63</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>9.665555555555557</v>
+        <v>24.16388888888889</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>72.66555555555556</v>
+        <v>87.16388888888889</v>
       </c>
       <c r="E112" s="11" t="n">
         <v>18</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>3.028333333333334</v>
+        <v>5.047222222222222</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>21.02833333333333</v>
+        <v>23.04722222222222</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>87</v>
+        <v>99.44133333333333</v>
       </c>
       <c r="I112" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>405.6938888888889</v>
+        <v>434.6524444444444</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>246.0283333333333</v>
+        <v>248.0472222222222</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -14885,7 +14988,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>-103.9716666666667</v>
+        <v>-101.9527777777778</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>350</v>
@@ -14905,16 +15008,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1570.064544444444</v>
+        <v>1653.561327777778</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>998.2393333333333</v>
+        <v>1011.791388888889</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>-401.7606666666667</v>
+        <v>-388.2086111111111</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>1400</v>
@@ -15662,31 +15765,31 @@
         <v>161</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>0</v>
+        <v>16.45032222222222</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>161</v>
+        <v>177.4503222222222</v>
       </c>
       <c r="E133" s="11" t="n">
         <v>24</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>0</v>
+        <v>3.225455555555556</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>24</v>
+        <v>27.22545555555556</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>111</v>
+        <v>125.6738666666667</v>
       </c>
       <c r="I133" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>521</v>
+        <v>555.3496444444445</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>249</v>
+        <v>252.2254555555556</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -15697,7 +15800,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-301</v>
+        <v>-297.7745444444445</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>550</v>
@@ -15713,10 +15816,10 @@
         <v>147</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>0</v>
+        <v>21.01883333333334</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>147</v>
+        <v>168.0188333333333</v>
       </c>
       <c r="E134" s="11" t="n">
         <v>12</v>
@@ -15728,13 +15831,13 @@
         <v>12</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>87</v>
+        <v>103.5712111111111</v>
       </c>
       <c r="I134" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>471</v>
+        <v>508.5900444444445</v>
       </c>
       <c r="K134" s="17" t="n">
         <v>237</v>
@@ -15764,10 +15867,10 @@
         <v>360</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>0</v>
+        <v>52.16246666666667</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>360</v>
+        <v>412.1624666666667</v>
       </c>
       <c r="E135" s="11" t="n">
         <v>0</v>
@@ -15785,10 +15888,10 @@
         <v>225</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>669</v>
+        <v>721.1624666666667</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>669</v>
+        <v>721.1624666666667</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -15799,7 +15902,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>79</v>
+        <v>131.1624666666667</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>590</v>
@@ -15815,10 +15918,10 @@
         <v>154</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>0</v>
+        <v>18.39498888888889</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>154</v>
+        <v>172.3949888888889</v>
       </c>
       <c r="E136" s="11" t="n">
         <v>12</v>
@@ -15830,13 +15933,13 @@
         <v>12</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>66</v>
+        <v>90.53322222222222</v>
       </c>
       <c r="I136" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>457</v>
+        <v>499.9282111111111</v>
       </c>
       <c r="K136" s="17" t="n">
         <v>237</v>
@@ -15870,16 +15973,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2118</v>
+        <v>2285.030366666667</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1392</v>
+        <v>1447.387922222222</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>-548</v>
+        <v>-492.6120777777778</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1940</v>
@@ -16706,22 +16809,22 @@
         <v>102</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0</v>
+        <v>12.40472222222222</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>102</v>
+        <v>114.4047222222222</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>27</v>
+        <v>36.28805555555556</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>529</v>
+        <v>550.6927777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>327</v>
+        <v>339.4047222222222</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -16732,7 +16835,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>77</v>
+        <v>89.40472222222223</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -16757,10 +16860,10 @@
         <v>102</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0</v>
+        <v>7.02138888888889</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>102</v>
+        <v>109.0213888888889</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>27</v>
@@ -16769,10 +16872,10 @@
         <v>225</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>484</v>
+        <v>491.0213888888889</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>327</v>
+        <v>334.0213888888889</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -16783,7 +16886,7 @@
         <v>544.3810526000001</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>327</v>
+        <v>334.0213888888889</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -16808,22 +16911,22 @@
         <v>78</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9.68311111111111</v>
+        <v>24.20777777777777</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>87.68311111111112</v>
+        <v>102.2077777777778</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>27</v>
+        <v>35.01533333333333</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>549.6831111111111</v>
+        <v>572.2231111111112</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>549.6831111111111</v>
+        <v>572.2231111111112</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -16834,7 +16937,7 @@
         <v>829.8586758000001</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>199.6831111111111</v>
+        <v>222.2231111111112</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -16850,31 +16953,31 @@
         <v>189</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>24.02881111111111</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>189</v>
+        <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>84</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6.685516666666666</v>
+        <v>16.71379166666667</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>90.68551666666667</v>
+        <v>100.7137916666667</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>17.86775</v>
+        <v>23.669375</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>522.5532666666667</v>
+        <v>562.4119777777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>315.6855166666667</v>
+        <v>325.7137916666667</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -16885,7 +16988,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>65.68551666666667</v>
+        <v>75.71379166666668</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>250</v>
@@ -16905,16 +17008,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>2085.236377777778</v>
+        <v>2176.349255555556</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1519.368627777778</v>
+        <v>1571.363013888889</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>669.3686277777776</v>
+        <v>721.3630138888889</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>850</v>
@@ -17671,22 +17774,22 @@
         <v>210</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0</v>
+        <v>27.07573333333333</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>210</v>
+        <v>237.0757333333333</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>72</v>
+        <v>82.24316111111111</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>668</v>
+        <v>705.3188944444445</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>435</v>
+        <v>462.0757333333333</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -17697,7 +17800,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>85</v>
+        <v>112.0757333333333</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -17713,31 +17816,31 @@
         <v>161</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>0</v>
+        <v>9.03216111111111</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>161</v>
+        <v>170.0321611111111</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>222</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0</v>
+        <v>17.88998888888889</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>222</v>
+        <v>239.8899888888889</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>84</v>
+        <v>98.42905555555555</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>692</v>
+        <v>733.3512055555556</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>447</v>
+        <v>464.8899888888889</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -17748,7 +17851,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-13</v>
+        <v>4.889988888888865</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -17764,31 +17867,31 @@
         <v>266</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>0</v>
+        <v>32.92766666666667</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>266</v>
+        <v>298.9276666666667</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>246</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0</v>
+        <v>32.75186111111112</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>246</v>
+        <v>278.7518611111111</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>105</v>
+        <v>135.1268611111111</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>842</v>
+        <v>937.8063888888889</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>842</v>
+        <v>937.8063888888889</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -17799,7 +17902,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>162</v>
+        <v>257.8063888888889</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -17815,31 +17918,31 @@
         <v>231</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>0</v>
+        <v>16.60519444444445</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>231</v>
+        <v>247.6051944444444</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>192</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0</v>
+        <v>41.3974611111111</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>192</v>
+        <v>233.3974611111111</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>86.98079444444444</v>
+        <v>118.4519861111111</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>734.9807944444444</v>
+        <v>824.4546416666666</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>734.9807944444444</v>
+        <v>824.4546416666666</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -17850,7 +17953,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>234.9807944444444</v>
+        <v>324.4546416666666</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -17870,16 +17973,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>2936.980794444445</v>
+        <v>3200.931130555556</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>2458.980794444445</v>
+        <v>2689.226752777778</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>468.9807944444447</v>
+        <v>699.2267527777776</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>1990</v>
@@ -18627,31 +18730,31 @@
         <v>155</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>0</v>
+        <v>20.48777777777778</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>155</v>
+        <v>175.4877777777778</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>144</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0</v>
+        <v>9.604027777777777</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>144</v>
+        <v>153.6040277777778</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>72</v>
+        <v>81.60402777777777</v>
       </c>
       <c r="I61" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>596</v>
+        <v>635.6958333333333</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>369</v>
+        <v>378.6040277777778</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -18662,7 +18765,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-131</v>
+        <v>-121.3959722222222</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -18738,22 +18841,22 @@
         <v>100</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0</v>
+        <v>8.035722222222221</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>100</v>
+        <v>108.0357222222222</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>48</v>
+        <v>55.79461111111111</v>
       </c>
       <c r="I63" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>569</v>
+        <v>584.8303333333333</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>325</v>
+        <v>333.0357222222222</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -18764,7 +18867,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-145</v>
+        <v>-136.9642777777778</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -18780,31 +18883,31 @@
         <v>105</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>0</v>
+        <v>11.4315</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>105</v>
+        <v>116.4315</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>108</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>0</v>
+        <v>6.054499999999998</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>108</v>
+        <v>114.0545</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>38</v>
+        <v>43.72116666666667</v>
       </c>
       <c r="I64" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>476</v>
+        <v>499.2071666666666</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>333</v>
+        <v>339.0545</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -18815,7 +18918,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>83</v>
+        <v>89.05450000000002</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -18835,16 +18938,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>2102</v>
+        <v>2180.733333333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>1366</v>
+        <v>1389.69425</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-104</v>
+        <v>-80.30574999999999</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>1470</v>
@@ -19592,31 +19695,31 @@
         <v>133</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>0</v>
+        <v>9.513916666666665</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>133</v>
+        <v>142.5139166666667</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>76</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0</v>
+        <v>10.93708333333333</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>76</v>
+        <v>86.93708333333333</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>34</v>
+        <v>44.64336111111111</v>
       </c>
       <c r="I85" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>468</v>
+        <v>499.0943611111111</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>301</v>
+        <v>311.9370833333334</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -19627,7 +19730,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-49</v>
+        <v>-38.06291666666664</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -19643,31 +19746,31 @@
         <v>115</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>0</v>
+        <v>4.693166666666667</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>115</v>
+        <v>119.6931666666667</v>
       </c>
       <c r="E86" s="11" t="n">
         <v>92</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>11.26969444444444</v>
+        <v>28.17423611111111</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>103.2696944444444</v>
+        <v>120.1742361111111</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>52.27080555555555</v>
+        <v>67.67701388888889</v>
       </c>
       <c r="I86" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>495.5405</v>
+        <v>532.5444166666666</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>328.2696944444444</v>
+        <v>345.1742361111111</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -19678,7 +19781,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-21.73030555555556</v>
+        <v>-4.825763888888901</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -19694,31 +19797,31 @@
         <v>135</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>16.74333333333333</v>
+        <v>41.85833333333333</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>151.7433333333333</v>
+        <v>176.8583333333333</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>56</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3.737055555555556</v>
+        <v>9.34263888888889</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>59.73705555555556</v>
+        <v>65.34263888888889</v>
       </c>
       <c r="H87" s="11" t="n">
-        <v>30.40372222222222</v>
+        <v>37.00930555555556</v>
       </c>
       <c r="I87" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>466.8841111111111</v>
+        <v>504.2102777777778</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>284.7370555555556</v>
+        <v>290.3426388888889</v>
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
@@ -19729,7 +19832,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>-65.26294444444443</v>
+        <v>-59.65736111111113</v>
       </c>
       <c r="O87" s="11" t="n">
         <v>350</v>
@@ -19745,31 +19848,31 @@
         <v>161</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0</v>
+        <v>17.5345</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>161</v>
+        <v>178.5345</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>68</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>6.77931111111111</v>
+        <v>16.94827777777778</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>74.77931111111111</v>
+        <v>84.94827777777778</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>37.12931111111111</v>
+        <v>47.82327777777778</v>
       </c>
       <c r="I88" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>497.9086222222222</v>
+        <v>536.3060555555555</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>299.7793111111111</v>
+        <v>309.9482777777778</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -19780,7 +19883,7 @@
         <v>924.3805879</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-50.2206888888889</v>
+        <v>-40.05172222222222</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>350</v>
@@ -19800,16 +19903,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1928.333233333333</v>
+        <v>2072.155111111111</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>1213.786061111111</v>
+        <v>1257.402236111111</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-186.2139388888888</v>
+        <v>-142.5977638888889</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>1400</v>
@@ -20566,22 +20669,22 @@
         <v>72</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0</v>
+        <v>5.239980555555555</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>72</v>
+        <v>77.23998055555556</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>28</v>
+        <v>32.52331388888889</v>
       </c>
       <c r="I109" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>395</v>
+        <v>404.7632944444445</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>297</v>
+        <v>302.2399805555556</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -20592,7 +20695,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>297</v>
+        <v>302.2399805555556</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -20608,31 +20711,31 @@
         <v>98</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>0</v>
+        <v>6.119027777777778</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>98</v>
+        <v>104.1190277777778</v>
       </c>
       <c r="E110" s="11" t="n">
         <v>102</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>12.6612</v>
+        <v>31.65300000000001</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>114.6612</v>
+        <v>133.653</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>24</v>
+        <v>27.8606</v>
       </c>
       <c r="I110" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>461.6612</v>
+        <v>490.6326277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>339.6612</v>
+        <v>358.653</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -20643,7 +20746,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>339.6612</v>
+        <v>358.653</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -20659,31 +20762,31 @@
         <v>95</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7.159655555555553</v>
+        <v>17.89913888888888</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>102.1596555555556</v>
+        <v>112.8991388888889</v>
       </c>
       <c r="E111" s="11" t="n">
         <v>64</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0</v>
+        <v>6.627027777777776</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>64</v>
+        <v>70.62702777777778</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>18</v>
+        <v>23.02269444444444</v>
       </c>
       <c r="I111" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>409.1596555555556</v>
+        <v>431.5488611111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>289</v>
+        <v>295.6270277777778</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -20694,7 +20797,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>289</v>
+        <v>295.6270277777778</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>0</v>
@@ -20710,31 +20813,31 @@
         <v>63</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>9.665555555555557</v>
+        <v>24.16388888888889</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>72.66555555555556</v>
+        <v>87.16388888888889</v>
       </c>
       <c r="E112" s="11" t="n">
         <v>102</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>14.79355555555556</v>
+        <v>36.98388888888889</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>116.7935555555556</v>
+        <v>138.9838888888889</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>45</v>
+        <v>51.054</v>
       </c>
       <c r="I112" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>459.4591111111111</v>
+        <v>502.2017777777778</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>341.7935555555555</v>
+        <v>363.9838888888889</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -20745,7 +20848,7 @@
         <v>895.0173385999999</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>341.7935555555555</v>
+        <v>363.9838888888889</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -20765,16 +20868,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1725.279966666667</v>
+        <v>1829.146561111111</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>1267.454755555555</v>
+        <v>1320.503897222222</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>1267.454755555555</v>
+        <v>1320.503897222222</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>0</v>
@@ -21522,31 +21625,31 @@
         <v>161</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>0</v>
+        <v>16.45032222222222</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>161</v>
+        <v>177.4503222222222</v>
       </c>
       <c r="E133" s="11" t="n">
         <v>144</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>0</v>
+        <v>9.116327777777778</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>144</v>
+        <v>153.1163277777778</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>57</v>
+        <v>64.17026666666666</v>
       </c>
       <c r="I133" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>587</v>
+        <v>619.7369166666666</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>369</v>
+        <v>378.1163277777778</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -21557,7 +21660,7 @@
         <v>985.1345504</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>19</v>
+        <v>28.11632777777777</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -21573,10 +21676,10 @@
         <v>147</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>0</v>
+        <v>21.01883333333334</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>147</v>
+        <v>168.0188333333333</v>
       </c>
       <c r="E134" s="11" t="n">
         <v>96</v>
@@ -21588,13 +21691,13 @@
         <v>96</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>45</v>
+        <v>53.11893888888889</v>
       </c>
       <c r="I134" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>513</v>
+        <v>542.1377722222222</v>
       </c>
       <c r="K134" s="17" t="n">
         <v>321</v>
@@ -21624,10 +21727,10 @@
         <v>360</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>0</v>
+        <v>52.16246666666667</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>360</v>
+        <v>412.1624666666667</v>
       </c>
       <c r="E135" s="11" t="n">
         <v>84</v>
@@ -21645,10 +21748,10 @@
         <v>225</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>711</v>
+        <v>763.1624666666667</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>711</v>
+        <v>763.1624666666667</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -21659,7 +21762,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>261</v>
+        <v>313.1624666666667</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -21675,31 +21778,31 @@
         <v>154</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>0</v>
+        <v>18.39498888888889</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>154</v>
+        <v>172.3949888888889</v>
       </c>
       <c r="E136" s="11" t="n">
         <v>78</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>0</v>
+        <v>6.863305555555556</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>78</v>
+        <v>84.86330555555556</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>33</v>
+        <v>45.26661111111111</v>
       </c>
       <c r="I136" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>490</v>
+        <v>527.5249055555555</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>303</v>
+        <v>309.8633055555555</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -21710,7 +21813,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>53</v>
+        <v>59.86330555555554</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -21730,16 +21833,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2301</v>
+        <v>2452.562061111111</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1704</v>
+        <v>1772.1421</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>304</v>
+        <v>372.1421</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1400</v>
@@ -22472,22 +22575,22 @@
         <v>102</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0</v>
+        <v>19.24277777777778</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>102</v>
+        <v>121.2427777777778</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>18</v>
+        <v>20.45</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>520</v>
+        <v>541.6927777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>327</v>
+        <v>346.2427777777777</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -22495,7 +22598,7 @@
         </is>
       </c>
       <c r="M13" s="11" t="n">
-        <v>77</v>
+        <v>96.24277777777775</v>
       </c>
       <c r="N13" s="11" t="n">
         <v>250</v>
@@ -22526,13 +22629,13 @@
         <v>114</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>14</v>
+        <v>15.84277777777778</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>483</v>
+        <v>484.8427777777778</v>
       </c>
       <c r="K14" s="17" t="n">
         <v>339</v>
@@ -22568,22 +22671,22 @@
         <v>102</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0</v>
+        <v>16.69733333333333</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>102</v>
+        <v>118.6973333333333</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>11.00111111111111</v>
+        <v>12.50277777777778</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>548.0011111111112</v>
+        <v>566.2001111111111</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>548.0011111111112</v>
+        <v>566.2001111111111</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -22591,7 +22694,7 @@
         </is>
       </c>
       <c r="M15" s="11" t="n">
-        <v>198.0011111111112</v>
+        <v>216.2001111111111</v>
       </c>
       <c r="N15" s="11" t="n">
         <v>350</v>
@@ -22607,31 +22710,31 @@
         <v>189</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>24.02881111111111</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>189</v>
+        <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>60</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7.068833333333335</v>
+        <v>17.67208333333334</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>67.06883333333333</v>
+        <v>77.67208333333333</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>29.48443333333334</v>
+        <v>34.71108333333333</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>510.5532666666667</v>
+        <v>550.4119777777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>292.0688333333333</v>
+        <v>302.6720833333333</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -22639,7 +22742,7 @@
         </is>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-57.93116666666668</v>
+        <v>-47.32791666666668</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>350</v>
@@ -22661,11 +22764,11 @@
       <c r="I17" s="34" t="n"/>
       <c r="J17" s="34" t="n"/>
       <c r="K17" s="19" t="n">
-        <v>1506.069944444444</v>
+        <v>1554.114972222222</v>
       </c>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="19" t="n">
-        <v>556.0699444444444</v>
+        <v>604.1149722222221</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>950</v>
@@ -23015,22 +23118,22 @@
         <v>288</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0</v>
+        <v>20.48632222222222</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>288</v>
+        <v>308.4863222222222</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>28.58941111111111</v>
+        <v>38.47352777777778</v>
       </c>
       <c r="I28" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>702.5894111111111</v>
+        <v>732.95985</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>513</v>
+        <v>533.4863222222223</v>
       </c>
       <c r="L28" s="33" t="inlineStr">
         <is>
@@ -23038,7 +23141,7 @@
         </is>
       </c>
       <c r="M28" s="11" t="n">
-        <v>263</v>
+        <v>283.4863222222223</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>250</v>
@@ -23054,31 +23157,31 @@
         <v>161</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0</v>
+        <v>9.03216111111111</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>161</v>
+        <v>170.0321611111111</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>336</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0</v>
+        <v>28.85811111111111</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>336</v>
+        <v>364.8581111111111</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>27</v>
+        <v>30.46093333333333</v>
       </c>
       <c r="I29" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>749</v>
+        <v>790.3512055555555</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>561</v>
+        <v>589.8581111111112</v>
       </c>
       <c r="L29" s="33" t="inlineStr">
         <is>
@@ -23086,7 +23189,7 @@
         </is>
       </c>
       <c r="M29" s="11" t="n">
-        <v>311</v>
+        <v>339.8581111111112</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>250</v>
@@ -23102,31 +23205,31 @@
         <v>266</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0</v>
+        <v>32.92766666666667</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>266</v>
+        <v>298.9276666666667</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>414</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0</v>
+        <v>60.92038888888889</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>414</v>
+        <v>474.9203888888889</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>16.9375</v>
+        <v>18.89583333333334</v>
       </c>
       <c r="I30" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>921.9375</v>
+        <v>1017.743888888889</v>
       </c>
       <c r="K30" s="17" t="n">
-        <v>921.9375</v>
+        <v>1017.743888888889</v>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
@@ -23134,7 +23237,7 @@
         </is>
       </c>
       <c r="M30" s="11" t="n">
-        <v>571.9375</v>
+        <v>667.7438888888889</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>350</v>
@@ -23150,31 +23253,31 @@
         <v>231</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>0</v>
+        <v>16.60519444444445</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>231</v>
+        <v>247.6051944444444</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>264</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>41.96158888888889</v>
+        <v>104.9039722222222</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>305.9615888888889</v>
+        <v>368.9039722222223</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I31" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>769.9615888888889</v>
+        <v>851.5091666666667</v>
       </c>
       <c r="K31" s="17" t="n">
-        <v>769.9615888888889</v>
+        <v>851.5091666666667</v>
       </c>
       <c r="L31" s="23" t="inlineStr">
         <is>
@@ -23182,7 +23285,7 @@
         </is>
       </c>
       <c r="M31" s="11" t="n">
-        <v>419.9615888888889</v>
+        <v>501.5091666666667</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>350</v>
@@ -23204,11 +23307,11 @@
       <c r="I32" s="34" t="n"/>
       <c r="J32" s="34" t="n"/>
       <c r="K32" s="19" t="n">
-        <v>2765.899088888889</v>
+        <v>2992.597488888889</v>
       </c>
       <c r="L32" s="34" t="n"/>
       <c r="M32" s="19" t="n">
-        <v>1565.899088888889</v>
+        <v>1792.597488888889</v>
       </c>
       <c r="N32" s="19" t="n">
         <v>1200</v>
@@ -23549,19 +23652,19 @@
         <v>155</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>0</v>
+        <v>20.48777777777778</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>155</v>
+        <v>175.4877777777778</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>288</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0</v>
+        <v>19.20805555555555</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>288</v>
+        <v>307.2080555555556</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
@@ -23570,10 +23673,10 @@
         <v>225</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>668</v>
+        <v>707.6958333333333</v>
       </c>
       <c r="K43" s="17" t="n">
-        <v>513</v>
+        <v>532.2080555555556</v>
       </c>
       <c r="L43" s="33" t="inlineStr">
         <is>
@@ -23581,7 +23684,7 @@
         </is>
       </c>
       <c r="M43" s="11" t="n">
-        <v>263</v>
+        <v>282.2080555555556</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>250</v>
@@ -23654,22 +23757,22 @@
         <v>192</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0</v>
+        <v>15.58922222222222</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>192</v>
+        <v>207.5892222222222</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>2</v>
+        <v>2.241111111111111</v>
       </c>
       <c r="I45" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>615</v>
+        <v>630.8303333333333</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>417</v>
+        <v>432.5892222222222</v>
       </c>
       <c r="L45" s="33" t="inlineStr">
         <is>
@@ -23677,7 +23780,7 @@
         </is>
       </c>
       <c r="M45" s="11" t="n">
-        <v>417</v>
+        <v>432.5892222222222</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>0</v>
@@ -23693,19 +23796,19 @@
         <v>105</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>0</v>
+        <v>11.4315</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>105</v>
+        <v>116.4315</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>148</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0</v>
+        <v>11.77566666666666</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>148</v>
+        <v>159.7756666666667</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>0</v>
@@ -23714,10 +23817,10 @@
         <v>225</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>478</v>
+        <v>501.2071666666667</v>
       </c>
       <c r="K46" s="17" t="n">
-        <v>373</v>
+        <v>384.7756666666667</v>
       </c>
       <c r="L46" s="33" t="inlineStr">
         <is>
@@ -23725,7 +23828,7 @@
         </is>
       </c>
       <c r="M46" s="11" t="n">
-        <v>373</v>
+        <v>384.7756666666667</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>0</v>
@@ -23747,11 +23850,11 @@
       <c r="I47" s="34" t="n"/>
       <c r="J47" s="34" t="n"/>
       <c r="K47" s="19" t="n">
-        <v>1750</v>
+        <v>1796.572944444444</v>
       </c>
       <c r="L47" s="34" t="n"/>
       <c r="M47" s="19" t="n">
-        <v>1500</v>
+        <v>1546.572944444444</v>
       </c>
       <c r="N47" s="19" t="n">
         <v>250</v>
@@ -24092,31 +24195,31 @@
         <v>133</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>0</v>
+        <v>9.513916666666665</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>133</v>
+        <v>142.5139166666667</v>
       </c>
       <c r="E58" s="11" t="n">
         <v>140</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>0</v>
+        <v>20.62005555555556</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>140</v>
+        <v>160.6200555555556</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>3</v>
+        <v>3.960388888888889</v>
       </c>
       <c r="I58" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>501</v>
+        <v>532.0943611111111</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>365</v>
+        <v>385.6200555555556</v>
       </c>
       <c r="L58" s="33" t="inlineStr">
         <is>
@@ -24124,7 +24227,7 @@
         </is>
       </c>
       <c r="M58" s="11" t="n">
-        <v>365</v>
+        <v>385.6200555555556</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>0</v>
@@ -24140,31 +24243,31 @@
         <v>115</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>0</v>
+        <v>4.693166666666667</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>115</v>
+        <v>119.6931666666667</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>168</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>20.54161111111111</v>
+        <v>51.35402777777777</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>188.5416111111111</v>
+        <v>219.3540277777778</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>4</v>
+        <v>4.499444444444444</v>
       </c>
       <c r="I59" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>532.5416111111111</v>
+        <v>568.546638888889</v>
       </c>
       <c r="K59" s="17" t="n">
-        <v>413.5416111111111</v>
+        <v>444.3540277777778</v>
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
@@ -24172,7 +24275,7 @@
         </is>
       </c>
       <c r="M59" s="11" t="n">
-        <v>413.5416111111111</v>
+        <v>444.3540277777778</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>0</v>
@@ -24188,19 +24291,19 @@
         <v>135</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>16.74333333333333</v>
+        <v>41.85833333333333</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>151.7433333333333</v>
+        <v>176.8583333333333</v>
       </c>
       <c r="E60" s="11" t="n">
         <v>108</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>8.140777777777778</v>
+        <v>20.35194444444445</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>116.1407777777778</v>
+        <v>128.3519444444445</v>
       </c>
       <c r="H60" s="11" t="n">
         <v>0</v>
@@ -24209,10 +24312,10 @@
         <v>225</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>492.8841111111111</v>
+        <v>530.2102777777778</v>
       </c>
       <c r="K60" s="17" t="n">
-        <v>341.1407777777778</v>
+        <v>353.3519444444445</v>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
@@ -24220,7 +24323,7 @@
         </is>
       </c>
       <c r="M60" s="11" t="n">
-        <v>341.1407777777778</v>
+        <v>353.3519444444445</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>0</v>
@@ -24236,31 +24339,31 @@
         <v>161</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>0</v>
+        <v>17.5345</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>161</v>
+        <v>178.5345</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>124</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>13.59195555555555</v>
+        <v>33.97988888888888</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>137.5919555555556</v>
+        <v>157.9798888888889</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>2.791666666666667</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>526.3836222222222</v>
+        <v>564.7810555555556</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>362.5919555555556</v>
+        <v>382.9798888888889</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -24268,7 +24371,7 @@
         </is>
       </c>
       <c r="M61" s="11" t="n">
-        <v>362.5919555555556</v>
+        <v>382.9798888888889</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>0</v>
@@ -24290,11 +24393,11 @@
       <c r="I62" s="34" t="n"/>
       <c r="J62" s="34" t="n"/>
       <c r="K62" s="19" t="n">
-        <v>1482.274344444445</v>
+        <v>1566.305916666666</v>
       </c>
       <c r="L62" s="34" t="n"/>
       <c r="M62" s="19" t="n">
-        <v>1482.274344444445</v>
+        <v>1566.305916666666</v>
       </c>
       <c r="N62" s="19" t="n">
         <v>0</v>
@@ -24644,22 +24747,22 @@
         <v>112</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0</v>
+        <v>9.046627777777777</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>112</v>
+        <v>121.0466277777778</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>8</v>
+        <v>8.716666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>415</v>
+        <v>424.7632944444445</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>337</v>
+        <v>346.0466277777778</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -24667,7 +24770,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="n">
-        <v>337</v>
+        <v>346.0466277777778</v>
       </c>
       <c r="N73" s="11" t="n">
         <v>0</v>
@@ -24683,31 +24786,31 @@
         <v>98</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0</v>
+        <v>6.119027777777778</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>98</v>
+        <v>104.1190277777778</v>
       </c>
       <c r="E74" s="11" t="n">
         <v>96</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>0</v>
+        <v>7.721199999999998</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>96</v>
+        <v>103.7212</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>19.94</v>
+        <v>27.35</v>
       </c>
       <c r="I74" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>438.94</v>
+        <v>460.1902277777777</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>321</v>
+        <v>328.7212</v>
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
@@ -24715,7 +24818,7 @@
         </is>
       </c>
       <c r="M74" s="11" t="n">
-        <v>321</v>
+        <v>328.7212</v>
       </c>
       <c r="N74" s="11" t="n">
         <v>0</v>
@@ -24731,31 +24834,31 @@
         <v>95</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>7.159655555555553</v>
+        <v>17.89913888888888</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>102.1596555555556</v>
+        <v>112.8991388888889</v>
       </c>
       <c r="E75" s="11" t="n">
         <v>76</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>0</v>
+        <v>9.378722222222221</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>76</v>
+        <v>85.37872222222222</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>14.271</v>
+        <v>17.6775</v>
       </c>
       <c r="I75" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>417.4306555555556</v>
+        <v>440.9553611111111</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>301</v>
+        <v>310.3787222222222</v>
       </c>
       <c r="L75" s="33" t="inlineStr">
         <is>
@@ -24763,7 +24866,7 @@
         </is>
       </c>
       <c r="M75" s="11" t="n">
-        <v>301</v>
+        <v>310.3787222222222</v>
       </c>
       <c r="N75" s="11" t="n">
         <v>0</v>
@@ -24779,31 +24882,31 @@
         <v>63</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>9.665555555555557</v>
+        <v>24.16388888888889</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>72.66555555555556</v>
+        <v>87.16388888888889</v>
       </c>
       <c r="E76" s="11" t="n">
         <v>174</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>0</v>
+        <v>12.44133333333333</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>174</v>
+        <v>186.4413333333333</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>12.02833333333333</v>
+        <v>14.04722222222222</v>
       </c>
       <c r="I76" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>483.6938888888889</v>
+        <v>512.6524444444444</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>399</v>
+        <v>411.4413333333333</v>
       </c>
       <c r="L76" s="33" t="inlineStr">
         <is>
@@ -24811,7 +24914,7 @@
         </is>
       </c>
       <c r="M76" s="11" t="n">
-        <v>399</v>
+        <v>411.4413333333333</v>
       </c>
       <c r="N76" s="11" t="n">
         <v>0</v>
@@ -24833,11 +24936,11 @@
       <c r="I77" s="34" t="n"/>
       <c r="J77" s="34" t="n"/>
       <c r="K77" s="19" t="n">
-        <v>1358</v>
+        <v>1396.587883333333</v>
       </c>
       <c r="L77" s="34" t="n"/>
       <c r="M77" s="19" t="n">
-        <v>1358</v>
+        <v>1396.587883333333</v>
       </c>
       <c r="N77" s="19" t="n">
         <v>0</v>
@@ -25178,31 +25281,31 @@
         <v>161</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0</v>
+        <v>16.45032222222222</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>161</v>
+        <v>177.4503222222222</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>222</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0</v>
+        <v>14.67386666666667</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>222</v>
+        <v>236.6738666666667</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>12</v>
+        <v>15.22545555555556</v>
       </c>
       <c r="I88" s="11" t="n">
         <v>225</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>620</v>
+        <v>654.3496444444444</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>447</v>
+        <v>461.6738666666666</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -25210,7 +25313,7 @@
         </is>
       </c>
       <c r="M88" s="11" t="n">
-        <v>447</v>
+        <v>461.6738666666666</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>0</v>
@@ -25226,19 +25329,19 @@
         <v>147</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0</v>
+        <v>21.01883333333334</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>147</v>
+        <v>168.0188333333333</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>174</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0</v>
+        <v>16.57121111111111</v>
       </c>
       <c r="G89" s="11" t="n">
-        <v>174</v>
+        <v>190.5712111111111</v>
       </c>
       <c r="H89" s="11" t="n">
         <v>6</v>
@@ -25247,10 +25350,10 @@
         <v>225</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>552</v>
+        <v>589.5900444444444</v>
       </c>
       <c r="K89" s="17" t="n">
-        <v>399</v>
+        <v>415.5712111111111</v>
       </c>
       <c r="L89" s="33" t="inlineStr">
         <is>
@@ -25258,7 +25361,7 @@
         </is>
       </c>
       <c r="M89" s="11" t="n">
-        <v>399</v>
+        <v>415.5712111111111</v>
       </c>
       <c r="N89" s="11" t="n">
         <v>0</v>
@@ -25274,10 +25377,10 @@
         <v>360</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0</v>
+        <v>52.16246666666667</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>360</v>
+        <v>412.1624666666667</v>
       </c>
       <c r="E90" s="11" t="n">
         <v>168</v>
@@ -25295,10 +25398,10 @@
         <v>225</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>753</v>
+        <v>805.1624666666667</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>753</v>
+        <v>805.1624666666667</v>
       </c>
       <c r="L90" s="23" t="inlineStr">
         <is>
@@ -25306,7 +25409,7 @@
         </is>
       </c>
       <c r="M90" s="11" t="n">
-        <v>403</v>
+        <v>455.1624666666667</v>
       </c>
       <c r="N90" s="11" t="n">
         <v>350</v>
@@ -25322,19 +25425,19 @@
         <v>154</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0</v>
+        <v>18.39498888888889</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>154</v>
+        <v>172.3949888888889</v>
       </c>
       <c r="E91" s="11" t="n">
         <v>132</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0</v>
+        <v>24.53322222222222</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>132</v>
+        <v>156.5332222222222</v>
       </c>
       <c r="H91" s="11" t="n">
         <v>6</v>
@@ -25343,10 +25446,10 @@
         <v>225</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>517</v>
+        <v>559.9282111111111</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>357</v>
+        <v>381.5332222222222</v>
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
@@ -25354,7 +25457,7 @@
         </is>
       </c>
       <c r="M91" s="11" t="n">
-        <v>357</v>
+        <v>381.5332222222222</v>
       </c>
       <c r="N91" s="11" t="n">
         <v>0</v>
@@ -25376,11 +25479,11 @@
       <c r="I92" s="34" t="n"/>
       <c r="J92" s="34" t="n"/>
       <c r="K92" s="19" t="n">
-        <v>1956</v>
+        <v>2063.940766666667</v>
       </c>
       <c r="L92" s="34" t="n"/>
       <c r="M92" s="19" t="n">
-        <v>1606</v>
+        <v>1713.940766666667</v>
       </c>
       <c r="N92" s="19" t="n">
         <v>350</v>

--- a/output/Bonus_Plan_FINAL.xlsx
+++ b/output/Bonus_Plan_FINAL.xlsx
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>12644.66911666667</v>
+        <v>7838.208116666666</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13911.87745277778</v>
+        <v>11737.87845277778</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14532.66911666667</v>
+        <v>14397.59311666666</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>7741.538411111112</v>
+        <v>2935.077411111111</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>10000.33225</v>
+        <v>7826.333250000001</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>11370.11997222222</v>
+        <v>11235.04397222222</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4702,13 +4702,13 @@
         <v>350</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>508.6927777777778</v>
+        <v>321.7177777777778</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>263.45</v>
+        <v>76.47499999999999</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>-86.55000000000001</v>
+        <v>-273.525</v>
       </c>
     </row>
     <row r="15">
@@ -4735,13 +4735,13 @@
         <v>660</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>610.95985</v>
+        <v>448.6122</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>285.4735277777778</v>
+        <v>123.1258777777778</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>-374.5264722222222</v>
+        <v>-536.8741222222222</v>
       </c>
     </row>
     <row r="16">
@@ -4768,13 +4768,13 @@
         <v>740</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>563.6958333333333</v>
+        <v>338.6958333333333</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>-515</v>
+        <v>-740</v>
       </c>
     </row>
     <row r="17">
@@ -4801,13 +4801,13 @@
         <v>490</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>465.0943611111111</v>
+        <v>247.4161111111111</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>231.9603888888889</v>
+        <v>14.28213888888889</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>-258.0396111111111</v>
+        <v>-475.7178611111111</v>
       </c>
     </row>
     <row r="18">
@@ -4834,13 +4834,13 @@
         <v>350</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>376.7632944444445</v>
+        <v>170.2132944444444</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>241.7166666666667</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-108.2833333333333</v>
+        <v>-314.8333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -4867,13 +4867,13 @@
         <v>550</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>555.3496444444445</v>
+        <v>362.8641944444444</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>252.2254555555556</v>
+        <v>59.74000555555556</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-297.7745444444445</v>
+        <v>-490.2599944444444</v>
       </c>
     </row>
     <row r="20">
@@ -4900,13 +4900,13 @@
         <v>250</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>441.8427777777778</v>
+        <v>254.4277777777778</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>254.8427777777778</v>
+        <v>67.42777777777778</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>4.842777777777769</v>
+        <v>-182.5722222222222</v>
       </c>
     </row>
     <row r="21">
@@ -4933,13 +4933,13 @@
         <v>740</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>649.3512055555556</v>
+        <v>482.4996055555555</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>282.4609333333333</v>
+        <v>115.6093333333333</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-457.5390666666667</v>
+        <v>-624.3906666666667</v>
       </c>
     </row>
     <row r="22">
@@ -4966,13 +4966,13 @@
         <v>450</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>405</v>
+        <v>185.315</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>229</v>
+        <v>9.315000000000001</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>-221</v>
+        <v>-440.685</v>
       </c>
     </row>
     <row r="23">
@@ -4999,13 +4999,13 @@
         <v>600</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>488.5466388888889</v>
+        <v>274.0416388888889</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>233.4994444444444</v>
+        <v>18.99444444444445</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>-366.5005555555556</v>
+        <v>-581.0055555555556</v>
       </c>
     </row>
     <row r="24">
@@ -5032,13 +5032,13 @@
         <v>350</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>427.1902277777777</v>
+        <v>239.4202277777778</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>267.35</v>
+        <v>79.58000000000001</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>-82.64999999999998</v>
+        <v>-270.42</v>
       </c>
     </row>
     <row r="25">
@@ -5065,13 +5065,13 @@
         <v>450</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>508.5900444444445</v>
+        <v>299.0500444444444</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>237</v>
+        <v>27.46</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>-213</v>
+        <v>-422.54</v>
       </c>
     </row>
     <row r="26">
@@ -5098,13 +5098,13 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>525.2001111111111</v>
+        <v>319.7051111111111</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>525.2001111111111</v>
+        <v>319.7051111111111</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>175.2001111111111</v>
+        <v>-30.29488888888886</v>
       </c>
     </row>
     <row r="27">
@@ -5131,13 +5131,13 @@
         <v>1020</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>824.7438888888889</v>
+        <v>629.5563888888889</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>824.7438888888889</v>
+        <v>629.5563888888889</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>-195.2561111111111</v>
+        <v>-390.4436111111111</v>
       </c>
     </row>
     <row r="28">
@@ -5164,13 +5164,13 @@
         <v>710</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>536.8303333333333</v>
+        <v>317.0003333333333</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>229.2411111111111</v>
+        <v>9.411111111111111</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>-480.7588888888889</v>
+        <v>-700.5888888888888</v>
       </c>
     </row>
     <row r="29">
@@ -5197,13 +5197,13 @@
         <v>490</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>476.2102777777778</v>
+        <v>251.2102777777778</v>
       </c>
       <c r="H29" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I29" s="16" t="n">
-        <v>-265</v>
+        <v>-490</v>
       </c>
     </row>
     <row r="30">
@@ -5230,13 +5230,13 @@
         <v>350</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>414.9553611111111</v>
+        <v>218.1748611111111</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>254.6775</v>
+        <v>57.89700000000001</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>-95.32249999999999</v>
+        <v>-292.103</v>
       </c>
     </row>
     <row r="31">
@@ -5263,13 +5263,13 @@
         <v>590</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>721.1624666666667</v>
+        <v>496.1624666666667</v>
       </c>
       <c r="H31" s="17" t="n">
-        <v>721.1624666666667</v>
+        <v>496.1624666666667</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>131.1624666666667</v>
+        <v>-93.83753333333334</v>
       </c>
     </row>
     <row r="32">
@@ -5296,13 +5296,13 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>546.4119777777778</v>
+        <v>376.0919277777778</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>285.7110833333334</v>
+        <v>115.3910333333333</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>-64.28891666666664</v>
+        <v>-234.6089666666667</v>
       </c>
     </row>
     <row r="33">
@@ -5329,13 +5329,13 @@
         <v>720</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>731.5091666666667</v>
+        <v>604.3841666666667</v>
       </c>
       <c r="H33" s="17" t="n">
-        <v>731.5091666666667</v>
+        <v>604.3841666666667</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>11.50916666666672</v>
+        <v>-115.6158333333333</v>
       </c>
     </row>
     <row r="34">
@@ -5362,13 +5362,13 @@
         <v>470</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>427.2071666666667</v>
+        <v>202.2071666666667</v>
       </c>
       <c r="H34" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>-245</v>
+        <v>-470</v>
       </c>
     </row>
     <row r="35">
@@ -5395,13 +5395,13 @@
         <v>490</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>504.7810555555556</v>
+        <v>284.2060555555556</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>230.2666666666667</v>
+        <v>9.691666666666666</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>-259.7333333333333</v>
+        <v>-480.3083333333333</v>
       </c>
     </row>
     <row r="36">
@@ -5428,13 +5428,13 @@
         <v>350</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>434.6524444444444</v>
+        <v>227.7374444444444</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>248.0472222222222</v>
+        <v>41.13222222222223</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>-101.9527777777778</v>
+        <v>-308.8677777777777</v>
       </c>
     </row>
     <row r="37">
@@ -5461,13 +5461,13 @@
         <v>350</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>499.9282111111111</v>
+        <v>287.4982111111111</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>237</v>
+        <v>24.57</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>-113</v>
+        <v>-325.43</v>
       </c>
     </row>
     <row r="38">
@@ -5480,13 +5480,13 @@
         <v>12220</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>12644.66911666667</v>
+        <v>7838.208116666667</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>7741.538411111112</v>
+        <v>2935.077411111111</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-4478.461588888888</v>
+        <v>-9284.922588888889</v>
       </c>
     </row>
     <row r="40">
@@ -5567,13 +5567,13 @@
         <v>250</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>550.6927777777778</v>
+        <v>432.5140277777778</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>339.4047222222222</v>
+        <v>221.2259722222222</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>89.40472222222223</v>
+        <v>-28.77402777777777</v>
       </c>
     </row>
     <row r="43">
@@ -5600,13 +5600,13 @@
         <v>350</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>705.3188944444445</v>
+        <v>707.1596944444445</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>462.0757333333333</v>
+        <v>463.9165333333334</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>112.0757333333333</v>
+        <v>113.9165333333334</v>
       </c>
     </row>
     <row r="44">
@@ -5633,13 +5633,13 @@
         <v>500</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>635.6958333333333</v>
+        <v>569.1320833333333</v>
       </c>
       <c r="H44" s="17" t="n">
-        <v>378.6040277777778</v>
+        <v>312.0402777777778</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>-121.3959722222222</v>
+        <v>-187.9597222222222</v>
       </c>
     </row>
     <row r="45">
@@ -5666,13 +5666,13 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>499.0943611111111</v>
+        <v>380.3112361111111</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>311.9370833333334</v>
+        <v>193.1539583333333</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>-38.06291666666664</v>
+        <v>-156.8460416666667</v>
       </c>
     </row>
     <row r="46">
@@ -5699,13 +5699,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>404.7632944444445</v>
+        <v>280.9231194444445</v>
       </c>
       <c r="H46" s="17" t="n">
-        <v>302.2399805555556</v>
+        <v>178.3998055555556</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>302.2399805555556</v>
+        <v>178.3998055555556</v>
       </c>
     </row>
     <row r="47">
@@ -5732,13 +5732,13 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>619.7369166666666</v>
+        <v>548.7838666666667</v>
       </c>
       <c r="H47" s="17" t="n">
-        <v>378.1163277777778</v>
+        <v>307.1632777777778</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>28.11632777777777</v>
+        <v>-42.83672222222219</v>
       </c>
     </row>
     <row r="48">
@@ -5765,13 +5765,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>491.0213888888889</v>
+        <v>380.2138888888889</v>
       </c>
       <c r="H48" s="17" t="n">
-        <v>334.0213888888889</v>
+        <v>223.2138888888889</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>334.0213888888889</v>
+        <v>223.2138888888889</v>
       </c>
     </row>
     <row r="49">
@@ -5798,13 +5798,13 @@
         <v>460</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>733.3512055555556</v>
+        <v>780.3611055555556</v>
       </c>
       <c r="H49" s="17" t="n">
-        <v>464.8899888888889</v>
+        <v>511.8998888888889</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>4.889988888888865</v>
+        <v>51.89988888888888</v>
       </c>
     </row>
     <row r="50">
@@ -5831,13 +5831,13 @@
         <v>250</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>461</v>
+        <v>366.29175</v>
       </c>
       <c r="H50" s="17" t="n">
-        <v>339</v>
+        <v>244.29175</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>89</v>
+        <v>-5.708249999999992</v>
       </c>
     </row>
     <row r="51">
@@ -5864,13 +5864,13 @@
         <v>350</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>532.5444166666666</v>
+        <v>427.2580416666667</v>
       </c>
       <c r="H51" s="17" t="n">
-        <v>345.1742361111111</v>
+        <v>239.8878611111111</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-4.825763888888901</v>
+        <v>-110.1121388888889</v>
       </c>
     </row>
     <row r="52">
@@ -5897,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>490.6326277777778</v>
+        <v>373.6080277777778</v>
       </c>
       <c r="H52" s="17" t="n">
-        <v>358.653</v>
+        <v>241.6284</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>358.653</v>
+        <v>241.6284</v>
       </c>
     </row>
     <row r="53">
@@ -5930,13 +5930,13 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>542.1377722222222</v>
+        <v>450.6682222222222</v>
       </c>
       <c r="H53" s="17" t="n">
-        <v>321</v>
+        <v>229.53045</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-29</v>
+        <v>-120.46955</v>
       </c>
     </row>
     <row r="54">
@@ -5963,13 +5963,13 @@
         <v>350</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>572.2231111111112</v>
+        <v>429.7971111111111</v>
       </c>
       <c r="H54" s="17" t="n">
-        <v>572.2231111111112</v>
+        <v>429.7971111111111</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>222.2231111111112</v>
+        <v>79.79711111111112</v>
       </c>
     </row>
     <row r="55">
@@ -5996,13 +5996,13 @@
         <v>680</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>937.8063888888889</v>
+        <v>983.1897638888889</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>937.8063888888889</v>
+        <v>983.1897638888889</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>257.8063888888889</v>
+        <v>303.1897638888889</v>
       </c>
     </row>
     <row r="56">
@@ -6029,13 +6029,13 @@
         <v>470</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>584.8303333333333</v>
+        <v>507.1518333333333</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>333.0357222222222</v>
+        <v>255.3572222222222</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>-136.9642777777778</v>
+        <v>-214.6427777777778</v>
       </c>
     </row>
     <row r="57">
@@ -6062,13 +6062,13 @@
         <v>350</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>504.2102777777778</v>
+        <v>338.0270277777778</v>
       </c>
       <c r="H57" s="17" t="n">
-        <v>290.3426388888889</v>
+        <v>124.1593888888889</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>-59.65736111111113</v>
+        <v>-225.8406111111111</v>
       </c>
     </row>
     <row r="58">
@@ -6095,13 +6095,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>431.5488611111111</v>
+        <v>284.3704861111111</v>
       </c>
       <c r="H58" s="17" t="n">
-        <v>295.6270277777778</v>
+        <v>148.4486527777778</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>295.6270277777778</v>
+        <v>148.4486527777778</v>
       </c>
     </row>
     <row r="59">
@@ -6128,13 +6128,13 @@
         <v>450</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>763.1624666666667</v>
+        <v>636.2990916666666</v>
       </c>
       <c r="H59" s="17" t="n">
-        <v>763.1624666666667</v>
+        <v>636.2990916666666</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>313.1624666666667</v>
+        <v>186.2990916666666</v>
       </c>
     </row>
     <row r="60">
@@ -6161,13 +6161,13 @@
         <v>250</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>562.4119777777778</v>
+        <v>430.4968027777778</v>
       </c>
       <c r="H60" s="17" t="n">
-        <v>325.7137916666667</v>
+        <v>193.7986166666667</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>75.71379166666668</v>
+        <v>-56.20138333333333</v>
       </c>
     </row>
     <row r="61">
@@ -6194,13 +6194,13 @@
         <v>500</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>824.4546416666666</v>
+        <v>857.7432166666665</v>
       </c>
       <c r="H61" s="17" t="n">
-        <v>824.4546416666666</v>
+        <v>857.7432166666665</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>324.4546416666666</v>
+        <v>357.7432166666665</v>
       </c>
     </row>
     <row r="62">
@@ -6227,13 +6227,13 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>499.2071666666666</v>
+        <v>382.6976666666666</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>339.0545</v>
+        <v>222.545</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>89.05450000000002</v>
+        <v>-27.45499999999998</v>
       </c>
     </row>
     <row r="63">
@@ -6260,13 +6260,13 @@
         <v>350</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>536.3060555555555</v>
+        <v>392.8129555555555</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>309.9482777777778</v>
+        <v>166.4551777777778</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v>-40.05172222222222</v>
+        <v>-183.5448222222222</v>
       </c>
     </row>
     <row r="64">
@@ -6293,13 +6293,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>502.2017777777778</v>
+        <v>394.7727777777778</v>
       </c>
       <c r="H64" s="17" t="n">
-        <v>363.9838888888889</v>
+        <v>256.5548888888889</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>363.9838888888889</v>
+        <v>256.5548888888889</v>
       </c>
     </row>
     <row r="65">
@@ -6326,13 +6326,13 @@
         <v>250</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>527.5249055555555</v>
+        <v>403.2946555555556</v>
       </c>
       <c r="H65" s="17" t="n">
-        <v>309.8633055555555</v>
+        <v>185.6330555555556</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v>59.86330555555554</v>
+        <v>-64.36694444444444</v>
       </c>
     </row>
     <row r="66">
@@ -6345,13 +6345,13 @@
         <v>7110</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>13911.87745277778</v>
+        <v>11737.87845277778</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>10000.33225</v>
+        <v>7826.333250000001</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>2890.332249999999</v>
+        <v>716.3332500000015</v>
       </c>
     </row>
     <row r="69">
@@ -6364,14 +6364,14 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $7,742 (less, because few agents clear the $45k NB gate today).</t>
+          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $2,935 (less, because few agents clear the $45k NB gate today).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,370 (93% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,235 (92% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6804,250 +6804,254 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Retention Rate</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>% retained</t>
+          <t>REN written premium x 0.5%</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>(NB premium written 6 months ago that is STILL ACTIVE today) / (NB premium written 6 months ago)</t>
+          <t>Bonus = $5 per $1,000 of REN premium the agent retained this month.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Monthly Pool</t>
+          <t>Scales with book size</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>A $50k REN month -&gt; $250 bonus. A $25k REN month -&gt; $125 bonus.</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Pool of bonus dollars at stake for retention.</t>
+          <t>Bigger book = bigger bonus. Agent with 40 renewals at $50k earns more than agent with 20 renewals at $25k, even at the same retention rate.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Retention Bonus</t>
+          <t>Why per-dollar</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Rate x Pool</t>
+          <t>Rewards both the renewal RATE and the BOOK SIZE</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>e.g., 75% x $300 = $225/mo. 90% x $300 = $270/mo. 100% x $300 = $300/mo.</t>
+          <t>Agent who retains $50k of book contributes more commission to the agency. Bonus reflects that.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Modeling assumption</t>
+          <t>Retention Rate threshold</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>75% retention rate</t>
+          <t>&gt;= 30% to qualify</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>For modeling in this workbook we use 75% (industry typical) = $225/mo. Actual is computed monthly from the agency's history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+          <t>Agent must retain at least 30% of their book to earn the retention bonus AND the per-policy REN bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Minimum gate</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>NOT gated by NB minimum</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Retention bonus pays regardless of monthly NB volume - it rewards keeping the book intact over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>4. RULES THAT APPLY ON TOP</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>How it works</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - NB</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>$45,000 written premium</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Monthly Minimum - REN</t>
+          <t>Monthly Minimum - NB</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Retain &gt;= 30% of agent's book</t>
+          <t>$45,000 written premium</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>REN base + REN collected paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
+          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Monthly Minimum - RWR</t>
+          <t>Monthly Minimum - REN</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>NB gate met (or both)</t>
+          <t>Retain &gt;= 30% of agent's book</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
+          <t>REN base + REN collected paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Retention Bonus exception</t>
+          <t>Monthly Minimum - RWR</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Always paid</t>
+          <t>NB gate met (or both)</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
+          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Retention Bonus exception</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>3 months (90 days)</t>
+          <t>Always paid</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Excel Tracker</t>
+          <t>Chargeback</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Required for every policy</t>
+          <t>3 months (90 days)</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
+          <t>Excel Tracker</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Required for every policy</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
           <t>Renewal Book of Business</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>Assigned per agent</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>Each agent has an assigned renewal book. Newer agents who do not have their own renewals get a book reassigned from former employees. The agent is responsible for renewing that book.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
@@ -7057,7 +7061,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
+          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr"/>
@@ -7070,7 +7074,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr"/>
@@ -7078,165 +7082,161 @@
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>NB base (tier)</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38 policies in tier "$1,200-$1,799" x $7</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>$266</t>
-        </is>
-      </c>
+          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>NB collected incentive</t>
+          <t>NB base (tier)</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$2/policy</t>
+          <t>38 policies in tier "$1,200-$1,799" x $7</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>$33</t>
+          <t>$266</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>REN base (tier)</t>
+          <t>NB collected incentive</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>7 policies in tier "Under $1,200" x $4</t>
+          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>$28</t>
+          <t>$33</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>REN collected incentive</t>
+          <t>REN base (tier)</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>~14% &gt;$1,200, collected 52% -&gt; +$5/policy</t>
+          <t>7 policies in tier "Under $1,200" x $4</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>$5</t>
+          <t>$28</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>RWR base (tier)</t>
+          <t>REN collected incentive</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>69 policies in tier "$1,200-$1,799" x $3</t>
+          <t>~14% &gt;$1,200, collected 52% -&gt; +$5/policy</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>$207</t>
+          <t>$5</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>RWR collected incentive</t>
+          <t>RWR base (tier)</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>~44% &gt;$1,200, collected 20% -&gt; +$2/policy</t>
+          <t>69 policies in tier "$1,200-$1,799" x $3</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>$61</t>
+          <t>$207</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Retention bonus</t>
+          <t>RWR collected incentive</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>75% retention x $300 pool</t>
+          <t>~44% &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>$225</t>
+          <t>$61</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Subtotal target</t>
+          <t>Retention bonus</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>(everything before gates)</t>
+          <t>REN $5,962 x 0.5% = $29.81</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>$825</t>
+          <t>$30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>NB gate ($45,000)</t>
+          <t>Subtotal target</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>NB written $52,435 vs $45,000</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>(everything before gates)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>$630</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>REN gate (&gt;= 30% retention)</t>
+          <t>NB gate ($45,000)</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Assumed retention 75% vs 30%</t>
+          <t>NB written $52,435 vs $45,000</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
@@ -7248,34 +7248,51 @@
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
+          <t>REN gate (&gt;= 30% retention)</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Assumed retention 75% vs 30%</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
           <t>RWR gate (both)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Both NB and REN gates passed?</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>FINAL PAID</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B55" s="24" t="inlineStr">
         <is>
           <t>Pay only the lines whose gates passed + retention bonus</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>$824.74</t>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>$629.56</t>
         </is>
       </c>
     </row>
@@ -7283,11 +7300,11 @@
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7800,7 +7817,7 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>263.45</v>
+        <v>76.47499999999999</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>78.20999999999999</v>
@@ -7842,7 +7859,7 @@
         </is>
       </c>
       <c r="H31" s="16" t="n">
-        <v>254.8427777777778</v>
+        <v>67.42777777777778</v>
       </c>
       <c r="I31" s="16" t="n">
         <v>60.83</v>
@@ -7884,7 +7901,7 @@
         </is>
       </c>
       <c r="H32" s="16" t="n">
-        <v>525.2001111111111</v>
+        <v>319.7051111111111</v>
       </c>
       <c r="I32" s="16" t="n">
         <v>475.825</v>
@@ -7926,7 +7943,7 @@
         </is>
       </c>
       <c r="H33" s="16" t="n">
-        <v>285.7110833333334</v>
+        <v>115.3910333333333</v>
       </c>
       <c r="I33" s="16" t="n">
         <v>118.105</v>
@@ -7968,7 +7985,7 @@
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>285.4735277777778</v>
+        <v>123.1258777777778</v>
       </c>
       <c r="I34" s="16" t="n">
         <v>99.935</v>
@@ -8010,7 +8027,7 @@
         </is>
       </c>
       <c r="H35" s="16" t="n">
-        <v>282.4609333333333</v>
+        <v>115.6093333333333</v>
       </c>
       <c r="I35" s="16" t="n">
         <v>78.20999999999999</v>
@@ -8052,7 +8069,7 @@
         </is>
       </c>
       <c r="H36" s="16" t="n">
-        <v>824.7438888888889</v>
+        <v>629.5563888888889</v>
       </c>
       <c r="I36" s="16" t="n">
         <v>765.74</v>
@@ -8094,7 +8111,7 @@
         </is>
       </c>
       <c r="H37" s="16" t="n">
-        <v>731.5091666666667</v>
+        <v>604.3841666666667</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>594.11</v>
@@ -8136,7 +8153,7 @@
         </is>
       </c>
       <c r="H38" s="16" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I38" s="16" t="n">
         <v>0</v>
@@ -8178,7 +8195,7 @@
         </is>
       </c>
       <c r="H39" s="16" t="n">
-        <v>229</v>
+        <v>9.315000000000001</v>
       </c>
       <c r="I39" s="16" t="n">
         <v>7.9</v>
@@ -8220,7 +8237,7 @@
         </is>
       </c>
       <c r="H40" s="16" t="n">
-        <v>229.2411111111111</v>
+        <v>9.411111111111111</v>
       </c>
       <c r="I40" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8262,7 +8279,7 @@
         </is>
       </c>
       <c r="H41" s="16" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I41" s="16" t="n">
         <v>0</v>
@@ -8304,7 +8321,7 @@
         </is>
       </c>
       <c r="H42" s="16" t="n">
-        <v>231.9603888888889</v>
+        <v>14.28213888888889</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8346,7 +8363,7 @@
         </is>
       </c>
       <c r="H43" s="16" t="n">
-        <v>233.4994444444444</v>
+        <v>18.99444444444445</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>17.38</v>
@@ -8388,7 +8405,7 @@
         </is>
       </c>
       <c r="H44" s="16" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I44" s="16" t="n">
         <v>0</v>
@@ -8430,7 +8447,7 @@
         </is>
       </c>
       <c r="H45" s="16" t="n">
-        <v>230.2666666666667</v>
+        <v>9.691666666666666</v>
       </c>
       <c r="I45" s="16" t="n">
         <v>9.875</v>
@@ -8472,7 +8489,7 @@
         </is>
       </c>
       <c r="H46" s="16" t="n">
-        <v>241.7166666666667</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>34.76000000000001</v>
@@ -8514,7 +8531,7 @@
         </is>
       </c>
       <c r="H47" s="16" t="n">
-        <v>267.35</v>
+        <v>79.58000000000001</v>
       </c>
       <c r="I47" s="16" t="n">
         <v>45.425</v>
@@ -8556,7 +8573,7 @@
         </is>
       </c>
       <c r="H48" s="16" t="n">
-        <v>254.6775</v>
+        <v>57.89700000000001</v>
       </c>
       <c r="I48" s="16" t="n">
         <v>54.50999999999999</v>
@@ -8598,7 +8615,7 @@
         </is>
       </c>
       <c r="H49" s="16" t="n">
-        <v>248.0472222222222</v>
+        <v>41.13222222222223</v>
       </c>
       <c r="I49" s="16" t="n">
         <v>28.44</v>
@@ -8640,7 +8657,7 @@
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>252.2254555555556</v>
+        <v>59.74000555555556</v>
       </c>
       <c r="I50" s="16" t="n">
         <v>52.14</v>
@@ -8682,7 +8699,7 @@
         </is>
       </c>
       <c r="H51" s="16" t="n">
-        <v>237</v>
+        <v>27.46</v>
       </c>
       <c r="I51" s="16" t="n">
         <v>15.8</v>
@@ -8724,7 +8741,7 @@
         </is>
       </c>
       <c r="H52" s="16" t="n">
-        <v>721.1624666666667</v>
+        <v>496.1624666666667</v>
       </c>
       <c r="I52" s="16" t="n">
         <v>574.7600000000001</v>
@@ -8766,7 +8783,7 @@
         </is>
       </c>
       <c r="H53" s="16" t="n">
-        <v>237</v>
+        <v>24.57</v>
       </c>
       <c r="I53" s="16" t="n">
         <v>15.8</v>
@@ -8867,7 +8884,7 @@
         </is>
       </c>
       <c r="H58" s="16" t="n">
-        <v>339.4047222222222</v>
+        <v>221.2259722222222</v>
       </c>
       <c r="I58" s="16" t="n">
         <v>147.73</v>
@@ -8909,7 +8926,7 @@
         </is>
       </c>
       <c r="H59" s="16" t="n">
-        <v>334.0213888888889</v>
+        <v>223.2138888888889</v>
       </c>
       <c r="I59" s="16" t="n">
         <v>147.73</v>
@@ -8951,7 +8968,7 @@
         </is>
       </c>
       <c r="H60" s="16" t="n">
-        <v>572.2231111111112</v>
+        <v>429.7971111111111</v>
       </c>
       <c r="I60" s="16" t="n">
         <v>530.905</v>
@@ -8993,7 +9010,7 @@
         </is>
       </c>
       <c r="H61" s="16" t="n">
-        <v>325.7137916666667</v>
+        <v>193.7986166666667</v>
       </c>
       <c r="I61" s="16" t="n">
         <v>190.785</v>
@@ -9035,7 +9052,7 @@
         </is>
       </c>
       <c r="H62" s="16" t="n">
-        <v>462.0757333333333</v>
+        <v>463.9165333333334</v>
       </c>
       <c r="I62" s="16" t="n">
         <v>304.15</v>
@@ -9077,7 +9094,7 @@
         </is>
       </c>
       <c r="H63" s="16" t="n">
-        <v>464.8899888888889</v>
+        <v>511.8998888888889</v>
       </c>
       <c r="I63" s="16" t="n">
         <v>321.53</v>
@@ -9119,7 +9136,7 @@
         </is>
       </c>
       <c r="H64" s="16" t="n">
-        <v>937.8063888888889</v>
+        <v>983.1897638888889</v>
       </c>
       <c r="I64" s="16" t="n">
         <v>980.8700000000001</v>
@@ -9161,7 +9178,7 @@
         </is>
       </c>
       <c r="H65" s="16" t="n">
-        <v>824.4546416666666</v>
+        <v>857.7432166666665</v>
       </c>
       <c r="I65" s="16" t="n">
         <v>734.6900000000001</v>
@@ -9203,7 +9220,7 @@
         </is>
       </c>
       <c r="H66" s="16" t="n">
-        <v>378.6040277777778</v>
+        <v>312.0402777777778</v>
       </c>
       <c r="I66" s="16" t="n">
         <v>208.56</v>
@@ -9245,7 +9262,7 @@
         </is>
       </c>
       <c r="H67" s="16" t="n">
-        <v>339</v>
+        <v>244.29175</v>
       </c>
       <c r="I67" s="16" t="n">
         <v>150.1</v>
@@ -9287,7 +9304,7 @@
         </is>
       </c>
       <c r="H68" s="16" t="n">
-        <v>333.0357222222222</v>
+        <v>255.3572222222222</v>
       </c>
       <c r="I68" s="16" t="n">
         <v>217.25</v>
@@ -9329,7 +9346,7 @@
         </is>
       </c>
       <c r="H69" s="16" t="n">
-        <v>339.0545</v>
+        <v>222.545</v>
       </c>
       <c r="I69" s="16" t="n">
         <v>156.42</v>
@@ -9371,7 +9388,7 @@
         </is>
       </c>
       <c r="H70" s="16" t="n">
-        <v>311.9370833333334</v>
+        <v>193.1539583333333</v>
       </c>
       <c r="I70" s="16" t="n">
         <v>165.11</v>
@@ -9413,7 +9430,7 @@
         </is>
       </c>
       <c r="H71" s="16" t="n">
-        <v>345.1742361111111</v>
+        <v>239.8878611111111</v>
       </c>
       <c r="I71" s="16" t="n">
         <v>208.955</v>
@@ -9455,7 +9472,7 @@
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>290.3426388888889</v>
+        <v>124.1593888888889</v>
       </c>
       <c r="I72" s="16" t="n">
         <v>127.19</v>
@@ -9497,7 +9514,7 @@
         </is>
       </c>
       <c r="H73" s="16" t="n">
-        <v>309.9482777777778</v>
+        <v>166.4551777777778</v>
       </c>
       <c r="I73" s="16" t="n">
         <v>154.445</v>
@@ -9539,7 +9556,7 @@
         </is>
       </c>
       <c r="H74" s="16" t="n">
-        <v>302.2399805555556</v>
+        <v>178.3998055555556</v>
       </c>
       <c r="I74" s="16" t="n">
         <v>156.42</v>
@@ -9581,7 +9598,7 @@
         </is>
       </c>
       <c r="H75" s="16" t="n">
-        <v>358.653</v>
+        <v>241.6284</v>
       </c>
       <c r="I75" s="16" t="n">
         <v>154.445</v>
@@ -9623,7 +9640,7 @@
         </is>
       </c>
       <c r="H76" s="16" t="n">
-        <v>295.6270277777778</v>
+        <v>148.4486527777778</v>
       </c>
       <c r="I76" s="16" t="n">
         <v>139.04</v>
@@ -9665,7 +9682,7 @@
         </is>
       </c>
       <c r="H77" s="16" t="n">
-        <v>363.9838888888889</v>
+        <v>256.5548888888889</v>
       </c>
       <c r="I77" s="16" t="n">
         <v>154.445</v>
@@ -9707,7 +9724,7 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>378.1163277777778</v>
+        <v>307.1632777777778</v>
       </c>
       <c r="I78" s="16" t="n">
         <v>208.56</v>
@@ -9749,7 +9766,7 @@
         </is>
       </c>
       <c r="H79" s="16" t="n">
-        <v>321</v>
+        <v>229.53045</v>
       </c>
       <c r="I79" s="16" t="n">
         <v>126.4</v>
@@ -9791,7 +9808,7 @@
         </is>
       </c>
       <c r="H80" s="16" t="n">
-        <v>763.1624666666667</v>
+        <v>636.2990916666666</v>
       </c>
       <c r="I80" s="16" t="n">
         <v>657.3600000000001</v>
@@ -9833,7 +9850,7 @@
         </is>
       </c>
       <c r="H81" s="16" t="n">
-        <v>309.8633055555555</v>
+        <v>185.6330555555556</v>
       </c>
       <c r="I81" s="16" t="n">
         <v>112.97</v>
@@ -10958,13 +10975,13 @@
         <v>70.24277777777777</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>225</v>
+        <v>38.025</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>508.6927777777778</v>
+        <v>321.7177777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>263.45</v>
+        <v>76.47499999999999</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -10975,7 +10992,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-86.55000000000001</v>
+        <v>-273.525</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>350</v>
@@ -11009,13 +11026,13 @@
         <v>57</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>225</v>
+        <v>37.585</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>441.8427777777778</v>
+        <v>254.4277777777778</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>254.8427777777778</v>
+        <v>67.42777777777778</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -11026,7 +11043,7 @@
         <v>544.3810526</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>4.842777777777769</v>
+        <v>-182.5722222222222</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>250</v>
@@ -11060,13 +11077,13 @@
         <v>67.69733333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>225</v>
+        <v>19.505</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>525.2001111111111</v>
+        <v>319.7051111111111</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>525.2001111111111</v>
+        <v>319.7051111111111</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -11077,7 +11094,7 @@
         <v>829.8586758</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>175.2001111111111</v>
+        <v>-30.29488888888886</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -11111,13 +11128,13 @@
         <v>47.67208333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>225</v>
+        <v>54.67995</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>546.4119777777778</v>
+        <v>376.0919277777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>285.7110833333334</v>
+        <v>115.3910333333333</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -11128,7 +11145,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-64.28891666666664</v>
+        <v>-234.6089666666667</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>350</v>
@@ -11148,16 +11165,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>2022.147644444444</v>
+        <v>1271.942594444444</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1329.203972222222</v>
+        <v>578.9989222222223</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>29.20397222222232</v>
+        <v>-721.0010777777777</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>1300</v>
@@ -11923,13 +11940,13 @@
         <v>164.4863222222222</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>225</v>
+        <v>62.65235</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>610.95985</v>
+        <v>448.6122</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>285.4735277777778</v>
+        <v>123.1258777777778</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -11940,7 +11957,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-374.5264722222222</v>
+        <v>-536.8741222222222</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>660</v>
@@ -11974,13 +11991,13 @@
         <v>196.8581111111111</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>225</v>
+        <v>58.1484</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>649.3512055555556</v>
+        <v>482.4996055555555</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>282.4609333333333</v>
+        <v>115.6093333333333</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -11991,7 +12008,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-457.5390666666667</v>
+        <v>-624.3906666666667</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>740</v>
@@ -12025,13 +12042,13 @@
         <v>267.9203888888889</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>225</v>
+        <v>29.8125</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>824.7438888888889</v>
+        <v>629.5563888888889</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>824.7438888888889</v>
+        <v>629.5563888888889</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -12042,7 +12059,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>-195.2561111111111</v>
+        <v>-390.4436111111111</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>1020</v>
@@ -12076,13 +12093,13 @@
         <v>236.9039722222222</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>225</v>
+        <v>97.875</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>731.5091666666667</v>
+        <v>604.3841666666667</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>731.5091666666667</v>
+        <v>604.3841666666667</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -12093,7 +12110,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>11.50916666666672</v>
+        <v>-115.6158333333333</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>720</v>
@@ -12113,16 +12130,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>2816.564111111111</v>
+        <v>2165.052361111111</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>2124.187516666667</v>
+        <v>1472.675766666667</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>-1015.812483333333</v>
+        <v>-1667.324233333333</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>3140</v>
@@ -12888,13 +12905,13 @@
         <v>163.2080555555555</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>563.6958333333333</v>
+        <v>338.6958333333333</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -12905,7 +12922,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-515</v>
+        <v>-740</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>740</v>
@@ -12939,13 +12956,13 @@
         <v>111</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>225</v>
+        <v>5.315</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>405</v>
+        <v>185.315</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>229</v>
+        <v>9.315000000000001</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -12956,7 +12973,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>-221</v>
+        <v>-440.685</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>450</v>
@@ -12990,13 +13007,13 @@
         <v>111.5892222222222</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>225</v>
+        <v>5.17</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>536.8303333333333</v>
+        <v>317.0003333333333</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>229.2411111111111</v>
+        <v>9.411111111111111</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -13007,7 +13024,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-480.7588888888889</v>
+        <v>-700.5888888888888</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>710</v>
@@ -13041,13 +13058,13 @@
         <v>85.77566666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>427.2071666666667</v>
+        <v>202.2071666666667</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -13058,7 +13075,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>-245</v>
+        <v>-470</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>470</v>
@@ -13078,16 +13095,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1932.733333333333</v>
+        <v>1043.218333333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>908.2411111111111</v>
+        <v>18.72611111111111</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-1461.758888888889</v>
+        <v>-2351.273888888889</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>2370</v>
@@ -13853,13 +13870,13 @@
         <v>90.62005555555555</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>225</v>
+        <v>7.32175</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>465.0943611111111</v>
+        <v>247.4161111111111</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>231.9603888888889</v>
+        <v>14.28213888888889</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -13870,7 +13887,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-258.0396111111111</v>
+        <v>-475.7178611111111</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>490</v>
@@ -13904,13 +13921,13 @@
         <v>135.3540277777778</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>225</v>
+        <v>10.495</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>488.5466388888889</v>
+        <v>274.0416388888889</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>233.4994444444444</v>
+        <v>18.99444444444445</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -13921,7 +13938,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-366.5005555555556</v>
+        <v>-581.0055555555556</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>600</v>
@@ -13955,13 +13972,13 @@
         <v>74.35194444444444</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>476.2102777777778</v>
+        <v>251.2102777777778</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
@@ -13972,7 +13989,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>-265</v>
+        <v>-490</v>
       </c>
       <c r="O87" s="11" t="n">
         <v>490</v>
@@ -14006,13 +14023,13 @@
         <v>95.97988888888888</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>225</v>
+        <v>4.425</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>504.7810555555556</v>
+        <v>284.2060555555556</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>230.2666666666667</v>
+        <v>9.691666666666666</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -14023,7 +14040,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-259.7333333333333</v>
+        <v>-480.3083333333333</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>490</v>
@@ -14043,16 +14060,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1934.632333333333</v>
+        <v>1056.874083333333</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>920.7265</v>
+        <v>42.96825</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-1149.2735</v>
+        <v>-2027.03175</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>2070</v>
@@ -14818,13 +14835,13 @@
         <v>65.04662777777777</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>225</v>
+        <v>18.45</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>376.7632944444445</v>
+        <v>170.2132944444444</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>241.7166666666667</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -14835,7 +14852,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>-108.2833333333333</v>
+        <v>-314.8333333333333</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>350</v>
@@ -14869,13 +14886,13 @@
         <v>55.7212</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>225</v>
+        <v>37.23</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>427.1902277777777</v>
+        <v>239.4202277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>267.35</v>
+        <v>79.58000000000001</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -14886,7 +14903,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>-82.64999999999998</v>
+        <v>-270.42</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>350</v>
@@ -14920,13 +14937,13 @@
         <v>47.37872222222222</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>225</v>
+        <v>28.2195</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>414.9553611111111</v>
+        <v>218.1748611111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>254.6775</v>
+        <v>57.89700000000001</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -14937,7 +14954,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>-95.32249999999999</v>
+        <v>-292.103</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>350</v>
@@ -14971,13 +14988,13 @@
         <v>99.44133333333333</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>225</v>
+        <v>18.085</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>434.6524444444444</v>
+        <v>227.7374444444444</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>248.0472222222222</v>
+        <v>41.13222222222223</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -14988,7 +15005,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>-101.9527777777778</v>
+        <v>-308.8677777777777</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>350</v>
@@ -15008,16 +15025,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1653.561327777778</v>
+        <v>855.5458277777777</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>1011.791388888889</v>
+        <v>213.7758888888889</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>-388.2086111111111</v>
+        <v>-1186.224111111111</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>1400</v>
@@ -15783,13 +15800,13 @@
         <v>125.6738666666667</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>225</v>
+        <v>32.51455</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>555.3496444444445</v>
+        <v>362.8641944444444</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>252.2254555555556</v>
+        <v>59.74000555555556</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -15800,7 +15817,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-297.7745444444445</v>
+        <v>-490.2599944444444</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>550</v>
@@ -15834,13 +15851,13 @@
         <v>103.5712111111111</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>225</v>
+        <v>15.46</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>508.5900444444445</v>
+        <v>299.0500444444444</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>237</v>
+        <v>27.46</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -15851,7 +15868,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-213</v>
+        <v>-422.54</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>450</v>
@@ -15885,13 +15902,13 @@
         <v>84</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>721.1624666666667</v>
+        <v>496.1624666666667</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>721.1624666666667</v>
+        <v>496.1624666666667</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -15902,7 +15919,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>131.1624666666667</v>
+        <v>-93.83753333333334</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>590</v>
@@ -15936,13 +15953,13 @@
         <v>90.53322222222222</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>225</v>
+        <v>12.57</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>499.9282111111111</v>
+        <v>287.4982111111111</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>237</v>
+        <v>24.57</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -15953,7 +15970,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-113</v>
+        <v>-325.43</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>350</v>
@@ -15973,16 +15990,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2285.030366666667</v>
+        <v>1445.574916666666</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1447.387922222222</v>
+        <v>607.9324722222223</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>-492.6120777777778</v>
+        <v>-1332.067527777778</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1940</v>
@@ -16818,13 +16835,13 @@
         <v>36.28805555555556</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>225</v>
+        <v>106.82125</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>550.6927777777778</v>
+        <v>432.5140277777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>339.4047222222222</v>
+        <v>221.2259722222222</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -16835,7 +16852,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>89.40472222222223</v>
+        <v>-28.77402777777777</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -16869,13 +16886,13 @@
         <v>27</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>225</v>
+        <v>114.1925</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>491.0213888888889</v>
+        <v>380.2138888888889</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>334.0213888888889</v>
+        <v>223.2138888888889</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -16886,7 +16903,7 @@
         <v>544.3810526000001</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>334.0213888888889</v>
+        <v>223.2138888888889</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -16920,13 +16937,13 @@
         <v>35.01533333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>225</v>
+        <v>82.574</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>572.2231111111112</v>
+        <v>429.7971111111111</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>572.2231111111112</v>
+        <v>429.7971111111111</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -16937,7 +16954,7 @@
         <v>829.8586758000001</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>222.2231111111112</v>
+        <v>79.79711111111112</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -16971,13 +16988,13 @@
         <v>23.669375</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>225</v>
+        <v>93.08482500000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>562.4119777777778</v>
+        <v>430.4968027777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>325.7137916666667</v>
+        <v>193.7986166666667</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -16988,7 +17005,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>75.71379166666668</v>
+        <v>-56.20138333333333</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>250</v>
@@ -17008,16 +17025,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>2176.349255555556</v>
+        <v>1673.021830555555</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1571.363013888889</v>
+        <v>1068.035588888889</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>721.3630138888889</v>
+        <v>218.0355888888889</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>850</v>
@@ -17783,13 +17800,13 @@
         <v>82.24316111111111</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>225</v>
+        <v>226.8408</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>705.3188944444445</v>
+        <v>707.1596944444445</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>462.0757333333333</v>
+        <v>463.9165333333334</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -17800,7 +17817,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>112.0757333333333</v>
+        <v>113.9165333333334</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -17834,13 +17851,13 @@
         <v>98.42905555555555</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>225</v>
+        <v>272.0099</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>733.3512055555556</v>
+        <v>780.3611055555556</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>464.8899888888889</v>
+        <v>511.8998888888889</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -17851,7 +17868,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>4.889988888888865</v>
+        <v>51.89988888888888</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -17885,13 +17902,13 @@
         <v>135.1268611111111</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>225</v>
+        <v>270.383375</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>937.8063888888889</v>
+        <v>983.1897638888889</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>937.8063888888889</v>
+        <v>983.1897638888889</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -17902,7 +17919,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>257.8063888888889</v>
+        <v>303.1897638888889</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -17936,13 +17953,13 @@
         <v>118.4519861111111</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>225</v>
+        <v>258.288575</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>824.4546416666666</v>
+        <v>857.7432166666665</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>824.4546416666666</v>
+        <v>857.7432166666665</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -17953,7 +17970,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>324.4546416666666</v>
+        <v>357.7432166666665</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -17973,16 +17990,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>3200.931130555556</v>
+        <v>3328.453780555556</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>2689.226752777778</v>
+        <v>2816.749402777778</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>699.2267527777776</v>
+        <v>826.7494027777775</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>1990</v>
@@ -18748,13 +18765,13 @@
         <v>81.60402777777777</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>225</v>
+        <v>158.43625</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>635.6958333333333</v>
+        <v>569.1320833333333</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>378.6040277777778</v>
+        <v>312.0402777777778</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -18765,7 +18782,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-121.3959722222222</v>
+        <v>-187.9597222222222</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -18799,13 +18816,13 @@
         <v>57</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>225</v>
+        <v>130.29175</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>461</v>
+        <v>366.29175</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>339</v>
+        <v>244.29175</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -18816,7 +18833,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>89</v>
+        <v>-5.708249999999992</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>250</v>
@@ -18850,13 +18867,13 @@
         <v>55.79461111111111</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>225</v>
+        <v>147.3215</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>584.8303333333333</v>
+        <v>507.1518333333333</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>333.0357222222222</v>
+        <v>255.3572222222222</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -18867,7 +18884,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-136.9642777777778</v>
+        <v>-214.6427777777778</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -18901,13 +18918,13 @@
         <v>43.72116666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>225</v>
+        <v>108.4905</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>499.2071666666666</v>
+        <v>382.6976666666666</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>339.0545</v>
+        <v>222.545</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -18918,7 +18935,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>89.05450000000002</v>
+        <v>-27.45499999999998</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -18938,16 +18955,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>2180.733333333333</v>
+        <v>1825.273333333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>1389.69425</v>
+        <v>1034.23425</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-80.30574999999999</v>
+        <v>-435.76575</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>1470</v>
@@ -19713,13 +19730,13 @@
         <v>44.64336111111111</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>225</v>
+        <v>106.216875</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>499.0943611111111</v>
+        <v>380.3112361111111</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>311.9370833333334</v>
+        <v>193.1539583333333</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -19730,7 +19747,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-38.06291666666664</v>
+        <v>-156.8460416666667</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -19764,13 +19781,13 @@
         <v>67.67701388888889</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>225</v>
+        <v>119.713625</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>532.5444166666666</v>
+        <v>427.2580416666667</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>345.1742361111111</v>
+        <v>239.8878611111111</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -19781,7 +19798,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-4.825763888888901</v>
+        <v>-110.1121388888889</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -19815,13 +19832,13 @@
         <v>37.00930555555556</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>225</v>
+        <v>58.81675000000001</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>504.2102777777778</v>
+        <v>338.0270277777778</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>290.3426388888889</v>
+        <v>124.1593888888889</v>
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
@@ -19832,7 +19849,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>-59.65736111111113</v>
+        <v>-225.8406111111111</v>
       </c>
       <c r="O87" s="11" t="n">
         <v>350</v>
@@ -19866,13 +19883,13 @@
         <v>47.82327777777778</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>225</v>
+        <v>81.5069</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>536.3060555555555</v>
+        <v>392.8129555555555</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>309.9482777777778</v>
+        <v>166.4551777777778</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -19883,7 +19900,7 @@
         <v>924.3805879</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-40.05172222222222</v>
+        <v>-183.5448222222222</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>350</v>
@@ -19903,16 +19920,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>2072.155111111111</v>
+        <v>1538.409261111111</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>1257.402236111111</v>
+        <v>723.656386111111</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-142.5977638888889</v>
+        <v>-676.343613888889</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>1400</v>
@@ -20678,13 +20695,13 @@
         <v>32.52331388888889</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>225</v>
+        <v>101.159825</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>404.7632944444445</v>
+        <v>280.9231194444445</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>302.2399805555556</v>
+        <v>178.3998055555556</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -20695,7 +20712,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>302.2399805555556</v>
+        <v>178.3998055555556</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -20729,13 +20746,13 @@
         <v>27.8606</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>225</v>
+        <v>107.9754</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>490.6326277777778</v>
+        <v>373.6080277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>358.653</v>
+        <v>241.6284</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -20746,7 +20763,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>358.653</v>
+        <v>241.6284</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -20780,13 +20797,13 @@
         <v>23.02269444444444</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>225</v>
+        <v>77.821625</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>431.5488611111111</v>
+        <v>284.3704861111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>295.6270277777778</v>
+        <v>148.4486527777778</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -20797,7 +20814,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>295.6270277777778</v>
+        <v>148.4486527777778</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>0</v>
@@ -20831,13 +20848,13 @@
         <v>51.054</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>225</v>
+        <v>117.571</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>502.2017777777778</v>
+        <v>394.7727777777778</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>363.9838888888889</v>
+        <v>256.5548888888889</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -20848,7 +20865,7 @@
         <v>895.0173385999999</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>363.9838888888889</v>
+        <v>256.5548888888889</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -20868,16 +20885,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1829.146561111111</v>
+        <v>1333.674411111111</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>1320.503897222222</v>
+        <v>825.0317472222223</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>1320.503897222222</v>
+        <v>825.0317472222223</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>0</v>
@@ -21643,13 +21660,13 @@
         <v>64.17026666666666</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>225</v>
+        <v>154.04695</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>619.7369166666666</v>
+        <v>548.7838666666667</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>378.1163277777778</v>
+        <v>307.1632777777778</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -21660,7 +21677,7 @@
         <v>985.1345504</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>28.11632777777777</v>
+        <v>-42.83672222222219</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -21694,13 +21711,13 @@
         <v>53.11893888888889</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>225</v>
+        <v>133.53045</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>542.1377722222222</v>
+        <v>450.6682222222222</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>321</v>
+        <v>229.53045</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -21711,7 +21728,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-29</v>
+        <v>-120.46955</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>350</v>
@@ -21745,13 +21762,13 @@
         <v>42</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>225</v>
+        <v>98.13662500000001</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>763.1624666666667</v>
+        <v>636.2990916666666</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>763.1624666666667</v>
+        <v>636.2990916666666</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -21762,7 +21779,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>313.1624666666667</v>
+        <v>186.2990916666666</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -21796,13 +21813,13 @@
         <v>45.26661111111111</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>225</v>
+        <v>100.76975</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>527.5249055555555</v>
+        <v>403.2946555555556</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>309.8633055555555</v>
+        <v>185.6330555555556</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -21813,7 +21830,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>59.86330555555554</v>
+        <v>-64.36694444444444</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -21833,16 +21850,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2452.562061111111</v>
+        <v>2039.045836111111</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1772.1421</v>
+        <v>1358.625875</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>372.1421</v>
+        <v>-41.37412500000005</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1400</v>
@@ -22584,13 +22601,13 @@
         <v>20.45</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>225</v>
+        <v>137.5925</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>541.6927777777778</v>
+        <v>454.2852777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>346.2427777777777</v>
+        <v>258.8352777777778</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -22598,7 +22615,7 @@
         </is>
       </c>
       <c r="M13" s="11" t="n">
-        <v>96.24277777777775</v>
+        <v>8.835277777777776</v>
       </c>
       <c r="N13" s="11" t="n">
         <v>250</v>
@@ -22632,13 +22649,13 @@
         <v>15.84277777777778</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>225</v>
+        <v>153.215</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>484.8427777777778</v>
+        <v>413.0577777777778</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>339</v>
+        <v>267.215</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -22646,7 +22663,7 @@
         </is>
       </c>
       <c r="M14" s="11" t="n">
-        <v>339</v>
+        <v>267.215</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>0</v>
@@ -22680,13 +22697,13 @@
         <v>12.50277777777778</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>225</v>
+        <v>126.138</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>566.2001111111111</v>
+        <v>467.3381111111111</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>566.2001111111111</v>
+        <v>467.3381111111111</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -22694,7 +22711,7 @@
         </is>
       </c>
       <c r="M15" s="11" t="n">
-        <v>216.2001111111111</v>
+        <v>117.3381111111111</v>
       </c>
       <c r="N15" s="11" t="n">
         <v>350</v>
@@ -22728,13 +22745,13 @@
         <v>34.71108333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>225</v>
+        <v>76.80975000000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>550.4119777777778</v>
+        <v>402.2217277777778</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>302.6720833333333</v>
+        <v>154.4818333333333</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -22742,7 +22759,7 @@
         </is>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-47.32791666666668</v>
+        <v>-195.5181666666667</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>350</v>
@@ -22764,11 +22781,11 @@
       <c r="I17" s="34" t="n"/>
       <c r="J17" s="34" t="n"/>
       <c r="K17" s="19" t="n">
-        <v>1554.114972222222</v>
+        <v>1147.870222222222</v>
       </c>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="19" t="n">
-        <v>604.1149722222221</v>
+        <v>197.8702222222223</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>950</v>
@@ -23127,13 +23144,13 @@
         <v>38.47352777777778</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>225</v>
+        <v>328.3769</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>732.95985</v>
+        <v>836.3367499999999</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>533.4863222222223</v>
+        <v>636.8632222222222</v>
       </c>
       <c r="L28" s="33" t="inlineStr">
         <is>
@@ -23141,7 +23158,7 @@
         </is>
       </c>
       <c r="M28" s="11" t="n">
-        <v>283.4863222222223</v>
+        <v>386.8632222222222</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>250</v>
@@ -23175,13 +23192,13 @@
         <v>30.46093333333333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>225</v>
+        <v>427.723</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>790.3512055555555</v>
+        <v>993.0742055555554</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>589.8581111111112</v>
+        <v>792.5811111111111</v>
       </c>
       <c r="L29" s="33" t="inlineStr">
         <is>
@@ -23189,7 +23206,7 @@
         </is>
       </c>
       <c r="M29" s="11" t="n">
-        <v>339.8581111111112</v>
+        <v>542.5811111111111</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>250</v>
@@ -23223,13 +23240,13 @@
         <v>18.89583333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>225</v>
+        <v>481.1417500000001</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>1017.743888888889</v>
+        <v>1273.885638888889</v>
       </c>
       <c r="K30" s="17" t="n">
-        <v>1017.743888888889</v>
+        <v>1273.885638888889</v>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
@@ -23237,7 +23254,7 @@
         </is>
       </c>
       <c r="M30" s="11" t="n">
-        <v>667.7438888888889</v>
+        <v>923.8856388888889</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>350</v>
@@ -23271,13 +23288,13 @@
         <v>10</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>225</v>
+        <v>320.82715</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>851.5091666666667</v>
+        <v>947.3363166666668</v>
       </c>
       <c r="K31" s="17" t="n">
-        <v>851.5091666666667</v>
+        <v>947.3363166666668</v>
       </c>
       <c r="L31" s="23" t="inlineStr">
         <is>
@@ -23285,7 +23302,7 @@
         </is>
       </c>
       <c r="M31" s="11" t="n">
-        <v>501.5091666666667</v>
+        <v>597.3363166666668</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>350</v>
@@ -23307,11 +23324,11 @@
       <c r="I32" s="34" t="n"/>
       <c r="J32" s="34" t="n"/>
       <c r="K32" s="19" t="n">
-        <v>2992.597488888889</v>
+        <v>3650.666288888889</v>
       </c>
       <c r="L32" s="34" t="n"/>
       <c r="M32" s="19" t="n">
-        <v>1792.597488888889</v>
+        <v>2450.666288888889</v>
       </c>
       <c r="N32" s="19" t="n">
         <v>1200</v>
@@ -23670,13 +23687,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>225</v>
+        <v>316.8725</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>707.6958333333333</v>
+        <v>799.5683333333334</v>
       </c>
       <c r="K43" s="17" t="n">
-        <v>532.2080555555556</v>
+        <v>624.0805555555555</v>
       </c>
       <c r="L43" s="33" t="inlineStr">
         <is>
@@ -23684,7 +23701,7 @@
         </is>
       </c>
       <c r="M43" s="11" t="n">
-        <v>282.2080555555556</v>
+        <v>374.0805555555555</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>250</v>
@@ -23718,13 +23735,13 @@
         <v>2</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>225</v>
+        <v>249.9535</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>514</v>
+        <v>538.9535</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>447</v>
+        <v>471.9535</v>
       </c>
       <c r="L44" s="33" t="inlineStr">
         <is>
@@ -23732,7 +23749,7 @@
         </is>
       </c>
       <c r="M44" s="11" t="n">
-        <v>447</v>
+        <v>471.9535</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>0</v>
@@ -23766,13 +23783,13 @@
         <v>2.241111111111111</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>225</v>
+        <v>284.303</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>630.8303333333333</v>
+        <v>690.1333333333334</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>432.5892222222222</v>
+        <v>491.8922222222222</v>
       </c>
       <c r="L45" s="33" t="inlineStr">
         <is>
@@ -23780,7 +23797,7 @@
         </is>
       </c>
       <c r="M45" s="11" t="n">
-        <v>432.5892222222222</v>
+        <v>491.8922222222222</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>0</v>
@@ -23814,13 +23831,13 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>225</v>
+        <v>216.981</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>501.2071666666667</v>
+        <v>493.1881666666667</v>
       </c>
       <c r="K46" s="17" t="n">
-        <v>384.7756666666667</v>
+        <v>376.7566666666667</v>
       </c>
       <c r="L46" s="33" t="inlineStr">
         <is>
@@ -23828,7 +23845,7 @@
         </is>
       </c>
       <c r="M46" s="11" t="n">
-        <v>384.7756666666667</v>
+        <v>376.7566666666667</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>0</v>
@@ -23850,11 +23867,11 @@
       <c r="I47" s="34" t="n"/>
       <c r="J47" s="34" t="n"/>
       <c r="K47" s="19" t="n">
-        <v>1796.572944444444</v>
+        <v>1964.682944444444</v>
       </c>
       <c r="L47" s="34" t="n"/>
       <c r="M47" s="19" t="n">
-        <v>1546.572944444444</v>
+        <v>1714.682944444444</v>
       </c>
       <c r="N47" s="19" t="n">
         <v>250</v>
@@ -24213,13 +24230,13 @@
         <v>3.960388888888889</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>225</v>
+        <v>197.79025</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>532.0943611111111</v>
+        <v>504.8846111111111</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>385.6200555555556</v>
+        <v>358.4103055555556</v>
       </c>
       <c r="L58" s="33" t="inlineStr">
         <is>
@@ -24227,7 +24244,7 @@
         </is>
       </c>
       <c r="M58" s="11" t="n">
-        <v>385.6200555555556</v>
+        <v>358.4103055555556</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>0</v>
@@ -24261,13 +24278,13 @@
         <v>4.499444444444444</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>225</v>
+        <v>218.43725</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>568.546638888889</v>
+        <v>561.9838888888889</v>
       </c>
       <c r="K59" s="17" t="n">
-        <v>444.3540277777778</v>
+        <v>437.7912777777777</v>
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
@@ -24275,7 +24292,7 @@
         </is>
       </c>
       <c r="M59" s="11" t="n">
-        <v>444.3540277777778</v>
+        <v>437.7912777777777</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>0</v>
@@ -24309,13 +24326,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>225</v>
+        <v>117.6335</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>530.2102777777778</v>
+        <v>422.8437777777779</v>
       </c>
       <c r="K60" s="17" t="n">
-        <v>353.3519444444445</v>
+        <v>245.9854444444445</v>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
@@ -24323,7 +24340,7 @@
         </is>
       </c>
       <c r="M60" s="11" t="n">
-        <v>353.3519444444445</v>
+        <v>245.9854444444445</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>0</v>
@@ -24357,13 +24374,13 @@
         <v>3.266666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>225</v>
+        <v>154.1638</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>564.7810555555556</v>
+        <v>493.9448555555556</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>382.9798888888889</v>
+        <v>312.1436888888888</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -24371,7 +24388,7 @@
         </is>
       </c>
       <c r="M61" s="11" t="n">
-        <v>382.9798888888889</v>
+        <v>312.1436888888888</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>0</v>
@@ -24393,11 +24410,11 @@
       <c r="I62" s="34" t="n"/>
       <c r="J62" s="34" t="n"/>
       <c r="K62" s="19" t="n">
-        <v>1566.305916666666</v>
+        <v>1354.330716666667</v>
       </c>
       <c r="L62" s="34" t="n"/>
       <c r="M62" s="19" t="n">
-        <v>1566.305916666666</v>
+        <v>1354.330716666667</v>
       </c>
       <c r="N62" s="19" t="n">
         <v>0</v>
@@ -24756,13 +24773,13 @@
         <v>8.716666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>225</v>
+        <v>165.41965</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>424.7632944444445</v>
+        <v>365.1829444444444</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>346.0466277777778</v>
+        <v>286.4662777777778</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -24770,7 +24787,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="n">
-        <v>346.0466277777778</v>
+        <v>286.4662777777778</v>
       </c>
       <c r="N73" s="11" t="n">
         <v>0</v>
@@ -24804,13 +24821,13 @@
         <v>27.35</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>225</v>
+        <v>141.4908</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>460.1902277777777</v>
+        <v>376.6810277777778</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>328.7212</v>
+        <v>245.212</v>
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
@@ -24818,7 +24835,7 @@
         </is>
       </c>
       <c r="M74" s="11" t="n">
-        <v>328.7212</v>
+        <v>245.212</v>
       </c>
       <c r="N74" s="11" t="n">
         <v>0</v>
@@ -24852,13 +24869,13 @@
         <v>17.6775</v>
       </c>
       <c r="I75" s="11" t="n">
-        <v>225</v>
+        <v>99.20425</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>440.9553611111111</v>
+        <v>315.1596111111111</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>310.3787222222222</v>
+        <v>184.5829722222222</v>
       </c>
       <c r="L75" s="33" t="inlineStr">
         <is>
@@ -24866,7 +24883,7 @@
         </is>
       </c>
       <c r="M75" s="11" t="n">
-        <v>310.3787222222222</v>
+        <v>184.5829722222222</v>
       </c>
       <c r="N75" s="11" t="n">
         <v>0</v>
@@ -24900,13 +24917,13 @@
         <v>14.04722222222222</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>225</v>
+        <v>198.972</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>512.6524444444444</v>
+        <v>486.6244444444444</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>411.4413333333333</v>
+        <v>385.4133333333334</v>
       </c>
       <c r="L76" s="33" t="inlineStr">
         <is>
@@ -24914,7 +24931,7 @@
         </is>
       </c>
       <c r="M76" s="11" t="n">
-        <v>411.4413333333333</v>
+        <v>385.4133333333334</v>
       </c>
       <c r="N76" s="11" t="n">
         <v>0</v>
@@ -24936,11 +24953,11 @@
       <c r="I77" s="34" t="n"/>
       <c r="J77" s="34" t="n"/>
       <c r="K77" s="19" t="n">
-        <v>1396.587883333333</v>
+        <v>1101.674583333333</v>
       </c>
       <c r="L77" s="34" t="n"/>
       <c r="M77" s="19" t="n">
-        <v>1396.587883333333</v>
+        <v>1101.674583333333</v>
       </c>
       <c r="N77" s="19" t="n">
         <v>0</v>
@@ -25299,13 +25316,13 @@
         <v>15.22545555555556</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>225</v>
+        <v>243.0648</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>654.3496444444444</v>
+        <v>672.4144444444444</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>461.6738666666666</v>
+        <v>479.7386666666666</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -25313,7 +25330,7 @@
         </is>
       </c>
       <c r="M88" s="11" t="n">
-        <v>461.6738666666666</v>
+        <v>479.7386666666666</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>0</v>
@@ -25347,13 +25364,13 @@
         <v>6</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>225</v>
+        <v>236.1409</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>589.5900444444444</v>
+        <v>600.7309444444444</v>
       </c>
       <c r="K89" s="17" t="n">
-        <v>415.5712111111111</v>
+        <v>426.7121111111111</v>
       </c>
       <c r="L89" s="33" t="inlineStr">
         <is>
@@ -25361,7 +25378,7 @@
         </is>
       </c>
       <c r="M89" s="11" t="n">
-        <v>415.5712111111111</v>
+        <v>426.7121111111111</v>
       </c>
       <c r="N89" s="11" t="n">
         <v>0</v>
@@ -25395,13 +25412,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="11" t="n">
-        <v>225</v>
+        <v>196.27325</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>805.1624666666667</v>
+        <v>776.4357166666666</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>805.1624666666667</v>
+        <v>776.4357166666666</v>
       </c>
       <c r="L90" s="23" t="inlineStr">
         <is>
@@ -25409,7 +25426,7 @@
         </is>
       </c>
       <c r="M90" s="11" t="n">
-        <v>455.1624666666667</v>
+        <v>426.4357166666666</v>
       </c>
       <c r="N90" s="11" t="n">
         <v>350</v>
@@ -25443,13 +25460,13 @@
         <v>6</v>
       </c>
       <c r="I91" s="11" t="n">
-        <v>225</v>
+        <v>176.3995</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>559.9282111111111</v>
+        <v>511.3277111111112</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>381.5332222222222</v>
+        <v>332.9327222222223</v>
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
@@ -25457,7 +25474,7 @@
         </is>
       </c>
       <c r="M91" s="11" t="n">
-        <v>381.5332222222222</v>
+        <v>332.9327222222223</v>
       </c>
       <c r="N91" s="11" t="n">
         <v>0</v>
@@ -25479,11 +25496,11 @@
       <c r="I92" s="34" t="n"/>
       <c r="J92" s="34" t="n"/>
       <c r="K92" s="19" t="n">
-        <v>2063.940766666667</v>
+        <v>2015.819216666667</v>
       </c>
       <c r="L92" s="34" t="n"/>
       <c r="M92" s="19" t="n">
-        <v>1713.940766666667</v>
+        <v>1665.819216666667</v>
       </c>
       <c r="N92" s="19" t="n">
         <v>350</v>

--- a/output/Bonus_Plan_FINAL.xlsx
+++ b/output/Bonus_Plan_FINAL.xlsx
@@ -3052,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3146,12 +3146,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>Per-policy BASE</t>
+          <t>Renewals</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
         <is>
-          <t>REN: &lt;$1,200=$4 | $1,200-$1,799=$6 | $1,800-$2,499=$8 | $2,500+=$10</t>
+          <t>NO per-policy REN. Renewals are paid via the RETENTION BONUS only.</t>
         </is>
       </c>
       <c r="C6" s="44" t="n"/>
@@ -3171,12 +3171,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t>Collected incentive</t>
+          <t>Retention Bonus</t>
         </is>
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>Only on policies &gt; $1,200 premium. 15-19%=+$1 | 20-24%=+$2 | 25-99%=+$5 | 100% PIF=+$8</t>
+          <t>REN written premium x 1% (e.g., $50k REN -&gt; $500 bonus). Paid monthly at the agent level, not per policy.</t>
         </is>
       </c>
       <c r="C7" s="44" t="n"/>
@@ -3196,12 +3196,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>Minimums (monthly)</t>
+          <t>Collected incentive</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>NB premium &gt;= $45,000 | REN retention &gt;= 30% of book | RWR follows NB gate</t>
+          <t>Only on policies &gt; $1,200 premium. 15-19%=+$1 | 20-24%=+$2 | 25-99%=+$5 | 100% PIF=+$8</t>
         </is>
       </c>
       <c r="C8" s="44" t="n"/>
@@ -3221,12 +3221,12 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Minimums (monthly)</t>
         </is>
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
+          <t>NB premium &gt;= $45,000 | REN retention &gt;= 30% of book | RWR follows NB gate</t>
         </is>
       </c>
       <c r="C9" s="44" t="n"/>
@@ -3243,106 +3243,114 @@
       <c r="N9" s="44" t="n"/>
       <c r="O9" s="45" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Chargeback</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>3 months (90 days) - bonus reversed if policy cancels/rewrites within 90 days</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+      <c r="I10" s="44" t="n"/>
+      <c r="J10" s="44" t="n"/>
+      <c r="K10" s="44" t="n"/>
+      <c r="L10" s="44" t="n"/>
+      <c r="M10" s="44" t="n"/>
+      <c r="N10" s="44" t="n"/>
+      <c r="O10" s="45" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ONE ROW PER POLICY</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Policy #</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Carrier</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Type (NB/RWR/REN)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Eff Date</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Exp Date</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>90-Day Review Date</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Written Premium</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>Down Payment $</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>Collected % (calc)</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>PIF?</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Per-Policy Base $</t>
         </is>
       </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Collected Incentive $</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>Total Bonus $</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="14" t="inlineStr"/>
-      <c r="K13" s="14" t="inlineStr"/>
-      <c r="L13" s="14" t="inlineStr"/>
-      <c r="M13" s="14" t="inlineStr"/>
-      <c r="N13" s="14" t="inlineStr"/>
-      <c r="O13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr"/>
@@ -3837,16 +3845,34 @@
       <c r="N42" s="14" t="inlineStr"/>
       <c r="O42" s="14" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr"/>
+      <c r="C43" s="14" t="inlineStr"/>
+      <c r="D43" s="14" t="inlineStr"/>
+      <c r="E43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="14" t="inlineStr"/>
+      <c r="H43" s="14" t="inlineStr"/>
+      <c r="I43" s="14" t="inlineStr"/>
+      <c r="J43" s="14" t="inlineStr"/>
+      <c r="K43" s="14" t="inlineStr"/>
+      <c r="L43" s="14" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+      <c r="N43" s="14" t="inlineStr"/>
+      <c r="O43" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B9:O9"/>
+    <mergeCell ref="A12:O12"/>
     <mergeCell ref="B8:O8"/>
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="B6:O6"/>
-    <mergeCell ref="A11:O11"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B10:O10"/>
     <mergeCell ref="B5:O5"/>
     <mergeCell ref="A3:O3"/>
   </mergeCells>
@@ -4582,13 +4608,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>7838.208116666666</v>
+        <v>7915.425727777778</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>11737.87845277778</v>
+        <v>11862.83671111111</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14397.59311666666</v>
+        <v>14902.49108333333</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4603,13 +4629,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>2935.077411111111</v>
+        <v>3012.295022222223</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7826.333250000001</v>
+        <v>7951.291508333333</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>11235.04397222222</v>
+        <v>11739.94193888889</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4702,13 +4728,13 @@
         <v>350</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>321.7177777777778</v>
+        <v>321.2927777777778</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>76.47499999999999</v>
+        <v>76.05</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>-273.525</v>
+        <v>-273.95</v>
       </c>
     </row>
     <row r="15">
@@ -4735,13 +4761,13 @@
         <v>660</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>448.6122</v>
+        <v>450.7910222222222</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>123.1258777777778</v>
+        <v>125.3047</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>-536.8741222222222</v>
+        <v>-534.6953</v>
       </c>
     </row>
     <row r="16">
@@ -4801,13 +4827,13 @@
         <v>490</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>247.4161111111111</v>
+        <v>247.7774722222222</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>14.28213888888889</v>
+        <v>14.6435</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>-475.7178611111111</v>
+        <v>-475.3565</v>
       </c>
     </row>
     <row r="18">
@@ -4834,13 +4860,13 @@
         <v>350</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>170.2132944444444</v>
+        <v>171.9466277777778</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>35.16666666666666</v>
+        <v>36.9</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-314.8333333333333</v>
+        <v>-313.1</v>
       </c>
     </row>
     <row r="19">
@@ -4867,13 +4893,13 @@
         <v>550</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>362.8641944444444</v>
+        <v>368.1532888888888</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>59.74000555555556</v>
+        <v>65.0291</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-490.2599944444444</v>
+        <v>-484.9709</v>
       </c>
     </row>
     <row r="20">
@@ -4900,13 +4926,13 @@
         <v>250</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>254.4277777777778</v>
+        <v>262.17</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>67.42777777777778</v>
+        <v>75.17</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>-182.5722222222222</v>
+        <v>-174.83</v>
       </c>
     </row>
     <row r="21">
@@ -4933,13 +4959,13 @@
         <v>740</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>482.4996055555555</v>
+        <v>483.1870722222222</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>115.6093333333333</v>
+        <v>116.2968</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-624.3906666666667</v>
+        <v>-623.7032</v>
       </c>
     </row>
     <row r="22">
@@ -4966,13 +4992,13 @@
         <v>450</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>185.315</v>
+        <v>186.63</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>9.315000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>-440.685</v>
+        <v>-439.37</v>
       </c>
     </row>
     <row r="23">
@@ -4999,13 +5025,13 @@
         <v>600</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>274.0416388888889</v>
+        <v>276.0371944444445</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>18.99444444444445</v>
+        <v>20.99</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>-581.0055555555556</v>
+        <v>-579.01</v>
       </c>
     </row>
     <row r="24">
@@ -5032,13 +5058,13 @@
         <v>350</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>239.4202277777778</v>
+        <v>234.3002277777778</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>79.58000000000001</v>
+        <v>74.46000000000001</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>-270.42</v>
+        <v>-275.54</v>
       </c>
     </row>
     <row r="25">
@@ -5065,13 +5091,13 @@
         <v>450</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>299.0500444444444</v>
+        <v>302.5100444444445</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>27.46</v>
+        <v>30.92</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>-422.54</v>
+        <v>-419.08</v>
       </c>
     </row>
     <row r="26">
@@ -5098,13 +5124,13 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>319.7051111111111</v>
+        <v>316.7073333333333</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>319.7051111111111</v>
+        <v>316.7073333333333</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>-30.29488888888886</v>
+        <v>-33.29266666666666</v>
       </c>
     </row>
     <row r="27">
@@ -5131,13 +5157,13 @@
         <v>1020</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>629.5563888888889</v>
+        <v>626.4730555555556</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>629.5563888888889</v>
+        <v>626.4730555555556</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>-390.4436111111111</v>
+        <v>-393.5269444444444</v>
       </c>
     </row>
     <row r="28">
@@ -5164,13 +5190,13 @@
         <v>710</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>317.0003333333333</v>
+        <v>317.9292222222222</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>9.411111111111111</v>
+        <v>10.34</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>-700.5888888888888</v>
+        <v>-699.66</v>
       </c>
     </row>
     <row r="29">
@@ -5230,13 +5256,13 @@
         <v>350</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>218.1748611111111</v>
+        <v>216.7168611111111</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>57.89700000000001</v>
+        <v>56.439</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>-292.103</v>
+        <v>-293.561</v>
       </c>
     </row>
     <row r="31">
@@ -5296,13 +5322,13 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>376.0919277777778</v>
+        <v>370.0607944444444</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>115.3910333333333</v>
+        <v>109.3599</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>-234.6089666666667</v>
+        <v>-240.6401</v>
       </c>
     </row>
     <row r="33">
@@ -5329,13 +5355,13 @@
         <v>720</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>604.3841666666667</v>
+        <v>680.2591666666667</v>
       </c>
       <c r="H33" s="17" t="n">
-        <v>604.3841666666667</v>
+        <v>680.2591666666667</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>-115.6158333333333</v>
+        <v>-39.74083333333328</v>
       </c>
     </row>
     <row r="34">
@@ -5395,13 +5421,13 @@
         <v>490</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>284.2060555555556</v>
+        <v>283.3643888888889</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>9.691666666666666</v>
+        <v>8.85</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>-480.3083333333333</v>
+        <v>-481.15</v>
       </c>
     </row>
     <row r="36">
@@ -5428,13 +5454,13 @@
         <v>350</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>227.7374444444444</v>
+        <v>222.7752222222222</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>41.13222222222223</v>
+        <v>36.17</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>-308.8677777777777</v>
+        <v>-313.83</v>
       </c>
     </row>
     <row r="37">
@@ -5461,13 +5487,13 @@
         <v>350</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>287.4982111111111</v>
+        <v>288.0682111111111</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>24.57</v>
+        <v>25.14</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>-325.43</v>
+        <v>-324.86</v>
       </c>
     </row>
     <row r="38">
@@ -5480,13 +5506,13 @@
         <v>12220</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>7838.208116666667</v>
+        <v>7915.42572777778</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>2935.077411111111</v>
+        <v>3012.295022222222</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-9284.922588888889</v>
+        <v>-9207.704977777777</v>
       </c>
     </row>
     <row r="40">
@@ -5567,13 +5593,13 @@
         <v>250</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>432.5140277777778</v>
+        <v>424.9305555555555</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>221.2259722222222</v>
+        <v>213.6425</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>-28.77402777777777</v>
+        <v>-36.35749999999999</v>
       </c>
     </row>
     <row r="43">
@@ -5600,13 +5626,13 @@
         <v>350</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>707.1596944444445</v>
+        <v>696.9247611111111</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>463.9165333333334</v>
+        <v>453.6816000000001</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>113.9165333333334</v>
+        <v>103.6816000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5633,13 +5659,13 @@
         <v>500</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>569.1320833333333</v>
+        <v>573.9643055555555</v>
       </c>
       <c r="H44" s="17" t="n">
-        <v>312.0402777777778</v>
+        <v>316.8725</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>-187.9597222222222</v>
+        <v>-183.1275</v>
       </c>
     </row>
     <row r="45">
@@ -5666,13 +5692,13 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>380.3112361111111</v>
+        <v>399.5910277777778</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>193.1539583333333</v>
+        <v>212.43375</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>-156.8460416666667</v>
+        <v>-137.56625</v>
       </c>
     </row>
     <row r="46">
@@ -5699,13 +5725,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>280.9231194444445</v>
+        <v>304.8429638888889</v>
       </c>
       <c r="H46" s="17" t="n">
-        <v>178.3998055555556</v>
+        <v>202.31965</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>178.3998055555556</v>
+        <v>202.31965</v>
       </c>
     </row>
     <row r="47">
@@ -5732,13 +5758,13 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>548.7838666666667</v>
+        <v>549.7144888888889</v>
       </c>
       <c r="H47" s="17" t="n">
-        <v>307.1632777777778</v>
+        <v>308.0939</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>-42.83672222222219</v>
+        <v>-41.90609999999998</v>
       </c>
     </row>
     <row r="48">
@@ -5765,13 +5791,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>380.2138888888889</v>
+        <v>385.385</v>
       </c>
       <c r="H48" s="17" t="n">
-        <v>223.2138888888889</v>
+        <v>228.385</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>223.2138888888889</v>
+        <v>228.385</v>
       </c>
     </row>
     <row r="49">
@@ -5798,13 +5824,13 @@
         <v>460</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>780.3611055555556</v>
+        <v>812.4810166666667</v>
       </c>
       <c r="H49" s="17" t="n">
-        <v>511.8998888888889</v>
+        <v>544.0198</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>51.89988888888888</v>
+        <v>84.01980000000003</v>
       </c>
     </row>
     <row r="50">
@@ -5831,13 +5857,13 @@
         <v>250</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>366.29175</v>
+        <v>382.5835</v>
       </c>
       <c r="H50" s="17" t="n">
-        <v>244.29175</v>
+        <v>260.5835</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-5.708249999999992</v>
+        <v>10.58350000000002</v>
       </c>
     </row>
     <row r="51">
@@ -5864,13 +5890,13 @@
         <v>350</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>427.2580416666667</v>
+        <v>426.7974305555556</v>
       </c>
       <c r="H51" s="17" t="n">
-        <v>239.8878611111111</v>
+        <v>239.42725</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-110.1121388888889</v>
+        <v>-110.57275</v>
       </c>
     </row>
     <row r="52">
@@ -5897,13 +5923,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>373.6080277777778</v>
+        <v>347.9304277777778</v>
       </c>
       <c r="H52" s="17" t="n">
-        <v>241.6284</v>
+        <v>215.9508</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>241.6284</v>
+        <v>215.9508</v>
       </c>
     </row>
     <row r="53">
@@ -5930,13 +5956,13 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>450.6682222222222</v>
+        <v>488.1986722222222</v>
       </c>
       <c r="H53" s="17" t="n">
-        <v>229.53045</v>
+        <v>267.0609</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-120.46955</v>
+        <v>-82.9391</v>
       </c>
     </row>
     <row r="54">
@@ -5963,13 +5989,13 @@
         <v>350</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>429.7971111111111</v>
+        <v>410.1633333333333</v>
       </c>
       <c r="H54" s="17" t="n">
-        <v>429.7971111111111</v>
+        <v>410.1633333333333</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>79.79711111111112</v>
+        <v>60.1633333333333</v>
       </c>
     </row>
     <row r="55">
@@ -5996,13 +6022,13 @@
         <v>680</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>983.1897638888889</v>
+        <v>974.8212777777778</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>983.1897638888889</v>
+        <v>974.8212777777778</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>303.1897638888889</v>
+        <v>294.8212777777778</v>
       </c>
     </row>
     <row r="56">
@@ -6029,13 +6055,13 @@
         <v>470</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>507.1518333333333</v>
+        <v>546.4376111111111</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>255.3572222222222</v>
+        <v>294.643</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>-214.6427777777778</v>
+        <v>-175.357</v>
       </c>
     </row>
     <row r="57">
@@ -6062,13 +6088,13 @@
         <v>350</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>338.0270277777778</v>
+        <v>331.5011388888889</v>
       </c>
       <c r="H57" s="17" t="n">
-        <v>124.1593888888889</v>
+        <v>117.6335</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>-225.8406111111111</v>
+        <v>-232.3665</v>
       </c>
     </row>
     <row r="58">
@@ -6095,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>284.3704861111111</v>
+        <v>291.5650833333333</v>
       </c>
       <c r="H58" s="17" t="n">
-        <v>148.4486527777778</v>
+        <v>155.64325</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>148.4486527777778</v>
+        <v>155.64325</v>
       </c>
     </row>
     <row r="59">
@@ -6128,13 +6154,13 @@
         <v>450</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>636.2990916666666</v>
+        <v>650.4357166666666</v>
       </c>
       <c r="H59" s="17" t="n">
-        <v>636.2990916666666</v>
+        <v>650.4357166666666</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>186.2990916666666</v>
+        <v>200.4357166666666</v>
       </c>
     </row>
     <row r="60">
@@ -6161,13 +6187,13 @@
         <v>250</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>430.4968027777778</v>
+        <v>422.8678361111112</v>
       </c>
       <c r="H60" s="17" t="n">
-        <v>193.7986166666667</v>
+        <v>186.16965</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>-56.20138333333333</v>
+        <v>-63.83034999999998</v>
       </c>
     </row>
     <row r="61">
@@ -6194,13 +6220,13 @@
         <v>500</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>857.7432166666665</v>
+        <v>882.6343305555555</v>
       </c>
       <c r="H61" s="17" t="n">
-        <v>857.7432166666665</v>
+        <v>882.6343305555555</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>357.7432166666665</v>
+        <v>382.6343305555555</v>
       </c>
     </row>
     <row r="62">
@@ -6227,13 +6253,13 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>382.6976666666666</v>
+        <v>377.1336666666667</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>222.545</v>
+        <v>216.981</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>-27.45499999999998</v>
+        <v>-33.01900000000001</v>
       </c>
     </row>
     <row r="63">
@@ -6260,13 +6286,13 @@
         <v>350</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>392.8129555555555</v>
+        <v>389.3715777777778</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>166.4551777777778</v>
+        <v>163.0138</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v>-183.5448222222222</v>
+        <v>-186.9862</v>
       </c>
     </row>
     <row r="64">
@@ -6293,13 +6319,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>394.7727777777778</v>
+        <v>373.3598888888889</v>
       </c>
       <c r="H64" s="17" t="n">
-        <v>256.5548888888889</v>
+        <v>235.142</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>256.5548888888889</v>
+        <v>235.142</v>
       </c>
     </row>
     <row r="65">
@@ -6326,13 +6352,13 @@
         <v>250</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>403.2946555555556</v>
+        <v>419.2011</v>
       </c>
       <c r="H65" s="17" t="n">
-        <v>185.6330555555556</v>
+        <v>201.5395</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v>-64.36694444444444</v>
+        <v>-48.4605</v>
       </c>
     </row>
     <row r="66">
@@ -6345,13 +6371,13 @@
         <v>7110</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>11737.87845277778</v>
+        <v>11862.83671111111</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>7826.333250000001</v>
+        <v>7951.291508333333</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>716.3332500000015</v>
+        <v>841.2915083333328</v>
       </c>
     </row>
     <row r="69">
@@ -6364,14 +6390,14 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $2,935 (less, because few agents clear the $45k NB gate today).</t>
+          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $3,012 (less, because few agents clear the $45k NB gate today).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,235 (92% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,740 (96% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6472,11 +6498,6 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>REN pays</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
           <t>Plain English</t>
         </is>
       </c>
@@ -6499,11 +6520,6 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>$4</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
           <t>Low-premium policies earn the base. Smaller bonus.</t>
         </is>
       </c>
@@ -6526,11 +6542,6 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>$6</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
           <t>Standard FL policies. The bulk of the book.</t>
         </is>
       </c>
@@ -6553,11 +6564,6 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$8</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
           <t>Higher premium - more commission for the agency, more bonus for the agent.</t>
         </is>
       </c>
@@ -6580,11 +6586,6 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>$10</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
           <t>Strong premium business.</t>
         </is>
       </c>
@@ -6607,477 +6608,485 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$10</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
           <t>Commercial / high-end auto. Upside on big premium.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2. PER-POLICY COLLECTED INCENTIVE (only on policies with premium &gt; $1,200)</t>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Renewals (REN)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>See Section 3</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>See Section 3</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Renewals are paid via the RETENTION BONUS only - not per-policy. See Section 3 below.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2. PER-POLICY COLLECTED INCENTIVE (only on NB and RWR policies with premium &gt; $1,200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Collected % of premium</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Extra per policy</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Below 15%</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>$0 (no incentive)</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Premium barely collected. No incentive.</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>$1,500 policy, 10% down -&gt; $0 incentive</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>15% to 19%</t>
+          <t>Below 15%</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>+$1 per policy</t>
+          <t>$0 (no incentive)</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Minimum down. Small bump.</t>
+          <t>Premium barely collected. No incentive.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>$1,500 policy, 17% down -&gt; +$1</t>
+          <t>$1,500 policy, 10% down -&gt; $0 incentive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>20% to 24%</t>
+          <t>15% to 19%</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>+$2 per policy</t>
+          <t>+$1 per policy</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Standard down. Standard bump.</t>
+          <t>Minimum down. Small bump.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$1,500 policy, 22% down -&gt; +$2</t>
+          <t>$1,500 policy, 17% down -&gt; +$1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>25% to 99%</t>
+          <t>20% to 24%</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>+$5 per policy</t>
+          <t>+$2 per policy</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>High collection. Big bump.</t>
+          <t>Standard down. Standard bump.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>$1,500 policy, 30% down -&gt; +$5</t>
+          <t>$1,500 policy, 22% down -&gt; +$2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>100% PIF</t>
+          <t>25% to 99%</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>+$8 per policy</t>
+          <t>+$5 per policy</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+          <t>High collection. Big bump.</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>$1,500 policy PIF -&gt; +$8</t>
+          <t>$1,500 policy, 30% down -&gt; +$5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>100% PIF</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>+$8 per policy</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Paid in full. Zero chargeback risk. Top incentive.</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>$1,500 policy PIF -&gt; +$8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
           <t>Policy with premium &lt;= $1,200</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>$0 incentive</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Low-premium policies do not earn the incentive.</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>$800 policy at 50% -&gt; base only</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>3. BOOK RETENTION BONUS (separate, not gated by monthly minimums)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Math</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>REN written premium x 0.5%</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Bonus = $5 per $1,000 of REN premium the agent retained this month.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Scales with book size</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>A $50k REN month -&gt; $250 bonus. A $25k REN month -&gt; $125 bonus.</t>
+          <t>REN written premium x 1%</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Bigger book = bigger bonus. Agent with 40 renewals at $50k earns more than agent with 20 renewals at $25k, even at the same retention rate.</t>
+          <t>Bonus = $10 per $1,000 of REN premium the agent retained this month. This is the ONLY renewal pay - no per-policy REN base or collected incentive.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Why per-dollar</t>
+          <t>Scales with book SIZE</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Rewards both the renewal RATE and the BOOK SIZE</t>
+          <t>A $50k REN month -&gt; $500 bonus. A $25k REN month -&gt; $250 bonus.</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Agent who retains $50k of book contributes more commission to the agency. Bonus reflects that.</t>
+          <t>Bigger book = bigger bonus. Agent with 40 renewals at $50k earns more than agent with 20 renewals at $25k.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Retention Rate threshold</t>
+          <t>Scales with PREMIUM</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>&gt;= 30% to qualify</t>
+          <t>A $2,000 renewal contributes $20 to the bonus. A $1,000 renewal contributes $10.</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Agent must retain at least 30% of their book to earn the retention bonus AND the per-policy REN bonus.</t>
+          <t>Higher-premium renewals are worth more to the agency, so they earn more bonus.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
+          <t>Scales with RETENTION rate</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>More renewed = bigger REN premium = bigger bonus</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Both rate and absolute volume drive the bonus through the same formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Retention rate threshold</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>&gt;= 30% to qualify</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Agent must retain at least 30% of their book to earn the retention bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
           <t>Minimum gate</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>NOT gated by NB minimum</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Retention bonus pays regardless of monthly NB volume - it rewards keeping the book intact over time.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>4. RULES THAT APPLY ON TOP</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>How it works</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - NB</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>$45,000 written premium</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Monthly Minimum - REN</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Retain &gt;= 30% of agent's book</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>REN base + REN collected paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Monthly Minimum - RWR</t>
+          <t>Monthly Minimum - NB</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>NB gate met (or both)</t>
+          <t>$45,000 written premium</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
+          <t>NB base + NB collected paid ONLY if NB premium clears this gate this month.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Retention Bonus exception</t>
+          <t>Monthly Minimum - REN</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Always paid</t>
+          <t>Retain &gt;= 30% of agent's book</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
+          <t>Retention bonus paid ONLY if the agent retained at least 30% of their assigned book this month.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Monthly Minimum - RWR</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>3 months (90 days)</t>
+          <t>NB gate met (or both)</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+          <t>RWR base + RWR collected paid ONLY if NB gate met. Meeting both NB and REN also works.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Excel Tracker</t>
+          <t>Retention Bonus exception</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Required for every policy</t>
+          <t>Always paid</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+          <t>Retention bonus is paid regardless of monthly minimums - it tracks long-term book persistency.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
+          <t>Chargeback</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>3 months (90 days)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>100% of the paid bonus on a policy is REVERSED if the policy cancels/rewrites within 90 days of effective date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Excel Tracker</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Required for every policy</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Agent must enter policy info, down payment, and premium in the manual tracker. No entry = no bonus on that policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
           <t>Renewal Book of Business</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Assigned per agent</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Each agent has an assigned renewal book. Newer agents who do not have their own renewals get a book reassigned from former employees. The agent is responsible for renewing that book.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>5. WORKED EXAMPLE - Dialinerys Dieguez, March 2026</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr"/>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Volumes</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
@@ -7087,7 +7096,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+          <t>NB 38 ($52,435 written, $10,547 collected = 20.1%, avg policy $1,380)</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
@@ -7095,165 +7104,157 @@
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>NB base (tier)</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>38 policies in tier "$1,200-$1,799" x $7</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>$266</t>
-        </is>
-      </c>
+          <t>RWR 69 ($96,228 written, $19,700 collected = 20.5%, avg policy $1,395)</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>NB collected incentive</t>
+          <t>Volumes</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$2/policy</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>$33</t>
-        </is>
-      </c>
+          <t>REN 7 ($5,962 written, $3,080 collected = 51.7%, avg policy $852)</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>REN base (tier)</t>
+          <t>NB base (tier)</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>7 policies in tier "Under $1,200" x $4</t>
+          <t>38 policies in tier "$1,200-$1,799" x $7</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>$28</t>
+          <t>$266</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>REN collected incentive</t>
+          <t>NB collected incentive</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>~14% &gt;$1,200, collected 52% -&gt; +$5/policy</t>
+          <t>~43% of policies &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>$5</t>
+          <t>$33</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>RWR base (tier)</t>
+          <t>REN base / collected</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>69 policies in tier "$1,200-$1,799" x $3</t>
+          <t>No per-policy REN pay - renewals are paid via retention bonus only</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>$207</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>RWR collected incentive</t>
+          <t>RWR base (tier)</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>~44% &gt;$1,200, collected 20% -&gt; +$2/policy</t>
+          <t>69 policies in tier "$1,200-$1,799" x $3</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>$61</t>
+          <t>$207</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Retention bonus</t>
+          <t>RWR collected incentive</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>REN $5,962 x 0.5% = $29.81</t>
+          <t>~44% &gt;$1,200, collected 20% -&gt; +$2/policy</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>$30</t>
+          <t>$61</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Subtotal target</t>
+          <t>Retention bonus (renewal pay)</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>(everything before gates)</t>
+          <t>REN $5,962 x 1% = $59.62</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>$630</t>
+          <t>$60</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>NB gate ($45,000)</t>
+          <t>Subtotal target</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>NB written $52,435 vs $45,000</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>(everything before gates)</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>$626</t>
         </is>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>REN gate (&gt;= 30% retention)</t>
+          <t>NB gate ($45,000)</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Assumed retention 75% vs 30%</t>
+          <t>NB written $52,435 vs $45,000</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -7265,46 +7266,63 @@
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
+          <t>REN gate (&gt;= 30% retention)</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Assumed retention 75% vs 30%</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
           <t>RWR gate (both)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Both NB and REN gates passed?</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>FINAL PAID</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B56" s="24" t="inlineStr">
         <is>
           <t>Pay only the lines whose gates passed + retention bonus</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>$629.56</t>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>$626.47</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7817,7 +7835,7 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>76.47499999999999</v>
+        <v>76.05</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>78.20999999999999</v>
@@ -7859,7 +7877,7 @@
         </is>
       </c>
       <c r="H31" s="16" t="n">
-        <v>67.42777777777778</v>
+        <v>75.17</v>
       </c>
       <c r="I31" s="16" t="n">
         <v>60.83</v>
@@ -7901,7 +7919,7 @@
         </is>
       </c>
       <c r="H32" s="16" t="n">
-        <v>319.7051111111111</v>
+        <v>316.7073333333333</v>
       </c>
       <c r="I32" s="16" t="n">
         <v>475.825</v>
@@ -7943,7 +7961,7 @@
         </is>
       </c>
       <c r="H33" s="16" t="n">
-        <v>115.3910333333333</v>
+        <v>109.3599</v>
       </c>
       <c r="I33" s="16" t="n">
         <v>118.105</v>
@@ -7985,7 +8003,7 @@
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>123.1258777777778</v>
+        <v>125.3047</v>
       </c>
       <c r="I34" s="16" t="n">
         <v>99.935</v>
@@ -8027,7 +8045,7 @@
         </is>
       </c>
       <c r="H35" s="16" t="n">
-        <v>115.6093333333333</v>
+        <v>116.2968</v>
       </c>
       <c r="I35" s="16" t="n">
         <v>78.20999999999999</v>
@@ -8069,7 +8087,7 @@
         </is>
       </c>
       <c r="H36" s="16" t="n">
-        <v>629.5563888888889</v>
+        <v>626.4730555555556</v>
       </c>
       <c r="I36" s="16" t="n">
         <v>765.74</v>
@@ -8111,7 +8129,7 @@
         </is>
       </c>
       <c r="H37" s="16" t="n">
-        <v>604.3841666666667</v>
+        <v>680.2591666666667</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>594.11</v>
@@ -8195,7 +8213,7 @@
         </is>
       </c>
       <c r="H39" s="16" t="n">
-        <v>9.315000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="I39" s="16" t="n">
         <v>7.9</v>
@@ -8237,7 +8255,7 @@
         </is>
       </c>
       <c r="H40" s="16" t="n">
-        <v>9.411111111111111</v>
+        <v>10.34</v>
       </c>
       <c r="I40" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8321,7 +8339,7 @@
         </is>
       </c>
       <c r="H42" s="16" t="n">
-        <v>14.28213888888889</v>
+        <v>14.6435</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8363,7 +8381,7 @@
         </is>
       </c>
       <c r="H43" s="16" t="n">
-        <v>18.99444444444445</v>
+        <v>20.99</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>17.38</v>
@@ -8447,7 +8465,7 @@
         </is>
       </c>
       <c r="H45" s="16" t="n">
-        <v>9.691666666666666</v>
+        <v>8.85</v>
       </c>
       <c r="I45" s="16" t="n">
         <v>9.875</v>
@@ -8489,7 +8507,7 @@
         </is>
       </c>
       <c r="H46" s="16" t="n">
-        <v>35.16666666666666</v>
+        <v>36.9</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>34.76000000000001</v>
@@ -8531,7 +8549,7 @@
         </is>
       </c>
       <c r="H47" s="16" t="n">
-        <v>79.58000000000001</v>
+        <v>74.46000000000001</v>
       </c>
       <c r="I47" s="16" t="n">
         <v>45.425</v>
@@ -8573,7 +8591,7 @@
         </is>
       </c>
       <c r="H48" s="16" t="n">
-        <v>57.89700000000001</v>
+        <v>56.439</v>
       </c>
       <c r="I48" s="16" t="n">
         <v>54.50999999999999</v>
@@ -8615,7 +8633,7 @@
         </is>
       </c>
       <c r="H49" s="16" t="n">
-        <v>41.13222222222223</v>
+        <v>36.17</v>
       </c>
       <c r="I49" s="16" t="n">
         <v>28.44</v>
@@ -8657,7 +8675,7 @@
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>59.74000555555556</v>
+        <v>65.0291</v>
       </c>
       <c r="I50" s="16" t="n">
         <v>52.14</v>
@@ -8699,7 +8717,7 @@
         </is>
       </c>
       <c r="H51" s="16" t="n">
-        <v>27.46</v>
+        <v>30.92</v>
       </c>
       <c r="I51" s="16" t="n">
         <v>15.8</v>
@@ -8783,7 +8801,7 @@
         </is>
       </c>
       <c r="H53" s="16" t="n">
-        <v>24.57</v>
+        <v>25.14</v>
       </c>
       <c r="I53" s="16" t="n">
         <v>15.8</v>
@@ -8884,7 +8902,7 @@
         </is>
       </c>
       <c r="H58" s="16" t="n">
-        <v>221.2259722222222</v>
+        <v>213.6425</v>
       </c>
       <c r="I58" s="16" t="n">
         <v>147.73</v>
@@ -8926,7 +8944,7 @@
         </is>
       </c>
       <c r="H59" s="16" t="n">
-        <v>223.2138888888889</v>
+        <v>228.385</v>
       </c>
       <c r="I59" s="16" t="n">
         <v>147.73</v>
@@ -8968,7 +8986,7 @@
         </is>
       </c>
       <c r="H60" s="16" t="n">
-        <v>429.7971111111111</v>
+        <v>410.1633333333333</v>
       </c>
       <c r="I60" s="16" t="n">
         <v>530.905</v>
@@ -9010,7 +9028,7 @@
         </is>
       </c>
       <c r="H61" s="16" t="n">
-        <v>193.7986166666667</v>
+        <v>186.16965</v>
       </c>
       <c r="I61" s="16" t="n">
         <v>190.785</v>
@@ -9052,7 +9070,7 @@
         </is>
       </c>
       <c r="H62" s="16" t="n">
-        <v>463.9165333333334</v>
+        <v>453.6816000000001</v>
       </c>
       <c r="I62" s="16" t="n">
         <v>304.15</v>
@@ -9094,7 +9112,7 @@
         </is>
       </c>
       <c r="H63" s="16" t="n">
-        <v>511.8998888888889</v>
+        <v>544.0198</v>
       </c>
       <c r="I63" s="16" t="n">
         <v>321.53</v>
@@ -9136,7 +9154,7 @@
         </is>
       </c>
       <c r="H64" s="16" t="n">
-        <v>983.1897638888889</v>
+        <v>974.8212777777778</v>
       </c>
       <c r="I64" s="16" t="n">
         <v>980.8700000000001</v>
@@ -9178,7 +9196,7 @@
         </is>
       </c>
       <c r="H65" s="16" t="n">
-        <v>857.7432166666665</v>
+        <v>882.6343305555555</v>
       </c>
       <c r="I65" s="16" t="n">
         <v>734.6900000000001</v>
@@ -9220,7 +9238,7 @@
         </is>
       </c>
       <c r="H66" s="16" t="n">
-        <v>312.0402777777778</v>
+        <v>316.8725</v>
       </c>
       <c r="I66" s="16" t="n">
         <v>208.56</v>
@@ -9262,7 +9280,7 @@
         </is>
       </c>
       <c r="H67" s="16" t="n">
-        <v>244.29175</v>
+        <v>260.5835</v>
       </c>
       <c r="I67" s="16" t="n">
         <v>150.1</v>
@@ -9304,7 +9322,7 @@
         </is>
       </c>
       <c r="H68" s="16" t="n">
-        <v>255.3572222222222</v>
+        <v>294.643</v>
       </c>
       <c r="I68" s="16" t="n">
         <v>217.25</v>
@@ -9346,7 +9364,7 @@
         </is>
       </c>
       <c r="H69" s="16" t="n">
-        <v>222.545</v>
+        <v>216.981</v>
       </c>
       <c r="I69" s="16" t="n">
         <v>156.42</v>
@@ -9388,7 +9406,7 @@
         </is>
       </c>
       <c r="H70" s="16" t="n">
-        <v>193.1539583333333</v>
+        <v>212.43375</v>
       </c>
       <c r="I70" s="16" t="n">
         <v>165.11</v>
@@ -9430,7 +9448,7 @@
         </is>
       </c>
       <c r="H71" s="16" t="n">
-        <v>239.8878611111111</v>
+        <v>239.42725</v>
       </c>
       <c r="I71" s="16" t="n">
         <v>208.955</v>
@@ -9472,7 +9490,7 @@
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>124.1593888888889</v>
+        <v>117.6335</v>
       </c>
       <c r="I72" s="16" t="n">
         <v>127.19</v>
@@ -9514,7 +9532,7 @@
         </is>
       </c>
       <c r="H73" s="16" t="n">
-        <v>166.4551777777778</v>
+        <v>163.0138</v>
       </c>
       <c r="I73" s="16" t="n">
         <v>154.445</v>
@@ -9556,7 +9574,7 @@
         </is>
       </c>
       <c r="H74" s="16" t="n">
-        <v>178.3998055555556</v>
+        <v>202.31965</v>
       </c>
       <c r="I74" s="16" t="n">
         <v>156.42</v>
@@ -9598,7 +9616,7 @@
         </is>
       </c>
       <c r="H75" s="16" t="n">
-        <v>241.6284</v>
+        <v>215.9508</v>
       </c>
       <c r="I75" s="16" t="n">
         <v>154.445</v>
@@ -9640,7 +9658,7 @@
         </is>
       </c>
       <c r="H76" s="16" t="n">
-        <v>148.4486527777778</v>
+        <v>155.64325</v>
       </c>
       <c r="I76" s="16" t="n">
         <v>139.04</v>
@@ -9682,7 +9700,7 @@
         </is>
       </c>
       <c r="H77" s="16" t="n">
-        <v>256.5548888888889</v>
+        <v>235.142</v>
       </c>
       <c r="I77" s="16" t="n">
         <v>154.445</v>
@@ -9724,7 +9742,7 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>307.1632777777778</v>
+        <v>308.0939</v>
       </c>
       <c r="I78" s="16" t="n">
         <v>208.56</v>
@@ -9766,7 +9784,7 @@
         </is>
       </c>
       <c r="H79" s="16" t="n">
-        <v>229.53045</v>
+        <v>267.0609</v>
       </c>
       <c r="I79" s="16" t="n">
         <v>126.4</v>
@@ -9808,7 +9826,7 @@
         </is>
       </c>
       <c r="H80" s="16" t="n">
-        <v>636.2990916666666</v>
+        <v>650.4357166666666</v>
       </c>
       <c r="I80" s="16" t="n">
         <v>657.3600000000001</v>
@@ -9850,7 +9868,7 @@
         </is>
       </c>
       <c r="H81" s="16" t="n">
-        <v>185.6330555555556</v>
+        <v>201.5395</v>
       </c>
       <c r="I81" s="16" t="n">
         <v>112.97</v>
@@ -10963,25 +10981,25 @@
         <v>175</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>38.45</v>
+        <v>0</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>70.24277777777777</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>38.025</v>
+        <v>76.05</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>321.7177777777778</v>
+        <v>321.2927777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>76.47499999999999</v>
+        <v>76.05</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -10992,7 +11010,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-273.525</v>
+        <v>-273.95</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>350</v>
@@ -11014,25 +11032,25 @@
         <v>130</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1.842777777777778</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>29.84277777777778</v>
+        <v>0</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>57</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>37.585</v>
+        <v>75.17</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>254.4277777777778</v>
+        <v>262.17</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>67.42777777777778</v>
+        <v>75.17</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -11043,7 +11061,7 @@
         <v>544.3810526</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>-182.5722222222222</v>
+        <v>-174.83</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>250</v>
@@ -11065,25 +11083,25 @@
         <v>210</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2.502777777777778</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>22.50277777777778</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>67.69733333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>19.505</v>
+        <v>39.01</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>319.7051111111111</v>
+        <v>316.7073333333333</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>319.7051111111111</v>
+        <v>316.7073333333333</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -11094,7 +11112,7 @@
         <v>829.8586758</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-30.29488888888886</v>
+        <v>-33.29266666666666</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -11116,25 +11134,25 @@
         <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8.711083333333335</v>
+        <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>60.71108333333333</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>47.67208333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>54.67995</v>
+        <v>109.3599</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>376.0919277777778</v>
+        <v>370.0607944444444</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>115.3910333333333</v>
+        <v>109.3599</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -11145,7 +11163,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-234.6089666666667</v>
+        <v>-240.6401</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>350</v>
@@ -11165,16 +11183,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>1271.942594444444</v>
+        <v>1270.230905555555</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>578.9989222222223</v>
+        <v>577.2872333333333</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>-721.0010777777777</v>
+        <v>-722.7127666666667</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>1300</v>
@@ -11928,25 +11946,25 @@
         <v>161</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>16.47352777777778</v>
+        <v>0</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>60.47352777777778</v>
+        <v>0</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>164.4863222222222</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>62.65235</v>
+        <v>125.3047</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>448.6122</v>
+        <v>450.7910222222222</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>123.1258777777778</v>
+        <v>125.3047</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -11957,7 +11975,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-536.8741222222222</v>
+        <v>-534.6953</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>660</v>
@@ -11979,25 +11997,25 @@
         <v>170.0321611111111</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3.460933333333334</v>
+        <v>0</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>57.46093333333334</v>
+        <v>0</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>196.8581111111111</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>58.1484</v>
+        <v>116.2968</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>482.4996055555555</v>
+        <v>483.1870722222222</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>115.6093333333333</v>
+        <v>116.2968</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -12008,7 +12026,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-624.3906666666667</v>
+        <v>-623.7032</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>740</v>
@@ -12030,25 +12048,25 @@
         <v>298.9276666666667</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4.895833333333334</v>
+        <v>0</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>32.89583333333334</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>267.9203888888889</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>29.8125</v>
+        <v>59.625</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>629.5563888888889</v>
+        <v>626.4730555555556</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>629.5563888888889</v>
+        <v>626.4730555555556</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -12059,7 +12077,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>-390.4436111111111</v>
+        <v>-393.5269444444444</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>1020</v>
@@ -12081,25 +12099,25 @@
         <v>247.6051944444444</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>236.9039722222222</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>97.875</v>
+        <v>195.75</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>604.3841666666667</v>
+        <v>680.2591666666667</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>604.3841666666667</v>
+        <v>680.2591666666667</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -12110,7 +12128,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>-115.6158333333333</v>
+        <v>-39.74083333333328</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>720</v>
@@ -12130,16 +12148,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>2165.052361111111</v>
+        <v>2240.710316666667</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1472.675766666667</v>
+        <v>1548.333722222222</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>-1667.324233333333</v>
+        <v>-1591.666277777778</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>3140</v>
@@ -12944,25 +12962,25 @@
         <v>65</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H62" s="11" t="n">
         <v>111</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>5.315</v>
+        <v>10.63</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>185.315</v>
+        <v>186.63</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>9.315000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -12973,7 +12991,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>-440.685</v>
+        <v>-439.37</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>450</v>
@@ -12995,25 +13013,25 @@
         <v>196</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.2411111111111111</v>
+        <v>0</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>4.241111111111111</v>
+        <v>0</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>111.5892222222222</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>5.17</v>
+        <v>10.34</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>317.0003333333333</v>
+        <v>317.9292222222222</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>9.411111111111111</v>
+        <v>10.34</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -13024,7 +13042,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-700.5888888888888</v>
+        <v>-699.66</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>710</v>
@@ -13095,16 +13113,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1043.218333333333</v>
+        <v>1045.462222222222</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>18.72611111111111</v>
+        <v>20.97</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-2351.273888888889</v>
+        <v>-2349.03</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>2370</v>
@@ -13858,25 +13876,25 @@
         <v>142.5139166666667</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.9603888888888887</v>
+        <v>0</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>6.960388888888889</v>
+        <v>0</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>90.62005555555555</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>7.32175</v>
+        <v>14.6435</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>247.4161111111111</v>
+        <v>247.7774722222222</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>14.28213888888889</v>
+        <v>14.6435</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -13887,7 +13905,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-475.7178611111111</v>
+        <v>-475.3565</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>490</v>
@@ -13909,25 +13927,25 @@
         <v>119.6931666666667</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>0.4994444444444445</v>
+        <v>0</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>8.499444444444444</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>135.3540277777778</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>10.495</v>
+        <v>20.99</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>274.0416388888889</v>
+        <v>276.0371944444445</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>18.99444444444445</v>
+        <v>20.99</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -13938,7 +13956,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-581.0055555555556</v>
+        <v>-579.01</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>600</v>
@@ -14011,25 +14029,25 @@
         <v>178.5345</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1.266666666666667</v>
+        <v>0</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>5.266666666666667</v>
+        <v>0</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>95.97988888888888</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>4.425</v>
+        <v>8.85</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>284.2060555555556</v>
+        <v>283.3643888888889</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>9.691666666666666</v>
+        <v>8.85</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -14040,7 +14058,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-480.3083333333333</v>
+        <v>-481.15</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>490</v>
@@ -14060,16 +14078,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1056.874083333333</v>
+        <v>1058.389333333333</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>42.96825</v>
+        <v>44.4835</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-2027.03175</v>
+        <v>-2025.5165</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>2070</v>
@@ -14823,25 +14841,25 @@
         <v>70</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.7166666666666667</v>
+        <v>0</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>16.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>65.04662777777777</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>18.45</v>
+        <v>36.9</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>170.2132944444444</v>
+        <v>171.9466277777778</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>35.16666666666666</v>
+        <v>36.9</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -14852,7 +14870,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>-314.8333333333333</v>
+        <v>-313.1</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>350</v>
@@ -14874,25 +14892,25 @@
         <v>104.1190277777778</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>12.35</v>
+        <v>0</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>42.35</v>
+        <v>0</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>55.7212</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>37.23</v>
+        <v>74.46000000000001</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>239.4202277777778</v>
+        <v>234.3002277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>79.58000000000001</v>
+        <v>74.46000000000001</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -14903,7 +14921,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>-270.42</v>
+        <v>-275.54</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>350</v>
@@ -14925,25 +14943,25 @@
         <v>112.8991388888889</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>5.6775</v>
+        <v>0</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>29.6775</v>
+        <v>0</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>47.37872222222222</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>28.2195</v>
+        <v>56.439</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>218.1748611111111</v>
+        <v>216.7168611111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>57.89700000000001</v>
+        <v>56.439</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -14954,7 +14972,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>-292.103</v>
+        <v>-293.561</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>350</v>
@@ -14976,25 +14994,25 @@
         <v>87.16388888888889</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>5.047222222222222</v>
+        <v>0</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>23.04722222222222</v>
+        <v>0</v>
       </c>
       <c r="H112" s="11" t="n">
         <v>99.44133333333333</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>18.085</v>
+        <v>36.17</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>227.7374444444444</v>
+        <v>222.7752222222222</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>41.13222222222223</v>
+        <v>36.17</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -15005,7 +15023,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>-308.8677777777777</v>
+        <v>-313.83</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>350</v>
@@ -15025,16 +15043,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>855.5458277777777</v>
+        <v>845.7389388888889</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>213.7758888888889</v>
+        <v>203.969</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>-1186.224111111111</v>
+        <v>-1196.031</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>1400</v>
@@ -15788,25 +15806,25 @@
         <v>177.4503222222222</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>3.225455555555556</v>
+        <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>27.22545555555556</v>
+        <v>0</v>
       </c>
       <c r="H133" s="11" t="n">
         <v>125.6738666666667</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>32.51455</v>
+        <v>65.0291</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>362.8641944444444</v>
+        <v>368.1532888888888</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>59.74000555555556</v>
+        <v>65.0291</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -15817,7 +15835,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-490.2599944444444</v>
+        <v>-484.9709</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>550</v>
@@ -15839,25 +15857,25 @@
         <v>168.0188333333333</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H134" s="11" t="n">
         <v>103.5712111111111</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>15.46</v>
+        <v>30.92</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>299.0500444444444</v>
+        <v>302.5100444444445</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>27.46</v>
+        <v>30.92</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -15868,7 +15886,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-422.54</v>
+        <v>-419.08</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>450</v>
@@ -15941,25 +15959,25 @@
         <v>172.3949888888889</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H136" s="11" t="n">
         <v>90.53322222222222</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>12.57</v>
+        <v>25.14</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>287.4982111111111</v>
+        <v>288.0682111111111</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>24.57</v>
+        <v>25.14</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -15970,7 +15988,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-325.43</v>
+        <v>-324.86</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>350</v>
@@ -15990,16 +16008,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>1445.574916666666</v>
+        <v>1454.894011111111</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>607.9324722222223</v>
+        <v>617.2515666666667</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>-1332.067527777778</v>
+        <v>-1322.748433333333</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1940</v>
@@ -16823,25 +16841,25 @@
         <v>175</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>12.40472222222222</v>
+        <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>114.4047222222222</v>
+        <v>0</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>36.28805555555556</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>106.82125</v>
+        <v>213.6425</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>432.5140277777778</v>
+        <v>424.9305555555555</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>221.2259722222222</v>
+        <v>213.6425</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -16852,7 +16870,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-28.77402777777777</v>
+        <v>-36.35749999999999</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -16874,25 +16892,25 @@
         <v>130</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7.02138888888889</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>109.0213888888889</v>
+        <v>0</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>27</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>114.1925</v>
+        <v>228.385</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>380.2138888888889</v>
+        <v>385.385</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>223.2138888888889</v>
+        <v>228.385</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -16903,7 +16921,7 @@
         <v>544.3810526000001</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>223.2138888888889</v>
+        <v>228.385</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -16925,25 +16943,25 @@
         <v>210</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>24.20777777777777</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>102.2077777777778</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>35.01533333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>82.574</v>
+        <v>165.148</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>429.7971111111111</v>
+        <v>410.1633333333333</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>429.7971111111111</v>
+        <v>410.1633333333333</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -16954,7 +16972,7 @@
         <v>829.8586758000001</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>79.79711111111112</v>
+        <v>60.1633333333333</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -16976,25 +16994,25 @@
         <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>16.71379166666667</v>
+        <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>100.7137916666667</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>23.669375</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>93.08482500000001</v>
+        <v>186.16965</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>430.4968027777778</v>
+        <v>422.8678361111112</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>193.7986166666667</v>
+        <v>186.16965</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -17005,7 +17023,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-56.20138333333333</v>
+        <v>-63.83034999999998</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>250</v>
@@ -17025,16 +17043,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>1673.021830555555</v>
+        <v>1643.346725</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1068.035588888889</v>
+        <v>1038.360483333333</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>218.0355888888889</v>
+        <v>188.3604833333334</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>850</v>
@@ -17788,25 +17806,25 @@
         <v>161</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>27.07573333333333</v>
+        <v>0</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>237.0757333333333</v>
+        <v>0</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>82.24316111111111</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>226.8408</v>
+        <v>453.6816000000001</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>707.1596944444445</v>
+        <v>696.9247611111111</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>463.9165333333334</v>
+        <v>453.6816000000001</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -17817,7 +17835,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>113.9165333333334</v>
+        <v>103.6816000000001</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -17839,25 +17857,25 @@
         <v>170.0321611111111</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>17.88998888888889</v>
+        <v>0</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>239.8899888888889</v>
+        <v>0</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>98.42905555555555</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>272.0099</v>
+        <v>544.0198</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>780.3611055555556</v>
+        <v>812.4810166666667</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>511.8998888888889</v>
+        <v>544.0198</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -17868,7 +17886,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>51.89988888888888</v>
+        <v>84.01980000000003</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -17890,25 +17908,25 @@
         <v>298.9276666666667</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>32.75186111111112</v>
+        <v>0</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>278.7518611111111</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>135.1268611111111</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>270.383375</v>
+        <v>540.76675</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>983.1897638888889</v>
+        <v>974.8212777777778</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>983.1897638888889</v>
+        <v>974.8212777777778</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -17919,7 +17937,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>303.1897638888889</v>
+        <v>294.8212777777778</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -17941,25 +17959,25 @@
         <v>247.6051944444444</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>41.3974611111111</v>
+        <v>0</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>233.3974611111111</v>
+        <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>118.4519861111111</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>258.288575</v>
+        <v>516.57715</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>857.7432166666665</v>
+        <v>882.6343305555555</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>857.7432166666665</v>
+        <v>882.6343305555555</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -17970,7 +17988,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>357.7432166666665</v>
+        <v>382.6343305555555</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -17990,16 +18008,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>3328.453780555556</v>
+        <v>3366.861386111112</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>2816.749402777778</v>
+        <v>2855.157008333334</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>826.7494027777775</v>
+        <v>865.1570083333336</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>1990</v>
@@ -18753,25 +18771,25 @@
         <v>175.4877777777778</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9.604027777777777</v>
+        <v>0</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>153.6040277777778</v>
+        <v>0</v>
       </c>
       <c r="H61" s="11" t="n">
         <v>81.60402777777777</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>158.43625</v>
+        <v>316.8725</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>569.1320833333333</v>
+        <v>573.9643055555555</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>312.0402777777778</v>
+        <v>316.8725</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -18782,7 +18800,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-187.9597222222222</v>
+        <v>-183.1275</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -18804,25 +18822,25 @@
         <v>65</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H62" s="11" t="n">
         <v>57</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>130.29175</v>
+        <v>260.5835</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>366.29175</v>
+        <v>382.5835</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>244.29175</v>
+        <v>260.5835</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -18833,7 +18851,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>-5.708249999999992</v>
+        <v>10.58350000000002</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>250</v>
@@ -18855,25 +18873,25 @@
         <v>196</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8.035722222222221</v>
+        <v>0</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>108.0357222222222</v>
+        <v>0</v>
       </c>
       <c r="H63" s="11" t="n">
         <v>55.79461111111111</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>147.3215</v>
+        <v>294.643</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>507.1518333333333</v>
+        <v>546.4376111111111</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>255.3572222222222</v>
+        <v>294.643</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -18884,7 +18902,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-214.6427777777778</v>
+        <v>-175.357</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -18906,25 +18924,25 @@
         <v>116.4315</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>6.054499999999998</v>
+        <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>114.0545</v>
+        <v>0</v>
       </c>
       <c r="H64" s="11" t="n">
         <v>43.72116666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>108.4905</v>
+        <v>216.981</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>382.6976666666666</v>
+        <v>377.1336666666667</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>222.545</v>
+        <v>216.981</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -18935,7 +18953,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>-27.45499999999998</v>
+        <v>-33.01900000000001</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -18955,16 +18973,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1825.273333333333</v>
+        <v>1880.119083333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>1034.23425</v>
+        <v>1089.08</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-435.76575</v>
+        <v>-380.9200000000001</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>1470</v>
@@ -19718,25 +19736,25 @@
         <v>142.5139166666667</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>10.93708333333333</v>
+        <v>0</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>86.93708333333333</v>
+        <v>0</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>44.64336111111111</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>106.216875</v>
+        <v>212.43375</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>380.3112361111111</v>
+        <v>399.5910277777778</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>193.1539583333333</v>
+        <v>212.43375</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -19747,7 +19765,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-156.8460416666667</v>
+        <v>-137.56625</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -19769,25 +19787,25 @@
         <v>119.6931666666667</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>28.17423611111111</v>
+        <v>0</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>120.1742361111111</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>67.67701388888889</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>119.713625</v>
+        <v>239.42725</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>427.2580416666667</v>
+        <v>426.7974305555556</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>239.8878611111111</v>
+        <v>239.42725</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -19798,7 +19816,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-110.1121388888889</v>
+        <v>-110.57275</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -19820,25 +19838,25 @@
         <v>176.8583333333333</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>9.34263888888889</v>
+        <v>0</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>65.34263888888889</v>
+        <v>0</v>
       </c>
       <c r="H87" s="11" t="n">
         <v>37.00930555555556</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>58.81675000000001</v>
+        <v>117.6335</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>338.0270277777778</v>
+        <v>331.5011388888889</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>124.1593888888889</v>
+        <v>117.6335</v>
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
@@ -19849,7 +19867,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>-225.8406111111111</v>
+        <v>-232.3665</v>
       </c>
       <c r="O87" s="11" t="n">
         <v>350</v>
@@ -19871,25 +19889,25 @@
         <v>178.5345</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>16.94827777777778</v>
+        <v>0</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>84.94827777777778</v>
+        <v>0</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>47.82327777777778</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>81.5069</v>
+        <v>163.0138</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>392.8129555555555</v>
+        <v>389.3715777777778</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>166.4551777777778</v>
+        <v>163.0138</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -19900,7 +19918,7 @@
         <v>924.3805879</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-183.5448222222222</v>
+        <v>-186.9862</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>350</v>
@@ -19920,16 +19938,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1538.409261111111</v>
+        <v>1547.261175</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>723.656386111111</v>
+        <v>732.5083</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-676.343613888889</v>
+        <v>-667.4917</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>1400</v>
@@ -20683,25 +20701,25 @@
         <v>70</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>5.239980555555555</v>
+        <v>0</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>77.23998055555556</v>
+        <v>0</v>
       </c>
       <c r="H109" s="11" t="n">
         <v>32.52331388888889</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>101.159825</v>
+        <v>202.31965</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>280.9231194444445</v>
+        <v>304.8429638888889</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>178.3998055555556</v>
+        <v>202.31965</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -20712,7 +20730,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>178.3998055555556</v>
+        <v>202.31965</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -20734,25 +20752,25 @@
         <v>104.1190277777778</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>31.65300000000001</v>
+        <v>0</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>133.653</v>
+        <v>0</v>
       </c>
       <c r="H110" s="11" t="n">
         <v>27.8606</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>107.9754</v>
+        <v>215.9508</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>373.6080277777778</v>
+        <v>347.9304277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>241.6284</v>
+        <v>215.9508</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -20763,7 +20781,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>241.6284</v>
+        <v>215.9508</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -20785,25 +20803,25 @@
         <v>112.8991388888889</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>6.627027777777776</v>
+        <v>0</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>70.62702777777778</v>
+        <v>0</v>
       </c>
       <c r="H111" s="11" t="n">
         <v>23.02269444444444</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>77.821625</v>
+        <v>155.64325</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>284.3704861111111</v>
+        <v>291.5650833333333</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>148.4486527777778</v>
+        <v>155.64325</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -20814,7 +20832,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>148.4486527777778</v>
+        <v>155.64325</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>0</v>
@@ -20836,25 +20854,25 @@
         <v>87.16388888888889</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>36.98388888888889</v>
+        <v>0</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>138.9838888888889</v>
+        <v>0</v>
       </c>
       <c r="H112" s="11" t="n">
         <v>51.054</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>117.571</v>
+        <v>235.142</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>394.7727777777778</v>
+        <v>373.3598888888889</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>256.5548888888889</v>
+        <v>235.142</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -20865,7 +20883,7 @@
         <v>895.0173385999999</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>256.5548888888889</v>
+        <v>235.142</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -20885,16 +20903,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1333.674411111111</v>
+        <v>1317.698363888889</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>825.0317472222223</v>
+        <v>809.0557</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>825.0317472222223</v>
+        <v>809.0557</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>0</v>
@@ -21648,25 +21666,25 @@
         <v>177.4503222222222</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>9.116327777777778</v>
+        <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>153.1163277777778</v>
+        <v>0</v>
       </c>
       <c r="H133" s="11" t="n">
         <v>64.17026666666666</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>154.04695</v>
+        <v>308.0939</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>548.7838666666667</v>
+        <v>549.7144888888889</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>307.1632777777778</v>
+        <v>308.0939</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -21677,7 +21695,7 @@
         <v>985.1345504</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-42.83672222222219</v>
+        <v>-41.90609999999998</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -21699,25 +21717,25 @@
         <v>168.0188333333333</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H134" s="11" t="n">
         <v>53.11893888888889</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>133.53045</v>
+        <v>267.0609</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>450.6682222222222</v>
+        <v>488.1986722222222</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>229.53045</v>
+        <v>267.0609</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -21728,7 +21746,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-120.46955</v>
+        <v>-82.9391</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>350</v>
@@ -21750,25 +21768,25 @@
         <v>412.1624666666667</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H135" s="11" t="n">
         <v>42</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>98.13662500000001</v>
+        <v>196.27325</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>636.2990916666666</v>
+        <v>650.4357166666666</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>636.2990916666666</v>
+        <v>650.4357166666666</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -21779,7 +21797,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>186.2990916666666</v>
+        <v>200.4357166666666</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -21801,25 +21819,25 @@
         <v>172.3949888888889</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>6.863305555555556</v>
+        <v>0</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>84.86330555555556</v>
+        <v>0</v>
       </c>
       <c r="H136" s="11" t="n">
         <v>45.26661111111111</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>100.76975</v>
+        <v>201.5395</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>403.2946555555556</v>
+        <v>419.2011</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>185.6330555555556</v>
+        <v>201.5395</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -21830,7 +21848,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-64.36694444444444</v>
+        <v>-48.4605</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -21850,16 +21868,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2039.045836111111</v>
+        <v>2107.549977777778</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1358.625875</v>
+        <v>1427.130016666667</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>-41.37412500000005</v>
+        <v>27.13001666666673</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1400</v>
@@ -22589,25 +22607,25 @@
         <v>175</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>19.24277777777778</v>
+        <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>121.2427777777778</v>
+        <v>0</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>20.45</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>137.5925</v>
+        <v>275.185</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>454.2852777777778</v>
+        <v>470.635</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>258.8352777777778</v>
+        <v>275.185</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -22615,7 +22633,7 @@
         </is>
       </c>
       <c r="M13" s="11" t="n">
-        <v>8.835277777777776</v>
+        <v>25.185</v>
       </c>
       <c r="N13" s="11" t="n">
         <v>250</v>
@@ -22637,25 +22655,25 @@
         <v>130</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>15.84277777777778</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>153.215</v>
+        <v>306.43</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>413.0577777777778</v>
+        <v>452.2727777777778</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>267.215</v>
+        <v>306.43</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -22663,7 +22681,7 @@
         </is>
       </c>
       <c r="M14" s="11" t="n">
-        <v>267.215</v>
+        <v>306.43</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>0</v>
@@ -22685,25 +22703,25 @@
         <v>210</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>16.69733333333333</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>118.6973333333333</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>12.50277777777778</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>126.138</v>
+        <v>252.276</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>467.3381111111111</v>
+        <v>474.7787777777777</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>467.3381111111111</v>
+        <v>474.7787777777777</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -22711,7 +22729,7 @@
         </is>
       </c>
       <c r="M15" s="11" t="n">
-        <v>117.3381111111111</v>
+        <v>124.7787777777777</v>
       </c>
       <c r="N15" s="11" t="n">
         <v>350</v>
@@ -22733,25 +22751,25 @@
         <v>213.0288111111111</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>17.67208333333334</v>
+        <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>77.67208333333333</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>34.71108333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>76.80975000000001</v>
+        <v>153.6195</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>402.2217277777778</v>
+        <v>401.3593944444444</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>154.4818333333333</v>
+        <v>153.6195</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -22759,7 +22777,7 @@
         </is>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-195.5181666666667</v>
+        <v>-196.3805</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>350</v>
@@ -22781,11 +22799,11 @@
       <c r="I17" s="34" t="n"/>
       <c r="J17" s="34" t="n"/>
       <c r="K17" s="19" t="n">
-        <v>1147.870222222222</v>
+        <v>1210.013277777778</v>
       </c>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="19" t="n">
-        <v>197.8702222222223</v>
+        <v>260.0132777777778</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>950</v>
@@ -23132,25 +23150,25 @@
         <v>161</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>20.48632222222222</v>
+        <v>0</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>308.4863222222222</v>
+        <v>0</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>38.47352777777778</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>328.3769</v>
+        <v>656.7538000000001</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>836.3367499999999</v>
+        <v>856.2273277777779</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>636.8632222222222</v>
+        <v>656.7538000000001</v>
       </c>
       <c r="L28" s="33" t="inlineStr">
         <is>
@@ -23158,7 +23176,7 @@
         </is>
       </c>
       <c r="M28" s="11" t="n">
-        <v>386.8632222222222</v>
+        <v>406.7538000000001</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>250</v>
@@ -23180,25 +23198,25 @@
         <v>170.0321611111111</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>28.85811111111111</v>
+        <v>0</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>364.8581111111111</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>30.46093333333333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>427.723</v>
+        <v>855.446</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>993.0742055555554</v>
+        <v>1055.939094444444</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>792.5811111111111</v>
+        <v>855.446</v>
       </c>
       <c r="L29" s="33" t="inlineStr">
         <is>
@@ -23206,7 +23224,7 @@
         </is>
       </c>
       <c r="M29" s="11" t="n">
-        <v>542.5811111111111</v>
+        <v>605.446</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>250</v>
@@ -23228,25 +23246,25 @@
         <v>298.9276666666667</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>60.92038888888889</v>
+        <v>0</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>474.9203888888889</v>
+        <v>0</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>18.89583333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>481.1417500000001</v>
+        <v>962.2835000000001</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>1273.885638888889</v>
+        <v>1280.107</v>
       </c>
       <c r="K30" s="17" t="n">
-        <v>1273.885638888889</v>
+        <v>1280.107</v>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
@@ -23254,7 +23272,7 @@
         </is>
       </c>
       <c r="M30" s="11" t="n">
-        <v>923.8856388888889</v>
+        <v>930.107</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>350</v>
@@ -23276,25 +23294,25 @@
         <v>247.6051944444444</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>104.9039722222222</v>
+        <v>0</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>368.9039722222223</v>
+        <v>0</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>10</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>320.82715</v>
+        <v>641.6543</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>947.3363166666668</v>
+        <v>899.2594944444445</v>
       </c>
       <c r="K31" s="17" t="n">
-        <v>947.3363166666668</v>
+        <v>899.2594944444445</v>
       </c>
       <c r="L31" s="23" t="inlineStr">
         <is>
@@ -23302,7 +23320,7 @@
         </is>
       </c>
       <c r="M31" s="11" t="n">
-        <v>597.3363166666668</v>
+        <v>549.2594944444445</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>350</v>
@@ -23324,11 +23342,11 @@
       <c r="I32" s="34" t="n"/>
       <c r="J32" s="34" t="n"/>
       <c r="K32" s="19" t="n">
-        <v>3650.666288888889</v>
+        <v>3691.566294444445</v>
       </c>
       <c r="L32" s="34" t="n"/>
       <c r="M32" s="19" t="n">
-        <v>2450.666288888889</v>
+        <v>2491.566294444445</v>
       </c>
       <c r="N32" s="19" t="n">
         <v>1200</v>
@@ -23675,25 +23693,25 @@
         <v>175.4877777777778</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>19.20805555555555</v>
+        <v>0</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>307.2080555555556</v>
+        <v>0</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>316.8725</v>
+        <v>633.745</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>799.5683333333334</v>
+        <v>809.2327777777778</v>
       </c>
       <c r="K43" s="17" t="n">
-        <v>624.0805555555555</v>
+        <v>633.745</v>
       </c>
       <c r="L43" s="33" t="inlineStr">
         <is>
@@ -23701,7 +23719,7 @@
         </is>
       </c>
       <c r="M43" s="11" t="n">
-        <v>374.0805555555555</v>
+        <v>383.745</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>250</v>
@@ -23723,25 +23741,25 @@
         <v>65</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>249.9535</v>
+        <v>499.907</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>538.9535</v>
+        <v>566.9069999999999</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>471.9535</v>
+        <v>499.907</v>
       </c>
       <c r="L44" s="33" t="inlineStr">
         <is>
@@ -23749,7 +23767,7 @@
         </is>
       </c>
       <c r="M44" s="11" t="n">
-        <v>471.9535</v>
+        <v>499.907</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>0</v>
@@ -23771,25 +23789,25 @@
         <v>196</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>15.58922222222222</v>
+        <v>0</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>207.5892222222222</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>2.241111111111111</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>284.303</v>
+        <v>568.606</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>690.1333333333334</v>
+        <v>766.8471111111111</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>491.8922222222222</v>
+        <v>568.606</v>
       </c>
       <c r="L45" s="33" t="inlineStr">
         <is>
@@ -23797,7 +23815,7 @@
         </is>
       </c>
       <c r="M45" s="11" t="n">
-        <v>491.8922222222222</v>
+        <v>568.606</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>0</v>
@@ -23819,25 +23837,25 @@
         <v>116.4315</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>11.77566666666666</v>
+        <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>159.7756666666667</v>
+        <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>216.981</v>
+        <v>433.962</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>493.1881666666667</v>
+        <v>550.3935</v>
       </c>
       <c r="K46" s="17" t="n">
-        <v>376.7566666666667</v>
+        <v>433.962</v>
       </c>
       <c r="L46" s="33" t="inlineStr">
         <is>
@@ -23845,7 +23863,7 @@
         </is>
       </c>
       <c r="M46" s="11" t="n">
-        <v>376.7566666666667</v>
+        <v>433.962</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>0</v>
@@ -23867,11 +23885,11 @@
       <c r="I47" s="34" t="n"/>
       <c r="J47" s="34" t="n"/>
       <c r="K47" s="19" t="n">
-        <v>1964.682944444444</v>
+        <v>2136.22</v>
       </c>
       <c r="L47" s="34" t="n"/>
       <c r="M47" s="19" t="n">
-        <v>1714.682944444444</v>
+        <v>1886.22</v>
       </c>
       <c r="N47" s="19" t="n">
         <v>250</v>
@@ -24218,25 +24236,25 @@
         <v>142.5139166666667</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>20.62005555555556</v>
+        <v>0</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>160.6200555555556</v>
+        <v>0</v>
       </c>
       <c r="H58" s="11" t="n">
         <v>3.960388888888889</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>197.79025</v>
+        <v>395.5805</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>504.8846111111111</v>
+        <v>542.0548055555556</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>358.4103055555556</v>
+        <v>395.5805</v>
       </c>
       <c r="L58" s="33" t="inlineStr">
         <is>
@@ -24244,7 +24262,7 @@
         </is>
       </c>
       <c r="M58" s="11" t="n">
-        <v>358.4103055555556</v>
+        <v>395.5805</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>0</v>
@@ -24266,25 +24284,25 @@
         <v>119.6931666666667</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>51.35402777777777</v>
+        <v>0</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>219.3540277777778</v>
+        <v>0</v>
       </c>
       <c r="H59" s="11" t="n">
         <v>4.499444444444444</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>218.43725</v>
+        <v>436.8745</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>561.9838888888889</v>
+        <v>561.0671111111111</v>
       </c>
       <c r="K59" s="17" t="n">
-        <v>437.7912777777777</v>
+        <v>436.8745</v>
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
@@ -24292,7 +24310,7 @@
         </is>
       </c>
       <c r="M59" s="11" t="n">
-        <v>437.7912777777777</v>
+        <v>436.8745</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>0</v>
@@ -24314,25 +24332,25 @@
         <v>176.8583333333333</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>20.35194444444445</v>
+        <v>0</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>128.3519444444445</v>
+        <v>0</v>
       </c>
       <c r="H60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>117.6335</v>
+        <v>235.267</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>422.8437777777779</v>
+        <v>412.1253333333334</v>
       </c>
       <c r="K60" s="17" t="n">
-        <v>245.9854444444445</v>
+        <v>235.267</v>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
@@ -24340,7 +24358,7 @@
         </is>
       </c>
       <c r="M60" s="11" t="n">
-        <v>245.9854444444445</v>
+        <v>235.267</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>0</v>
@@ -24362,25 +24380,25 @@
         <v>178.5345</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>33.97988888888888</v>
+        <v>0</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>157.9798888888889</v>
+        <v>0</v>
       </c>
       <c r="H61" s="11" t="n">
         <v>3.266666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>154.1638</v>
+        <v>308.3276</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>493.9448555555556</v>
+        <v>490.1287666666667</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>312.1436888888888</v>
+        <v>308.3276</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -24388,7 +24406,7 @@
         </is>
       </c>
       <c r="M61" s="11" t="n">
-        <v>312.1436888888888</v>
+        <v>308.3276</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>0</v>
@@ -24410,11 +24428,11 @@
       <c r="I62" s="34" t="n"/>
       <c r="J62" s="34" t="n"/>
       <c r="K62" s="19" t="n">
-        <v>1354.330716666667</v>
+        <v>1376.0496</v>
       </c>
       <c r="L62" s="34" t="n"/>
       <c r="M62" s="19" t="n">
-        <v>1354.330716666667</v>
+        <v>1376.0496</v>
       </c>
       <c r="N62" s="19" t="n">
         <v>0</v>
@@ -24761,25 +24779,25 @@
         <v>70</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>9.046627777777777</v>
+        <v>0</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>121.0466277777778</v>
+        <v>0</v>
       </c>
       <c r="H73" s="11" t="n">
         <v>8.716666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>165.41965</v>
+        <v>330.8393</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>365.1829444444444</v>
+        <v>409.5559666666667</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>286.4662777777778</v>
+        <v>330.8393</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -24787,7 +24805,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="n">
-        <v>286.4662777777778</v>
+        <v>330.8393</v>
       </c>
       <c r="N73" s="11" t="n">
         <v>0</v>
@@ -24809,25 +24827,25 @@
         <v>104.1190277777778</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>7.721199999999998</v>
+        <v>0</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>103.7212</v>
+        <v>0</v>
       </c>
       <c r="H74" s="11" t="n">
         <v>27.35</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>141.4908</v>
+        <v>282.9816</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>376.6810277777778</v>
+        <v>414.4506277777778</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>245.212</v>
+        <v>282.9816</v>
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
@@ -24835,7 +24853,7 @@
         </is>
       </c>
       <c r="M74" s="11" t="n">
-        <v>245.212</v>
+        <v>282.9816</v>
       </c>
       <c r="N74" s="11" t="n">
         <v>0</v>
@@ -24857,25 +24875,25 @@
         <v>112.8991388888889</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>9.378722222222221</v>
+        <v>0</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>85.37872222222222</v>
+        <v>0</v>
       </c>
       <c r="H75" s="11" t="n">
         <v>17.6775</v>
       </c>
       <c r="I75" s="11" t="n">
-        <v>99.20425</v>
+        <v>198.4085</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>315.1596111111111</v>
+        <v>328.9851388888889</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>184.5829722222222</v>
+        <v>198.4085</v>
       </c>
       <c r="L75" s="33" t="inlineStr">
         <is>
@@ -24883,7 +24901,7 @@
         </is>
       </c>
       <c r="M75" s="11" t="n">
-        <v>184.5829722222222</v>
+        <v>198.4085</v>
       </c>
       <c r="N75" s="11" t="n">
         <v>0</v>
@@ -24905,25 +24923,25 @@
         <v>87.16388888888889</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>12.44133333333333</v>
+        <v>0</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>186.4413333333333</v>
+        <v>0</v>
       </c>
       <c r="H76" s="11" t="n">
         <v>14.04722222222222</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>198.972</v>
+        <v>397.944</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>486.6244444444444</v>
+        <v>499.1551111111111</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>385.4133333333334</v>
+        <v>397.944</v>
       </c>
       <c r="L76" s="33" t="inlineStr">
         <is>
@@ -24931,7 +24949,7 @@
         </is>
       </c>
       <c r="M76" s="11" t="n">
-        <v>385.4133333333334</v>
+        <v>397.944</v>
       </c>
       <c r="N76" s="11" t="n">
         <v>0</v>
@@ -24953,11 +24971,11 @@
       <c r="I77" s="34" t="n"/>
       <c r="J77" s="34" t="n"/>
       <c r="K77" s="19" t="n">
-        <v>1101.674583333333</v>
+        <v>1210.1734</v>
       </c>
       <c r="L77" s="34" t="n"/>
       <c r="M77" s="19" t="n">
-        <v>1101.674583333333</v>
+        <v>1210.1734</v>
       </c>
       <c r="N77" s="19" t="n">
         <v>0</v>
@@ -25304,25 +25322,25 @@
         <v>177.4503222222222</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>14.67386666666667</v>
+        <v>0</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>236.6738666666667</v>
+        <v>0</v>
       </c>
       <c r="H88" s="11" t="n">
         <v>15.22545555555556</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>243.0648</v>
+        <v>486.1296</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>672.4144444444444</v>
+        <v>678.8053777777777</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>479.7386666666666</v>
+        <v>486.1296</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -25330,7 +25348,7 @@
         </is>
       </c>
       <c r="M88" s="11" t="n">
-        <v>479.7386666666666</v>
+        <v>486.1296</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>0</v>
@@ -25352,25 +25370,25 @@
         <v>168.0188333333333</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>16.57121111111111</v>
+        <v>0</v>
       </c>
       <c r="G89" s="11" t="n">
-        <v>190.5712111111111</v>
+        <v>0</v>
       </c>
       <c r="H89" s="11" t="n">
         <v>6</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>236.1409</v>
+        <v>472.2818</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>600.7309444444444</v>
+        <v>646.3006333333334</v>
       </c>
       <c r="K89" s="17" t="n">
-        <v>426.7121111111111</v>
+        <v>472.2818</v>
       </c>
       <c r="L89" s="33" t="inlineStr">
         <is>
@@ -25378,7 +25396,7 @@
         </is>
       </c>
       <c r="M89" s="11" t="n">
-        <v>426.7121111111111</v>
+        <v>472.2818</v>
       </c>
       <c r="N89" s="11" t="n">
         <v>0</v>
@@ -25400,25 +25418,25 @@
         <v>412.1624666666667</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="11" t="n">
-        <v>196.27325</v>
+        <v>392.5465</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>776.4357166666666</v>
+        <v>804.7089666666667</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>776.4357166666666</v>
+        <v>804.7089666666667</v>
       </c>
       <c r="L90" s="23" t="inlineStr">
         <is>
@@ -25426,7 +25444,7 @@
         </is>
       </c>
       <c r="M90" s="11" t="n">
-        <v>426.4357166666666</v>
+        <v>454.7089666666667</v>
       </c>
       <c r="N90" s="11" t="n">
         <v>350</v>
@@ -25448,25 +25466,25 @@
         <v>172.3949888888889</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>24.53322222222222</v>
+        <v>0</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>156.5332222222222</v>
+        <v>0</v>
       </c>
       <c r="H91" s="11" t="n">
         <v>6</v>
       </c>
       <c r="I91" s="11" t="n">
-        <v>176.3995</v>
+        <v>352.799</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>511.3277111111112</v>
+        <v>531.193988888889</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>332.9327222222223</v>
+        <v>352.799</v>
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
@@ -25474,7 +25492,7 @@
         </is>
       </c>
       <c r="M91" s="11" t="n">
-        <v>332.9327222222223</v>
+        <v>352.799</v>
       </c>
       <c r="N91" s="11" t="n">
         <v>0</v>
@@ -25496,11 +25514,11 @@
       <c r="I92" s="34" t="n"/>
       <c r="J92" s="34" t="n"/>
       <c r="K92" s="19" t="n">
-        <v>2015.819216666667</v>
+        <v>2115.919366666667</v>
       </c>
       <c r="L92" s="34" t="n"/>
       <c r="M92" s="19" t="n">
-        <v>1665.819216666667</v>
+        <v>1765.919366666667</v>
       </c>
       <c r="N92" s="19" t="n">
         <v>350</v>

--- a/output/Bonus_Plan_FINAL.xlsx
+++ b/output/Bonus_Plan_FINAL.xlsx
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B7" s="43" t="inlineStr">
         <is>
-          <t>REN written premium x 1% (e.g., $50k REN -&gt; $500 bonus). Paid monthly at the agent level, not per policy.</t>
+          <t>REN written premium x 0.5% (e.g., $50k REN -&gt; $250 bonus). Paid monthly at the agent level, not per policy.</t>
         </is>
       </c>
       <c r="C7" s="44" t="n"/>
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>7915.425727777778</v>
+        <v>7321.886727777778</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>11862.83671111111</v>
+        <v>8636.835711111113</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14902.49108333333</v>
+        <v>9637.567083333335</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>3012.295022222223</v>
+        <v>2418.756022222223</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7951.291508333333</v>
+        <v>4725.290508333333</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>11739.94193888889</v>
+        <v>6475.017938888889</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4728,13 +4728,13 @@
         <v>350</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>321.2927777777778</v>
+        <v>283.2677777777778</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>76.05</v>
+        <v>38.025</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>-273.95</v>
+        <v>-311.975</v>
       </c>
     </row>
     <row r="15">
@@ -4761,13 +4761,13 @@
         <v>660</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>450.7910222222222</v>
+        <v>388.1386722222222</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>125.3047</v>
+        <v>62.65235</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>-534.6953</v>
+        <v>-597.34765</v>
       </c>
     </row>
     <row r="16">
@@ -4827,13 +4827,13 @@
         <v>490</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>247.7774722222222</v>
+        <v>240.4557222222222</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>14.6435</v>
+        <v>7.32175</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>-475.3565</v>
+        <v>-482.67825</v>
       </c>
     </row>
     <row r="18">
@@ -4860,13 +4860,13 @@
         <v>350</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>171.9466277777778</v>
+        <v>153.4966277777777</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>36.9</v>
+        <v>18.45</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-313.1</v>
+        <v>-331.55</v>
       </c>
     </row>
     <row r="19">
@@ -4893,13 +4893,13 @@
         <v>550</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>368.1532888888888</v>
+        <v>335.6387388888888</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>65.0291</v>
+        <v>32.51455</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-484.9709</v>
+        <v>-517.48545</v>
       </c>
     </row>
     <row r="20">
@@ -4926,13 +4926,13 @@
         <v>250</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>262.17</v>
+        <v>224.585</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>75.17</v>
+        <v>37.585</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>-174.83</v>
+        <v>-212.415</v>
       </c>
     </row>
     <row r="21">
@@ -4959,13 +4959,13 @@
         <v>740</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>483.1870722222222</v>
+        <v>425.0386722222222</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>116.2968</v>
+        <v>58.1484</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-623.7032</v>
+        <v>-681.8516</v>
       </c>
     </row>
     <row r="22">
@@ -4992,13 +4992,13 @@
         <v>450</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>186.63</v>
+        <v>181.315</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>10.63</v>
+        <v>5.315</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>-439.37</v>
+        <v>-444.685</v>
       </c>
     </row>
     <row r="23">
@@ -5025,13 +5025,13 @@
         <v>600</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>276.0371944444445</v>
+        <v>265.5421944444445</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>20.99</v>
+        <v>10.495</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>-579.01</v>
+        <v>-589.505</v>
       </c>
     </row>
     <row r="24">
@@ -5058,13 +5058,13 @@
         <v>350</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>234.3002277777778</v>
+        <v>197.0702277777778</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>74.46000000000001</v>
+        <v>37.23</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>-275.54</v>
+        <v>-312.77</v>
       </c>
     </row>
     <row r="25">
@@ -5091,13 +5091,13 @@
         <v>450</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>302.5100444444445</v>
+        <v>287.0500444444444</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>30.92</v>
+        <v>15.46</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>-419.08</v>
+        <v>-434.54</v>
       </c>
     </row>
     <row r="26">
@@ -5124,13 +5124,13 @@
         <v>350</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>316.7073333333333</v>
+        <v>297.2023333333333</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>316.7073333333333</v>
+        <v>297.2023333333333</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>-33.29266666666666</v>
+        <v>-52.79766666666666</v>
       </c>
     </row>
     <row r="27">
@@ -5157,13 +5157,13 @@
         <v>1020</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>626.4730555555556</v>
+        <v>596.6605555555556</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>626.4730555555556</v>
+        <v>596.6605555555556</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>-393.5269444444444</v>
+        <v>-423.3394444444444</v>
       </c>
     </row>
     <row r="28">
@@ -5190,13 +5190,13 @@
         <v>710</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>317.9292222222222</v>
+        <v>312.7592222222223</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>10.34</v>
+        <v>5.17</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>-699.66</v>
+        <v>-704.83</v>
       </c>
     </row>
     <row r="29">
@@ -5256,13 +5256,13 @@
         <v>350</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>216.7168611111111</v>
+        <v>188.4973611111111</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>56.439</v>
+        <v>28.2195</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>-293.561</v>
+        <v>-321.7805</v>
       </c>
     </row>
     <row r="31">
@@ -5322,13 +5322,13 @@
         <v>350</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>370.0607944444444</v>
+        <v>315.3808444444444</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>109.3599</v>
+        <v>54.67995</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>-240.6401</v>
+        <v>-295.32005</v>
       </c>
     </row>
     <row r="33">
@@ -5355,13 +5355,13 @@
         <v>720</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>680.2591666666667</v>
+        <v>582.3841666666667</v>
       </c>
       <c r="H33" s="17" t="n">
-        <v>680.2591666666667</v>
+        <v>582.3841666666667</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>-39.74083333333328</v>
+        <v>-137.6158333333333</v>
       </c>
     </row>
     <row r="34">
@@ -5421,13 +5421,13 @@
         <v>490</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>283.3643888888889</v>
+        <v>278.9393888888889</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>8.85</v>
+        <v>4.425</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>-481.15</v>
+        <v>-485.575</v>
       </c>
     </row>
     <row r="36">
@@ -5454,13 +5454,13 @@
         <v>350</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>222.7752222222222</v>
+        <v>204.6902222222222</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>36.17</v>
+        <v>18.085</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>-313.83</v>
+        <v>-331.915</v>
       </c>
     </row>
     <row r="37">
@@ -5487,13 +5487,13 @@
         <v>350</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>288.0682111111111</v>
+        <v>275.4982111111111</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>25.14</v>
+        <v>12.57</v>
       </c>
       <c r="I37" s="16" t="n">
-        <v>-324.86</v>
+        <v>-337.43</v>
       </c>
     </row>
     <row r="38">
@@ -5506,13 +5506,13 @@
         <v>12220</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>7915.42572777778</v>
+        <v>7321.886727777779</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>3012.295022222222</v>
+        <v>2418.756022222223</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-9207.704977777777</v>
+        <v>-9801.243977777776</v>
       </c>
     </row>
     <row r="40">
@@ -5593,13 +5593,13 @@
         <v>250</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>424.9305555555555</v>
+        <v>318.1093055555556</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>213.6425</v>
+        <v>106.82125</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>-36.35749999999999</v>
+        <v>-143.17875</v>
       </c>
     </row>
     <row r="43">
@@ -5626,13 +5626,13 @@
         <v>350</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>696.9247611111111</v>
+        <v>470.0839611111111</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>453.6816000000001</v>
+        <v>226.8408</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>103.6816000000001</v>
+        <v>-123.1592</v>
       </c>
     </row>
     <row r="44">
@@ -5659,13 +5659,13 @@
         <v>500</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>573.9643055555555</v>
+        <v>415.5280555555555</v>
       </c>
       <c r="H44" s="17" t="n">
-        <v>316.8725</v>
+        <v>158.43625</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>-183.1275</v>
+        <v>-341.56375</v>
       </c>
     </row>
     <row r="45">
@@ -5692,13 +5692,13 @@
         <v>350</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>399.5910277777778</v>
+        <v>293.3741527777778</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>212.43375</v>
+        <v>106.216875</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>-137.56625</v>
+        <v>-243.783125</v>
       </c>
     </row>
     <row r="46">
@@ -5725,13 +5725,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>304.8429638888889</v>
+        <v>203.6831388888889</v>
       </c>
       <c r="H46" s="17" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
     </row>
     <row r="47">
@@ -5758,13 +5758,13 @@
         <v>350</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>549.7144888888889</v>
+        <v>395.6675388888889</v>
       </c>
       <c r="H47" s="17" t="n">
-        <v>308.0939</v>
+        <v>154.04695</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>-41.90609999999998</v>
+        <v>-195.95305</v>
       </c>
     </row>
     <row r="48">
@@ -5791,13 +5791,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>385.385</v>
+        <v>271.1925</v>
       </c>
       <c r="H48" s="17" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
     </row>
     <row r="49">
@@ -5824,13 +5824,13 @@
         <v>460</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>812.4810166666667</v>
+        <v>540.4711166666667</v>
       </c>
       <c r="H49" s="17" t="n">
-        <v>544.0198</v>
+        <v>272.0099</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>84.01980000000003</v>
+        <v>-187.9901</v>
       </c>
     </row>
     <row r="50">
@@ -5857,13 +5857,13 @@
         <v>250</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>382.5835</v>
+        <v>252.29175</v>
       </c>
       <c r="H50" s="17" t="n">
-        <v>260.5835</v>
+        <v>130.29175</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>10.58350000000002</v>
+        <v>-119.70825</v>
       </c>
     </row>
     <row r="51">
@@ -5890,13 +5890,13 @@
         <v>350</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>426.7974305555556</v>
+        <v>307.0838055555556</v>
       </c>
       <c r="H51" s="17" t="n">
-        <v>239.42725</v>
+        <v>119.713625</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-110.57275</v>
+        <v>-230.286375</v>
       </c>
     </row>
     <row r="52">
@@ -5923,13 +5923,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>347.9304277777778</v>
+        <v>239.9550277777778</v>
       </c>
       <c r="H52" s="17" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
     </row>
     <row r="53">
@@ -5956,13 +5956,13 @@
         <v>350</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>488.1986722222222</v>
+        <v>354.6682222222222</v>
       </c>
       <c r="H53" s="17" t="n">
-        <v>267.0609</v>
+        <v>133.53045</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-82.9391</v>
+        <v>-216.46955</v>
       </c>
     </row>
     <row r="54">
@@ -5989,13 +5989,13 @@
         <v>350</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>410.1633333333333</v>
+        <v>327.5893333333333</v>
       </c>
       <c r="H54" s="17" t="n">
-        <v>410.1633333333333</v>
+        <v>327.5893333333333</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>60.1633333333333</v>
+        <v>-22.41066666666666</v>
       </c>
     </row>
     <row r="55">
@@ -6022,13 +6022,13 @@
         <v>680</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>974.8212777777778</v>
+        <v>704.4379027777777</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>974.8212777777778</v>
+        <v>704.4379027777777</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>294.8212777777778</v>
+        <v>24.43790277777771</v>
       </c>
     </row>
     <row r="56">
@@ -6055,13 +6055,13 @@
         <v>470</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>546.4376111111111</v>
+        <v>399.1161111111111</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>294.643</v>
+        <v>147.3215</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>-175.357</v>
+        <v>-322.6785</v>
       </c>
     </row>
     <row r="57">
@@ -6088,13 +6088,13 @@
         <v>350</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>331.5011388888889</v>
+        <v>272.6843888888889</v>
       </c>
       <c r="H57" s="17" t="n">
-        <v>117.6335</v>
+        <v>58.81675000000001</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>-232.3665</v>
+        <v>-291.18325</v>
       </c>
     </row>
     <row r="58">
@@ -6121,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>291.5650833333333</v>
+        <v>213.7434583333333</v>
       </c>
       <c r="H58" s="17" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
     </row>
     <row r="59">
@@ -6154,13 +6154,13 @@
         <v>450</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>650.4357166666666</v>
+        <v>552.2990916666666</v>
       </c>
       <c r="H59" s="17" t="n">
-        <v>650.4357166666666</v>
+        <v>552.2990916666666</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>200.4357166666666</v>
+        <v>102.2990916666666</v>
       </c>
     </row>
     <row r="60">
@@ -6187,13 +6187,13 @@
         <v>250</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>422.8678361111112</v>
+        <v>329.7830111111111</v>
       </c>
       <c r="H60" s="17" t="n">
-        <v>186.16965</v>
+        <v>93.08482500000001</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>-63.83034999999998</v>
+        <v>-156.915175</v>
       </c>
     </row>
     <row r="61">
@@ -6220,13 +6220,13 @@
         <v>500</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>882.6343305555555</v>
+        <v>624.3457555555556</v>
       </c>
       <c r="H61" s="17" t="n">
-        <v>882.6343305555555</v>
+        <v>624.3457555555556</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>382.6343305555555</v>
+        <v>124.3457555555556</v>
       </c>
     </row>
     <row r="62">
@@ -6253,13 +6253,13 @@
         <v>250</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>377.1336666666667</v>
+        <v>268.6431666666667</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>216.981</v>
+        <v>108.4905</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>-33.01900000000001</v>
+        <v>-141.5095</v>
       </c>
     </row>
     <row r="63">
@@ -6286,13 +6286,13 @@
         <v>350</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>389.3715777777778</v>
+        <v>307.8646777777778</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>163.0138</v>
+        <v>81.5069</v>
       </c>
       <c r="I63" s="16" t="n">
-        <v>-186.9862</v>
+        <v>-268.4931</v>
       </c>
     </row>
     <row r="64">
@@ -6319,13 +6319,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>373.3598888888889</v>
+        <v>255.7888888888889</v>
       </c>
       <c r="H64" s="17" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
     </row>
     <row r="65">
@@ -6352,13 +6352,13 @@
         <v>250</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>419.2011</v>
+        <v>318.43135</v>
       </c>
       <c r="H65" s="17" t="n">
-        <v>201.5395</v>
+        <v>100.76975</v>
       </c>
       <c r="I65" s="16" t="n">
-        <v>-48.4605</v>
+        <v>-149.23025</v>
       </c>
     </row>
     <row r="66">
@@ -6371,13 +6371,13 @@
         <v>7110</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>11862.83671111111</v>
+        <v>8636.835711111113</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>7951.291508333333</v>
+        <v>4725.290508333334</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>841.2915083333328</v>
+        <v>-2384.709491666666</v>
       </c>
     </row>
     <row r="69">
@@ -6390,14 +6390,14 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $3,012 (less, because few agents clear the $45k NB gate today).</t>
+          <t>REAL DATA TODAY: Current pays $12,220 (broken plan, rewards rewriting). The Bonus Plan WITH MIN pays $2,419 (less, because few agents clear the $45k NB gate today).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $11,740 (96% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $6,475 (53% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6827,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>REN written premium x 1%</t>
+          <t>REN written premium x 0.5%</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Bonus = $10 per $1,000 of REN premium the agent retained this month. This is the ONLY renewal pay - no per-policy REN base or collected incentive.</t>
+          <t>Bonus = $5 per $1,000 of REN premium retained. This is the ONLY renewal pay - no per-policy REN base or collected incentive.</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>A $50k REN month -&gt; $500 bonus. A $25k REN month -&gt; $250 bonus.</t>
+          <t>A $50k REN month -&gt; $250 bonus. A $25k REN month -&gt; $125 bonus.</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>A $2,000 renewal contributes $20 to the bonus. A $1,000 renewal contributes $10.</t>
+          <t>A $2,000 renewal contributes $10 to the bonus. A $1,000 renewal contributes $5.</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>REN $5,962 x 1% = $59.62</t>
+          <t>REN $5,962 x 0.5% = $29.81</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>$60</t>
+          <t>$30</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>$626</t>
+          <t>$597</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>$626.47</t>
+          <t>$596.66</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>76.05</v>
+        <v>38.025</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>78.20999999999999</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="H31" s="16" t="n">
-        <v>75.17</v>
+        <v>37.585</v>
       </c>
       <c r="I31" s="16" t="n">
         <v>60.83</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="H32" s="16" t="n">
-        <v>316.7073333333333</v>
+        <v>297.2023333333333</v>
       </c>
       <c r="I32" s="16" t="n">
         <v>475.825</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="H33" s="16" t="n">
-        <v>109.3599</v>
+        <v>54.67995</v>
       </c>
       <c r="I33" s="16" t="n">
         <v>118.105</v>
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="H34" s="16" t="n">
-        <v>125.3047</v>
+        <v>62.65235</v>
       </c>
       <c r="I34" s="16" t="n">
         <v>99.935</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="H35" s="16" t="n">
-        <v>116.2968</v>
+        <v>58.1484</v>
       </c>
       <c r="I35" s="16" t="n">
         <v>78.20999999999999</v>
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="H36" s="16" t="n">
-        <v>626.4730555555556</v>
+        <v>596.6605555555556</v>
       </c>
       <c r="I36" s="16" t="n">
         <v>765.74</v>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="H37" s="16" t="n">
-        <v>680.2591666666667</v>
+        <v>582.3841666666667</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>594.11</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="H39" s="16" t="n">
-        <v>10.63</v>
+        <v>5.315</v>
       </c>
       <c r="I39" s="16" t="n">
         <v>7.9</v>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="H40" s="16" t="n">
-        <v>10.34</v>
+        <v>5.17</v>
       </c>
       <c r="I40" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="H42" s="16" t="n">
-        <v>14.6435</v>
+        <v>7.32175</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>8.690000000000001</v>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="H43" s="16" t="n">
-        <v>20.99</v>
+        <v>10.495</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>17.38</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="H45" s="16" t="n">
-        <v>8.85</v>
+        <v>4.425</v>
       </c>
       <c r="I45" s="16" t="n">
         <v>9.875</v>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="H46" s="16" t="n">
-        <v>36.9</v>
+        <v>18.45</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>34.76000000000001</v>
@@ -8549,7 +8549,7 @@
         </is>
       </c>
       <c r="H47" s="16" t="n">
-        <v>74.46000000000001</v>
+        <v>37.23</v>
       </c>
       <c r="I47" s="16" t="n">
         <v>45.425</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="H48" s="16" t="n">
-        <v>56.439</v>
+        <v>28.2195</v>
       </c>
       <c r="I48" s="16" t="n">
         <v>54.50999999999999</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H49" s="16" t="n">
-        <v>36.17</v>
+        <v>18.085</v>
       </c>
       <c r="I49" s="16" t="n">
         <v>28.44</v>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>65.0291</v>
+        <v>32.51455</v>
       </c>
       <c r="I50" s="16" t="n">
         <v>52.14</v>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="H51" s="16" t="n">
-        <v>30.92</v>
+        <v>15.46</v>
       </c>
       <c r="I51" s="16" t="n">
         <v>15.8</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="H53" s="16" t="n">
-        <v>25.14</v>
+        <v>12.57</v>
       </c>
       <c r="I53" s="16" t="n">
         <v>15.8</v>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="H58" s="16" t="n">
-        <v>213.6425</v>
+        <v>106.82125</v>
       </c>
       <c r="I58" s="16" t="n">
         <v>147.73</v>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="H59" s="16" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
       <c r="I59" s="16" t="n">
         <v>147.73</v>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="H60" s="16" t="n">
-        <v>410.1633333333333</v>
+        <v>327.5893333333333</v>
       </c>
       <c r="I60" s="16" t="n">
         <v>530.905</v>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="H61" s="16" t="n">
-        <v>186.16965</v>
+        <v>93.08482500000001</v>
       </c>
       <c r="I61" s="16" t="n">
         <v>190.785</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="H62" s="16" t="n">
-        <v>453.6816000000001</v>
+        <v>226.8408</v>
       </c>
       <c r="I62" s="16" t="n">
         <v>304.15</v>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="H63" s="16" t="n">
-        <v>544.0198</v>
+        <v>272.0099</v>
       </c>
       <c r="I63" s="16" t="n">
         <v>321.53</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="H64" s="16" t="n">
-        <v>974.8212777777778</v>
+        <v>704.4379027777777</v>
       </c>
       <c r="I64" s="16" t="n">
         <v>980.8700000000001</v>
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="H65" s="16" t="n">
-        <v>882.6343305555555</v>
+        <v>624.3457555555556</v>
       </c>
       <c r="I65" s="16" t="n">
         <v>734.6900000000001</v>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="H66" s="16" t="n">
-        <v>316.8725</v>
+        <v>158.43625</v>
       </c>
       <c r="I66" s="16" t="n">
         <v>208.56</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="H67" s="16" t="n">
-        <v>260.5835</v>
+        <v>130.29175</v>
       </c>
       <c r="I67" s="16" t="n">
         <v>150.1</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="H68" s="16" t="n">
-        <v>294.643</v>
+        <v>147.3215</v>
       </c>
       <c r="I68" s="16" t="n">
         <v>217.25</v>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="H69" s="16" t="n">
-        <v>216.981</v>
+        <v>108.4905</v>
       </c>
       <c r="I69" s="16" t="n">
         <v>156.42</v>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="H70" s="16" t="n">
-        <v>212.43375</v>
+        <v>106.216875</v>
       </c>
       <c r="I70" s="16" t="n">
         <v>165.11</v>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="H71" s="16" t="n">
-        <v>239.42725</v>
+        <v>119.713625</v>
       </c>
       <c r="I71" s="16" t="n">
         <v>208.955</v>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>117.6335</v>
+        <v>58.81675000000001</v>
       </c>
       <c r="I72" s="16" t="n">
         <v>127.19</v>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="H73" s="16" t="n">
-        <v>163.0138</v>
+        <v>81.5069</v>
       </c>
       <c r="I73" s="16" t="n">
         <v>154.445</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="H74" s="16" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
       <c r="I74" s="16" t="n">
         <v>156.42</v>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="H75" s="16" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
       <c r="I75" s="16" t="n">
         <v>154.445</v>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="H76" s="16" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
       <c r="I76" s="16" t="n">
         <v>139.04</v>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="H77" s="16" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
       <c r="I77" s="16" t="n">
         <v>154.445</v>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>308.0939</v>
+        <v>154.04695</v>
       </c>
       <c r="I78" s="16" t="n">
         <v>208.56</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="H79" s="16" t="n">
-        <v>267.0609</v>
+        <v>133.53045</v>
       </c>
       <c r="I79" s="16" t="n">
         <v>126.4</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="H80" s="16" t="n">
-        <v>650.4357166666666</v>
+        <v>552.2990916666666</v>
       </c>
       <c r="I80" s="16" t="n">
         <v>657.3600000000001</v>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="H81" s="16" t="n">
-        <v>201.5395</v>
+        <v>100.76975</v>
       </c>
       <c r="I81" s="16" t="n">
         <v>112.97</v>
@@ -10993,13 +10993,13 @@
         <v>70.24277777777777</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>76.05</v>
+        <v>38.025</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>321.2927777777778</v>
+        <v>283.2677777777778</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>76.05</v>
+        <v>38.025</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-273.95</v>
+        <v>-311.975</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>350</v>
@@ -11044,13 +11044,13 @@
         <v>57</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>75.17</v>
+        <v>37.585</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>262.17</v>
+        <v>224.585</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>75.17</v>
+        <v>37.585</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>544.3810526</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>-174.83</v>
+        <v>-212.415</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>250</v>
@@ -11095,13 +11095,13 @@
         <v>67.69733333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>39.01</v>
+        <v>19.505</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>316.7073333333333</v>
+        <v>297.2023333333333</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>316.7073333333333</v>
+        <v>297.2023333333333</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>829.8586758</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-33.29266666666666</v>
+        <v>-52.79766666666666</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -11146,13 +11146,13 @@
         <v>47.67208333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>109.3599</v>
+        <v>54.67995</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>370.0607944444444</v>
+        <v>315.3808444444444</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>109.3599</v>
+        <v>54.67995</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-240.6401</v>
+        <v>-295.32005</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>350</v>
@@ -11183,16 +11183,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>1270.230905555555</v>
+        <v>1120.435955555555</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>577.2872333333333</v>
+        <v>427.4922833333334</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>-722.7127666666667</v>
+        <v>-872.5077166666666</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>1300</v>
@@ -11958,13 +11958,13 @@
         <v>164.4863222222222</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>125.3047</v>
+        <v>62.65235</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>450.7910222222222</v>
+        <v>388.1386722222222</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>125.3047</v>
+        <v>62.65235</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-534.6953</v>
+        <v>-597.34765</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>660</v>
@@ -12009,13 +12009,13 @@
         <v>196.8581111111111</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>116.2968</v>
+        <v>58.1484</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>483.1870722222222</v>
+        <v>425.0386722222222</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>116.2968</v>
+        <v>58.1484</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>-623.7032</v>
+        <v>-681.8516</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>740</v>
@@ -12060,13 +12060,13 @@
         <v>267.9203888888889</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>59.625</v>
+        <v>29.8125</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>626.4730555555556</v>
+        <v>596.6605555555556</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>626.4730555555556</v>
+        <v>596.6605555555556</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>-393.5269444444444</v>
+        <v>-423.3394444444444</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>1020</v>
@@ -12111,13 +12111,13 @@
         <v>236.9039722222222</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>195.75</v>
+        <v>97.875</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>680.2591666666667</v>
+        <v>582.3841666666667</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>680.2591666666667</v>
+        <v>582.3841666666667</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>-39.74083333333328</v>
+        <v>-137.6158333333333</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>720</v>
@@ -12148,16 +12148,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>2240.710316666667</v>
+        <v>1992.222066666667</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1548.333722222222</v>
+        <v>1299.845472222222</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>-1591.666277777778</v>
+        <v>-1840.154527777778</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>3140</v>
@@ -12974,13 +12974,13 @@
         <v>111</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>10.63</v>
+        <v>5.315</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>186.63</v>
+        <v>181.315</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>10.63</v>
+        <v>5.315</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>-439.37</v>
+        <v>-444.685</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>450</v>
@@ -13025,13 +13025,13 @@
         <v>111.5892222222222</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>10.34</v>
+        <v>5.17</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>317.9292222222222</v>
+        <v>312.7592222222223</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>10.34</v>
+        <v>5.17</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-699.66</v>
+        <v>-704.83</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>710</v>
@@ -13113,16 +13113,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1045.462222222222</v>
+        <v>1034.977222222222</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>20.97</v>
+        <v>10.485</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-2349.03</v>
+        <v>-2359.515</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>2370</v>
@@ -13888,13 +13888,13 @@
         <v>90.62005555555555</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>14.6435</v>
+        <v>7.32175</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>247.7774722222222</v>
+        <v>240.4557222222222</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>14.6435</v>
+        <v>7.32175</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-475.3565</v>
+        <v>-482.67825</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>490</v>
@@ -13939,13 +13939,13 @@
         <v>135.3540277777778</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>20.99</v>
+        <v>10.495</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>276.0371944444445</v>
+        <v>265.5421944444445</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>20.99</v>
+        <v>10.495</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-579.01</v>
+        <v>-589.505</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>600</v>
@@ -14041,13 +14041,13 @@
         <v>95.97988888888888</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>8.85</v>
+        <v>4.425</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>283.3643888888889</v>
+        <v>278.9393888888889</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>8.85</v>
+        <v>4.425</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>924.3805879000001</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-481.15</v>
+        <v>-485.575</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>490</v>
@@ -14078,16 +14078,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1058.389333333333</v>
+        <v>1036.147583333333</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>44.4835</v>
+        <v>22.24175</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-2025.5165</v>
+        <v>-2047.75825</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>2070</v>
@@ -14853,13 +14853,13 @@
         <v>65.04662777777777</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>36.9</v>
+        <v>18.45</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>171.9466277777778</v>
+        <v>153.4966277777777</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>36.9</v>
+        <v>18.45</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>-313.1</v>
+        <v>-331.55</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>350</v>
@@ -14904,13 +14904,13 @@
         <v>55.7212</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>74.46000000000001</v>
+        <v>37.23</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>234.3002277777778</v>
+        <v>197.0702277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>74.46000000000001</v>
+        <v>37.23</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>-275.54</v>
+        <v>-312.77</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>350</v>
@@ -14955,13 +14955,13 @@
         <v>47.37872222222222</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>56.439</v>
+        <v>28.2195</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>216.7168611111111</v>
+        <v>188.4973611111111</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>56.439</v>
+        <v>28.2195</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>-293.561</v>
+        <v>-321.7805</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>350</v>
@@ -15006,13 +15006,13 @@
         <v>99.44133333333333</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>36.17</v>
+        <v>18.085</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>222.7752222222222</v>
+        <v>204.6902222222222</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>36.17</v>
+        <v>18.085</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>895.0173386000001</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>-313.83</v>
+        <v>-331.915</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>350</v>
@@ -15043,16 +15043,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>845.7389388888889</v>
+        <v>743.7544388888889</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>203.969</v>
+        <v>101.9845</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>-1196.031</v>
+        <v>-1298.0155</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>1400</v>
@@ -15818,13 +15818,13 @@
         <v>125.6738666666667</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>65.0291</v>
+        <v>32.51455</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>368.1532888888888</v>
+        <v>335.6387388888888</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>65.0291</v>
+        <v>32.51455</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>985.1345503999999</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-484.9709</v>
+        <v>-517.48545</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>550</v>
@@ -15869,13 +15869,13 @@
         <v>103.5712111111111</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>30.92</v>
+        <v>15.46</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>302.5100444444445</v>
+        <v>287.0500444444444</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>30.92</v>
+        <v>15.46</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-419.08</v>
+        <v>-434.54</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>450</v>
@@ -15971,13 +15971,13 @@
         <v>90.53322222222222</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>25.14</v>
+        <v>12.57</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>288.0682111111111</v>
+        <v>275.4982111111111</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>25.14</v>
+        <v>12.57</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-324.86</v>
+        <v>-337.43</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>350</v>
@@ -16008,16 +16008,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>1454.894011111111</v>
+        <v>1394.349461111111</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>617.2515666666667</v>
+        <v>556.7070166666667</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>-1322.748433333333</v>
+        <v>-1383.292983333333</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1940</v>
@@ -16853,13 +16853,13 @@
         <v>36.28805555555556</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>213.6425</v>
+        <v>106.82125</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>424.9305555555555</v>
+        <v>318.1093055555556</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>213.6425</v>
+        <v>106.82125</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>782.1916794999999</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-36.35749999999999</v>
+        <v>-143.17875</v>
       </c>
       <c r="O13" s="11" t="n">
         <v>250</v>
@@ -16904,13 +16904,13 @@
         <v>27</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>385.385</v>
+        <v>271.1925</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>544.3810526000001</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>228.385</v>
+        <v>114.1925</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>0</v>
@@ -16955,13 +16955,13 @@
         <v>35.01533333333333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>165.148</v>
+        <v>82.574</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>410.1633333333333</v>
+        <v>327.5893333333333</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>410.1633333333333</v>
+        <v>327.5893333333333</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>829.8586758000001</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>60.1633333333333</v>
+        <v>-22.41066666666666</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>350</v>
@@ -17006,13 +17006,13 @@
         <v>23.669375</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>186.16965</v>
+        <v>93.08482500000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>422.8678361111112</v>
+        <v>329.7830111111111</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>186.16965</v>
+        <v>93.08482500000001</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>1068.8268976</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>-63.83034999999998</v>
+        <v>-156.915175</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>250</v>
@@ -17043,16 +17043,16 @@
       <c r="G17" s="34" t="n"/>
       <c r="H17" s="34" t="n"/>
       <c r="I17" s="19" t="n">
-        <v>1643.346725</v>
+        <v>1246.67415</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1038.360483333333</v>
+        <v>641.6879083333334</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>188.3604833333334</v>
+        <v>-208.3120916666666</v>
       </c>
       <c r="O17" s="19" t="n">
         <v>850</v>
@@ -17818,13 +17818,13 @@
         <v>82.24316111111111</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>453.6816000000001</v>
+        <v>226.8408</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>696.9247611111111</v>
+        <v>470.0839611111111</v>
       </c>
       <c r="K37" s="17" t="n">
-        <v>453.6816000000001</v>
+        <v>226.8408</v>
       </c>
       <c r="L37" s="33" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>1266.0493153</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>103.6816000000001</v>
+        <v>-123.1592</v>
       </c>
       <c r="O37" s="11" t="n">
         <v>350</v>
@@ -17869,13 +17869,13 @@
         <v>98.42905555555555</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>544.0198</v>
+        <v>272.0099</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>812.4810166666667</v>
+        <v>540.4711166666667</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>544.0198</v>
+        <v>272.0099</v>
       </c>
       <c r="L38" s="33" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>1316.1026725</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>84.01980000000003</v>
+        <v>-187.9901</v>
       </c>
       <c r="O38" s="11" t="n">
         <v>460</v>
@@ -17920,13 +17920,13 @@
         <v>135.1268611111111</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>540.76675</v>
+        <v>270.383375</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>974.8212777777778</v>
+        <v>704.4379027777777</v>
       </c>
       <c r="K39" s="17" t="n">
-        <v>974.8212777777778</v>
+        <v>704.4379027777777</v>
       </c>
       <c r="L39" s="23" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>2027.2795851</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>294.8212777777778</v>
+        <v>24.43790277777771</v>
       </c>
       <c r="O39" s="11" t="n">
         <v>680</v>
@@ -17971,13 +17971,13 @@
         <v>118.4519861111111</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>516.57715</v>
+        <v>258.288575</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>882.6343305555555</v>
+        <v>624.3457555555556</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>882.6343305555555</v>
+        <v>624.3457555555556</v>
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>1729.9528862</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>382.6343305555555</v>
+        <v>124.3457555555556</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>500</v>
@@ -18008,16 +18008,16 @@
       <c r="G41" s="34" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>3366.861386111112</v>
+        <v>2339.338736111111</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>2855.157008333334</v>
+        <v>1827.634358333333</v>
       </c>
       <c r="K41" s="34" t="n"/>
       <c r="L41" s="34" t="n"/>
       <c r="M41" s="34" t="n"/>
       <c r="N41" s="19" t="n">
-        <v>865.1570083333336</v>
+        <v>-162.3656416666668</v>
       </c>
       <c r="O41" s="19" t="n">
         <v>1990</v>
@@ -18783,13 +18783,13 @@
         <v>81.60402777777777</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>316.8725</v>
+        <v>158.43625</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>573.9643055555555</v>
+        <v>415.5280555555555</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>316.8725</v>
+        <v>158.43625</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>1189.1480293</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>-183.1275</v>
+        <v>-341.56375</v>
       </c>
       <c r="O61" s="11" t="n">
         <v>500</v>
@@ -18834,13 +18834,13 @@
         <v>57</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>260.5835</v>
+        <v>130.29175</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>382.5835</v>
+        <v>252.29175</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>260.5835</v>
+        <v>130.29175</v>
       </c>
       <c r="L62" s="33" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>546.831285</v>
       </c>
       <c r="N62" s="11" t="n">
-        <v>10.58350000000002</v>
+        <v>-119.70825</v>
       </c>
       <c r="O62" s="11" t="n">
         <v>250</v>
@@ -18885,13 +18885,13 @@
         <v>55.79461111111111</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>294.643</v>
+        <v>147.3215</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>546.4376111111111</v>
+        <v>399.1161111111111</v>
       </c>
       <c r="K63" s="17" t="n">
-        <v>294.643</v>
+        <v>147.3215</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>880.2301739</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>-175.357</v>
+        <v>-322.6785</v>
       </c>
       <c r="O63" s="11" t="n">
         <v>470</v>
@@ -18936,13 +18936,13 @@
         <v>43.72116666666667</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>216.981</v>
+        <v>108.4905</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>377.1336666666667</v>
+        <v>268.6431666666667</v>
       </c>
       <c r="K64" s="17" t="n">
-        <v>216.981</v>
+        <v>108.4905</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>730.26415</v>
       </c>
       <c r="N64" s="11" t="n">
-        <v>-33.01900000000001</v>
+        <v>-141.5095</v>
       </c>
       <c r="O64" s="11" t="n">
         <v>250</v>
@@ -18973,16 +18973,16 @@
       <c r="G65" s="34" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="19" t="n">
-        <v>1880.119083333333</v>
+        <v>1335.579083333333</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>1089.08</v>
+        <v>544.54</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
       <c r="M65" s="34" t="n"/>
       <c r="N65" s="19" t="n">
-        <v>-380.9200000000001</v>
+        <v>-925.46</v>
       </c>
       <c r="O65" s="19" t="n">
         <v>1470</v>
@@ -19748,13 +19748,13 @@
         <v>44.64336111111111</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>212.43375</v>
+        <v>106.216875</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>399.5910277777778</v>
+        <v>293.3741527777778</v>
       </c>
       <c r="K85" s="17" t="n">
-        <v>212.43375</v>
+        <v>106.216875</v>
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>897.5350923</v>
       </c>
       <c r="N85" s="11" t="n">
-        <v>-137.56625</v>
+        <v>-243.783125</v>
       </c>
       <c r="O85" s="11" t="n">
         <v>350</v>
@@ -19799,13 +19799,13 @@
         <v>67.67701388888889</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>239.42725</v>
+        <v>119.713625</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>426.7974305555556</v>
+        <v>307.0838055555556</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>239.42725</v>
+        <v>119.713625</v>
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>1093.3395627</v>
       </c>
       <c r="N86" s="11" t="n">
-        <v>-110.57275</v>
+        <v>-230.286375</v>
       </c>
       <c r="O86" s="11" t="n">
         <v>350</v>
@@ -19850,13 +19850,13 @@
         <v>37.00930555555556</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>117.6335</v>
+        <v>58.81675000000001</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>331.5011388888889</v>
+        <v>272.6843888888889</v>
       </c>
       <c r="K87" s="17" t="n">
-        <v>117.6335</v>
+        <v>58.81675000000001</v>
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>1076.8521995</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>-232.3665</v>
+        <v>-291.18325</v>
       </c>
       <c r="O87" s="11" t="n">
         <v>350</v>
@@ -19901,13 +19901,13 @@
         <v>47.82327777777778</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>163.0138</v>
+        <v>81.5069</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>389.3715777777778</v>
+        <v>307.8646777777778</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>163.0138</v>
+        <v>81.5069</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>924.3805879</v>
       </c>
       <c r="N88" s="11" t="n">
-        <v>-186.9862</v>
+        <v>-268.4931</v>
       </c>
       <c r="O88" s="11" t="n">
         <v>350</v>
@@ -19938,16 +19938,16 @@
       <c r="G89" s="34" t="n"/>
       <c r="H89" s="34" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>1547.261175</v>
+        <v>1181.007025</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>732.5083</v>
+        <v>366.25415</v>
       </c>
       <c r="K89" s="34" t="n"/>
       <c r="L89" s="34" t="n"/>
       <c r="M89" s="34" t="n"/>
       <c r="N89" s="19" t="n">
-        <v>-667.4917</v>
+        <v>-1033.74585</v>
       </c>
       <c r="O89" s="19" t="n">
         <v>1400</v>
@@ -20713,13 +20713,13 @@
         <v>32.52331388888889</v>
       </c>
       <c r="I109" s="11" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>304.8429638888889</v>
+        <v>203.6831388888889</v>
       </c>
       <c r="K109" s="17" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>568.2616939999999</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>202.31965</v>
+        <v>101.159825</v>
       </c>
       <c r="O109" s="11" t="n">
         <v>0</v>
@@ -20764,13 +20764,13 @@
         <v>27.8606</v>
       </c>
       <c r="I110" s="11" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>347.9304277777778</v>
+        <v>239.9550277777778</v>
       </c>
       <c r="K110" s="17" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>742.7446410999999</v>
       </c>
       <c r="N110" s="11" t="n">
-        <v>215.9508</v>
+        <v>107.9754</v>
       </c>
       <c r="O110" s="11" t="n">
         <v>0</v>
@@ -20815,13 +20815,13 @@
         <v>23.02269444444444</v>
       </c>
       <c r="I111" s="11" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>291.5650833333333</v>
+        <v>213.7434583333333</v>
       </c>
       <c r="K111" s="17" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>640.1299058</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>155.64325</v>
+        <v>77.821625</v>
       </c>
       <c r="O111" s="11" t="n">
         <v>0</v>
@@ -20866,13 +20866,13 @@
         <v>51.054</v>
       </c>
       <c r="I112" s="11" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>373.3598888888889</v>
+        <v>255.7888888888889</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>895.0173385999999</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>235.142</v>
+        <v>117.571</v>
       </c>
       <c r="O112" s="11" t="n">
         <v>0</v>
@@ -20903,16 +20903,16 @@
       <c r="G113" s="34" t="n"/>
       <c r="H113" s="34" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>1317.698363888889</v>
+        <v>913.1705138888889</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>809.0557</v>
+        <v>404.52785</v>
       </c>
       <c r="K113" s="34" t="n"/>
       <c r="L113" s="34" t="n"/>
       <c r="M113" s="34" t="n"/>
       <c r="N113" s="19" t="n">
-        <v>809.0557</v>
+        <v>404.52785</v>
       </c>
       <c r="O113" s="19" t="n">
         <v>0</v>
@@ -21678,13 +21678,13 @@
         <v>64.17026666666666</v>
       </c>
       <c r="I133" s="11" t="n">
-        <v>308.0939</v>
+        <v>154.04695</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>549.7144888888889</v>
+        <v>395.6675388888889</v>
       </c>
       <c r="K133" s="17" t="n">
-        <v>308.0939</v>
+        <v>154.04695</v>
       </c>
       <c r="L133" s="33" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>985.1345504</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>-41.90609999999998</v>
+        <v>-195.95305</v>
       </c>
       <c r="O133" s="11" t="n">
         <v>350</v>
@@ -21729,13 +21729,13 @@
         <v>53.11893888888889</v>
       </c>
       <c r="I134" s="11" t="n">
-        <v>267.0609</v>
+        <v>133.53045</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>488.1986722222222</v>
+        <v>354.6682222222222</v>
       </c>
       <c r="K134" s="17" t="n">
-        <v>267.0609</v>
+        <v>133.53045</v>
       </c>
       <c r="L134" s="33" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>848.0292051</v>
       </c>
       <c r="N134" s="11" t="n">
-        <v>-82.9391</v>
+        <v>-216.46955</v>
       </c>
       <c r="O134" s="11" t="n">
         <v>350</v>
@@ -21780,13 +21780,13 @@
         <v>42</v>
       </c>
       <c r="I135" s="11" t="n">
-        <v>196.27325</v>
+        <v>98.13662500000001</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>650.4357166666666</v>
+        <v>552.2990916666666</v>
       </c>
       <c r="K135" s="17" t="n">
-        <v>650.4357166666666</v>
+        <v>552.2990916666666</v>
       </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>1357.7450656</v>
       </c>
       <c r="N135" s="11" t="n">
-        <v>200.4357166666666</v>
+        <v>102.2990916666666</v>
       </c>
       <c r="O135" s="11" t="n">
         <v>450</v>
@@ -21831,13 +21831,13 @@
         <v>45.26661111111111</v>
       </c>
       <c r="I136" s="11" t="n">
-        <v>201.5395</v>
+        <v>100.76975</v>
       </c>
       <c r="J136" s="11" t="n">
-        <v>419.2011</v>
+        <v>318.43135</v>
       </c>
       <c r="K136" s="17" t="n">
-        <v>201.5395</v>
+        <v>100.76975</v>
       </c>
       <c r="L136" s="33" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>839.0993611</v>
       </c>
       <c r="N136" s="11" t="n">
-        <v>-48.4605</v>
+        <v>-149.23025</v>
       </c>
       <c r="O136" s="11" t="n">
         <v>250</v>
@@ -21868,16 +21868,16 @@
       <c r="G137" s="34" t="n"/>
       <c r="H137" s="34" t="n"/>
       <c r="I137" s="19" t="n">
-        <v>2107.549977777778</v>
+        <v>1621.066202777778</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>1427.130016666667</v>
+        <v>940.6462416666667</v>
       </c>
       <c r="K137" s="34" t="n"/>
       <c r="L137" s="34" t="n"/>
       <c r="M137" s="34" t="n"/>
       <c r="N137" s="19" t="n">
-        <v>27.13001666666673</v>
+        <v>-459.3537583333333</v>
       </c>
       <c r="O137" s="19" t="n">
         <v>1400</v>
@@ -22619,13 +22619,13 @@
         <v>20.45</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>275.185</v>
+        <v>137.5925</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>470.635</v>
+        <v>333.0425</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>275.185</v>
+        <v>137.5925</v>
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         </is>
       </c>
       <c r="M13" s="11" t="n">
-        <v>25.185</v>
+        <v>-112.4075</v>
       </c>
       <c r="N13" s="11" t="n">
         <v>250</v>
@@ -22667,13 +22667,13 @@
         <v>15.84277777777778</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>306.43</v>
+        <v>153.215</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>452.2727777777778</v>
+        <v>299.0577777777778</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>306.43</v>
+        <v>153.215</v>
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         </is>
       </c>
       <c r="M14" s="11" t="n">
-        <v>306.43</v>
+        <v>153.215</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>0</v>
@@ -22715,13 +22715,13 @@
         <v>12.50277777777778</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>252.276</v>
+        <v>126.138</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>474.7787777777777</v>
+        <v>348.6407777777778</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>474.7787777777777</v>
+        <v>348.6407777777778</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         </is>
       </c>
       <c r="M15" s="11" t="n">
-        <v>124.7787777777777</v>
+        <v>-1.359222222222229</v>
       </c>
       <c r="N15" s="11" t="n">
         <v>350</v>
@@ -22763,13 +22763,13 @@
         <v>34.71108333333333</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>153.6195</v>
+        <v>76.80975000000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>401.3593944444444</v>
+        <v>324.5496444444444</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>153.6195</v>
+        <v>76.80975000000001</v>
       </c>
       <c r="L16" s="33" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-196.3805</v>
+        <v>-273.19025</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>350</v>
@@ -22799,11 +22799,11 @@
       <c r="I17" s="34" t="n"/>
       <c r="J17" s="34" t="n"/>
       <c r="K17" s="19" t="n">
-        <v>1210.013277777778</v>
+        <v>716.2580277777778</v>
       </c>
       <c r="L17" s="34" t="n"/>
       <c r="M17" s="19" t="n">
-        <v>260.0132777777778</v>
+        <v>-233.7419722222222</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>950</v>
@@ -23162,13 +23162,13 @@
         <v>38.47352777777778</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>656.7538000000001</v>
+        <v>328.3769</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>856.2273277777779</v>
+        <v>527.8504277777778</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>656.7538000000001</v>
+        <v>328.3769</v>
       </c>
       <c r="L28" s="33" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="M28" s="11" t="n">
-        <v>406.7538000000001</v>
+        <v>78.37690000000003</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>250</v>
@@ -23210,13 +23210,13 @@
         <v>30.46093333333333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>855.446</v>
+        <v>427.723</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>1055.939094444444</v>
+        <v>628.2160944444445</v>
       </c>
       <c r="K29" s="17" t="n">
-        <v>855.446</v>
+        <v>427.723</v>
       </c>
       <c r="L29" s="33" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         </is>
       </c>
       <c r="M29" s="11" t="n">
-        <v>605.446</v>
+        <v>177.723</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>250</v>
@@ -23258,13 +23258,13 @@
         <v>18.89583333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>962.2835000000001</v>
+        <v>481.1417500000001</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>1280.107</v>
+        <v>798.96525</v>
       </c>
       <c r="K30" s="17" t="n">
-        <v>1280.107</v>
+        <v>798.96525</v>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         </is>
       </c>
       <c r="M30" s="11" t="n">
-        <v>930.107</v>
+        <v>448.96525</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>350</v>
@@ -23306,13 +23306,13 @@
         <v>10</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>641.6543</v>
+        <v>320.82715</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>899.2594944444445</v>
+        <v>578.4323444444444</v>
       </c>
       <c r="K31" s="17" t="n">
-        <v>899.2594944444445</v>
+        <v>578.4323444444444</v>
       </c>
       <c r="L31" s="23" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         </is>
       </c>
       <c r="M31" s="11" t="n">
-        <v>549.2594944444445</v>
+        <v>228.4323444444444</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>350</v>
@@ -23342,11 +23342,11 @@
       <c r="I32" s="34" t="n"/>
       <c r="J32" s="34" t="n"/>
       <c r="K32" s="19" t="n">
-        <v>3691.566294444445</v>
+        <v>2133.497494444444</v>
       </c>
       <c r="L32" s="34" t="n"/>
       <c r="M32" s="19" t="n">
-        <v>2491.566294444445</v>
+        <v>933.4974944444443</v>
       </c>
       <c r="N32" s="19" t="n">
         <v>1200</v>
@@ -23705,13 +23705,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>633.745</v>
+        <v>316.8725</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>809.2327777777778</v>
+        <v>492.3602777777778</v>
       </c>
       <c r="K43" s="17" t="n">
-        <v>633.745</v>
+        <v>316.8725</v>
       </c>
       <c r="L43" s="33" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="M43" s="11" t="n">
-        <v>383.745</v>
+        <v>66.8725</v>
       </c>
       <c r="N43" s="11" t="n">
         <v>250</v>
@@ -23753,13 +23753,13 @@
         <v>2</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>499.907</v>
+        <v>249.9535</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>566.9069999999999</v>
+        <v>316.9535</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>499.907</v>
+        <v>249.9535</v>
       </c>
       <c r="L44" s="33" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         </is>
       </c>
       <c r="M44" s="11" t="n">
-        <v>499.907</v>
+        <v>249.9535</v>
       </c>
       <c r="N44" s="11" t="n">
         <v>0</v>
@@ -23801,13 +23801,13 @@
         <v>2.241111111111111</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>568.606</v>
+        <v>284.303</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>766.8471111111111</v>
+        <v>482.5441111111111</v>
       </c>
       <c r="K45" s="17" t="n">
-        <v>568.606</v>
+        <v>284.303</v>
       </c>
       <c r="L45" s="33" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="M45" s="11" t="n">
-        <v>568.606</v>
+        <v>284.303</v>
       </c>
       <c r="N45" s="11" t="n">
         <v>0</v>
@@ -23849,13 +23849,13 @@
         <v>0</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>433.962</v>
+        <v>216.981</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>550.3935</v>
+        <v>333.4125</v>
       </c>
       <c r="K46" s="17" t="n">
-        <v>433.962</v>
+        <v>216.981</v>
       </c>
       <c r="L46" s="33" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         </is>
       </c>
       <c r="M46" s="11" t="n">
-        <v>433.962</v>
+        <v>216.981</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>0</v>
@@ -23885,11 +23885,11 @@
       <c r="I47" s="34" t="n"/>
       <c r="J47" s="34" t="n"/>
       <c r="K47" s="19" t="n">
-        <v>2136.22</v>
+        <v>1068.11</v>
       </c>
       <c r="L47" s="34" t="n"/>
       <c r="M47" s="19" t="n">
-        <v>1886.22</v>
+        <v>818.1100000000001</v>
       </c>
       <c r="N47" s="19" t="n">
         <v>250</v>
@@ -24248,13 +24248,13 @@
         <v>3.960388888888889</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>395.5805</v>
+        <v>197.79025</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>542.0548055555556</v>
+        <v>344.2645555555556</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>395.5805</v>
+        <v>197.79025</v>
       </c>
       <c r="L58" s="33" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         </is>
       </c>
       <c r="M58" s="11" t="n">
-        <v>395.5805</v>
+        <v>197.79025</v>
       </c>
       <c r="N58" s="11" t="n">
         <v>0</v>
@@ -24296,13 +24296,13 @@
         <v>4.499444444444444</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>436.8745</v>
+        <v>218.43725</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>561.0671111111111</v>
+        <v>342.6298611111111</v>
       </c>
       <c r="K59" s="17" t="n">
-        <v>436.8745</v>
+        <v>218.43725</v>
       </c>
       <c r="L59" s="33" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         </is>
       </c>
       <c r="M59" s="11" t="n">
-        <v>436.8745</v>
+        <v>218.43725</v>
       </c>
       <c r="N59" s="11" t="n">
         <v>0</v>
@@ -24344,13 +24344,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>235.267</v>
+        <v>117.6335</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>412.1253333333334</v>
+        <v>294.4918333333334</v>
       </c>
       <c r="K60" s="17" t="n">
-        <v>235.267</v>
+        <v>117.6335</v>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         </is>
       </c>
       <c r="M60" s="11" t="n">
-        <v>235.267</v>
+        <v>117.6335</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>0</v>
@@ -24392,13 +24392,13 @@
         <v>3.266666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>308.3276</v>
+        <v>154.1638</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>490.1287666666667</v>
+        <v>335.9649666666667</v>
       </c>
       <c r="K61" s="17" t="n">
-        <v>308.3276</v>
+        <v>154.1638</v>
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         </is>
       </c>
       <c r="M61" s="11" t="n">
-        <v>308.3276</v>
+        <v>154.1638</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>0</v>
@@ -24428,11 +24428,11 @@
       <c r="I62" s="34" t="n"/>
       <c r="J62" s="34" t="n"/>
       <c r="K62" s="19" t="n">
-        <v>1376.0496</v>
+        <v>688.0248</v>
       </c>
       <c r="L62" s="34" t="n"/>
       <c r="M62" s="19" t="n">
-        <v>1376.0496</v>
+        <v>688.0248</v>
       </c>
       <c r="N62" s="19" t="n">
         <v>0</v>
@@ -24791,13 +24791,13 @@
         <v>8.716666666666667</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>330.8393</v>
+        <v>165.41965</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>409.5559666666667</v>
+        <v>244.1363166666667</v>
       </c>
       <c r="K73" s="17" t="n">
-        <v>330.8393</v>
+        <v>165.41965</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="n">
-        <v>330.8393</v>
+        <v>165.41965</v>
       </c>
       <c r="N73" s="11" t="n">
         <v>0</v>
@@ -24839,13 +24839,13 @@
         <v>27.35</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>282.9816</v>
+        <v>141.4908</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>414.4506277777778</v>
+        <v>272.9598277777778</v>
       </c>
       <c r="K74" s="17" t="n">
-        <v>282.9816</v>
+        <v>141.4908</v>
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         </is>
       </c>
       <c r="M74" s="11" t="n">
-        <v>282.9816</v>
+        <v>141.4908</v>
       </c>
       <c r="N74" s="11" t="n">
         <v>0</v>
@@ -24887,13 +24887,13 @@
         <v>17.6775</v>
       </c>
       <c r="I75" s="11" t="n">
-        <v>198.4085</v>
+        <v>99.20425</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>328.9851388888889</v>
+        <v>229.7808888888889</v>
       </c>
       <c r="K75" s="17" t="n">
-        <v>198.4085</v>
+        <v>99.20425</v>
       </c>
       <c r="L75" s="33" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         </is>
       </c>
       <c r="M75" s="11" t="n">
-        <v>198.4085</v>
+        <v>99.20425</v>
       </c>
       <c r="N75" s="11" t="n">
         <v>0</v>
@@ -24935,13 +24935,13 @@
         <v>14.04722222222222</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>397.944</v>
+        <v>198.972</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>499.1551111111111</v>
+        <v>300.1831111111111</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>397.944</v>
+        <v>198.972</v>
       </c>
       <c r="L76" s="33" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         </is>
       </c>
       <c r="M76" s="11" t="n">
-        <v>397.944</v>
+        <v>198.972</v>
       </c>
       <c r="N76" s="11" t="n">
         <v>0</v>
@@ -24971,11 +24971,11 @@
       <c r="I77" s="34" t="n"/>
       <c r="J77" s="34" t="n"/>
       <c r="K77" s="19" t="n">
-        <v>1210.1734</v>
+        <v>605.0867000000001</v>
       </c>
       <c r="L77" s="34" t="n"/>
       <c r="M77" s="19" t="n">
-        <v>1210.1734</v>
+        <v>605.0867000000001</v>
       </c>
       <c r="N77" s="19" t="n">
         <v>0</v>
@@ -25334,13 +25334,13 @@
         <v>15.22545555555556</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>486.1296</v>
+        <v>243.0648</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>678.8053777777777</v>
+        <v>435.7405777777777</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>486.1296</v>
+        <v>243.0648</v>
       </c>
       <c r="L88" s="33" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="M88" s="11" t="n">
-        <v>486.1296</v>
+        <v>243.0648</v>
       </c>
       <c r="N88" s="11" t="n">
         <v>0</v>
@@ -25382,13 +25382,13 @@
         <v>6</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>472.2818</v>
+        <v>236.1409</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>646.3006333333334</v>
+        <v>410.1597333333333</v>
       </c>
       <c r="K89" s="17" t="n">
-        <v>472.2818</v>
+        <v>236.1409</v>
       </c>
       <c r="L89" s="33" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M89" s="11" t="n">
-        <v>472.2818</v>
+        <v>236.1409</v>
       </c>
       <c r="N89" s="11" t="n">
         <v>0</v>
@@ -25430,13 +25430,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="11" t="n">
-        <v>392.5465</v>
+        <v>196.27325</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>804.7089666666667</v>
+        <v>608.4357166666666</v>
       </c>
       <c r="K90" s="17" t="n">
-        <v>804.7089666666667</v>
+        <v>608.4357166666666</v>
       </c>
       <c r="L90" s="23" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         </is>
       </c>
       <c r="M90" s="11" t="n">
-        <v>454.7089666666667</v>
+        <v>258.4357166666666</v>
       </c>
       <c r="N90" s="11" t="n">
         <v>350</v>
@@ -25478,13 +25478,13 @@
         <v>6</v>
       </c>
       <c r="I91" s="11" t="n">
-        <v>352.799</v>
+        <v>176.3995</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>531.193988888889</v>
+        <v>354.7944888888889</v>
       </c>
       <c r="K91" s="17" t="n">
-        <v>352.799</v>
+        <v>176.3995</v>
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         </is>
       </c>
       <c r="M91" s="11" t="n">
-        <v>352.799</v>
+        <v>176.3995</v>
       </c>
       <c r="N91" s="11" t="n">
         <v>0</v>
@@ -25514,11 +25514,11 @@
       <c r="I92" s="34" t="n"/>
       <c r="J92" s="34" t="n"/>
       <c r="K92" s="19" t="n">
-        <v>2115.919366666667</v>
+        <v>1264.040916666667</v>
       </c>
       <c r="L92" s="34" t="n"/>
       <c r="M92" s="19" t="n">
-        <v>1765.919366666667</v>
+        <v>914.0409166666666</v>
       </c>
       <c r="N92" s="19" t="n">
         <v>350</v>

--- a/output/Bonus_Plan_FINAL.xlsx
+++ b/output/Bonus_Plan_FINAL.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TODAY: $12,220 paid out under current plan. NEW PLAN with the tiered-premium structure: $1,675 today (most agents do not yet write $45k NB consistently), $3,450 if half the rewrites become renewals, $6,905 if all rewrites had been renewals. The new plan pays LESS when agents are under the entry tier and rewards the SHIFT to writing more premium AND retaining the book.</t>
+          <t>TODAY: $12,220 paid out under current plan. NEW PLAN with the tiered-premium structure: $1,675 today (most agents do not yet write $45k NB consistently), $3,875 if half the rewrites become renewals, $7,975 if all rewrites had been renewals. The new plan pays LESS when agents are under the entry tier and rewards the SHIFT to writing more premium AND retaining the book.</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Same tier ladder as NB, paying HALF: T1=$125, T2=$187.50, T3=$262.50, T4=$362.50, T5=$500. Above $100k: +$25/$5k. No separate floor - gated by NB $45k minimum.</t>
+          <t>Same tier breakpoints as NB, pays about half: T1=$100, T2=$200, T3=$275, T4=$350, T5=$500. Above $100k: +$25/$5k. No separate floor - gated by NB $45k minimum.</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>5 tiers by monthly REN written premium starting at $25k: T1 $25k=$200, T2 $45k=$300, T3 $65k=$420, T4 $85k=$580, T5 $100k=$800. Above $100k: +$40 per $5k. Gate = retention rate &gt;= 30%.</t>
+          <t>5 tiers by monthly REN written premium starting at $25k: T1 $25k=$250, T2 $40k=$350, T3 $65k=$450, T4 $80k=$550, T5 $100k=$800. Above $100k: +$40 per $5k. Gate = retention rate &gt;= 30%.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t>The 4-month modeled cost: Current $12,220, New plan $6,905 at 100% FLIP (still cheaper than today AND aligns pay with the right behavior).</t>
+          <t>The 4-month modeled cost: Current $12,220, New plan $7,975 at 100% FLIP (still cheaper than today AND aligns pay with the right behavior).</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>Same breakpoints as NB, pays HALF: T1=$125 | T2=$187.50 | T3=$262.50 | T4=$362.50 | T5=$500. Above $100k: +$25 per $5k.</t>
+          <t>Same breakpoints as NB, pays ~half: T1=$100 | T2=$200 | T3=$275 | T4=$350 | T5=$500. Above $100k: +$25 per $5k.</t>
         </is>
       </c>
       <c r="C5" s="39" t="n"/>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>Own breakpoints: T1 $25k=$200 | T2 $45k=$300 | T3 $65k=$420 | T4 $85k=$580 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
+          <t>Own breakpoints: T1 $25k=$250 | T2 $40k=$350 | T3 $65k=$450 | T4 $80k=$550 | T5 $100k=$800. Above $100k: +$40 per $5k.</t>
         </is>
       </c>
       <c r="C6" s="39" t="n"/>
@@ -3730,17 +3730,17 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>$125 / $187.50 / $262.50 / $362.50 / $500</t>
+          <t>$100 / $200 / $275 / $350 / $500</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>Same breakpoints as NB ($45k-$100k), pays HALF of NB.</t>
+          <t>Same breakpoints as NB ($45k-$100k), pays roughly half of NB at each tier.</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>Rewrites pay half of new business.</t>
+          <t>Rewrites pay about half of new business.</t>
         </is>
       </c>
     </row>
@@ -3774,17 +3774,17 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>$200 / $300 / $420 / $580 / $800</t>
+          <t>$250 / $350 / $450 / $550 / $800</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Own breakpoints at $25k / $45k / $65k / $85k / $100k REN written premium.</t>
+          <t>Own breakpoints at $25k / $40k / $65k / $80k / $100k REN written premium.</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Pays roughly 0.80x of NB - the midpoint between NB and RWR with a slight boost.</t>
+          <t>Pays roughly the intersection between NB and RWR, with a slight boost.</t>
         </is>
       </c>
     </row>
@@ -3960,15 +3960,18 @@
   <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4047,13 +4050,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>2975</v>
+        <v>2925</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3450</v>
+        <v>3875</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>6905</v>
+        <v>7975</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4071,10 +4074,10 @@
         <v>1675</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3450</v>
+        <v>3875</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>6905</v>
+        <v>7975</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
@@ -4109,35 +4112,50 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>NB #</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>RWR</t>
+          <t>NB $</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RWR #</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
+          <t>RWR $</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>REN #</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>REN $</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>Plan no-min</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>Plan WITH MIN</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>vs Current</t>
         </is>
@@ -4157,22 +4175,31 @@
       <c r="C14" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
+        <v>38611.42</v>
+      </c>
+      <c r="E14" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="F14" s="16" t="n">
+        <v>27518.5</v>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="H14" s="16" t="n">
+        <v>7605</v>
+      </c>
+      <c r="I14" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="16" t="n">
+      <c r="J14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4190,22 +4217,31 @@
       <c r="C15" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="F15" s="16" t="n">
+        <v>65675.38</v>
+      </c>
+      <c r="G15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="H15" s="16" t="n">
+        <v>12530.47</v>
+      </c>
+      <c r="I15" s="16" t="n">
         <v>660</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="16" t="n">
+      <c r="J15" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16" t="n">
         <v>-660</v>
       </c>
     </row>
@@ -4223,22 +4259,31 @@
       <c r="C16" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
+        <v>37039</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="16" t="n">
+        <v>63374.5</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
         <v>740</v>
       </c>
-      <c r="G16" s="11" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="16" t="n">
+      <c r="J16" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
         <v>-740</v>
       </c>
     </row>
@@ -4256,22 +4301,31 @@
       <c r="C17" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
+        <v>28525.05</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="F17" s="16" t="n">
+        <v>39558.05</v>
+      </c>
+      <c r="G17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="H17" s="16" t="n">
+        <v>1464.35</v>
+      </c>
+      <c r="I17" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="16" t="n">
+      <c r="J17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -4289,22 +4343,31 @@
       <c r="C18" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
+        <v>15503.9</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="F18" s="16" t="n">
+        <v>33083.93</v>
+      </c>
+      <c r="G18" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="H18" s="16" t="n">
+        <v>3690</v>
+      </c>
+      <c r="I18" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="16" t="n">
+      <c r="J18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4322,22 +4385,31 @@
       <c r="C19" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
+        <v>28605.29</v>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="F19" s="16" t="n">
+        <v>48612.96</v>
+      </c>
+      <c r="G19" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="H19" s="16" t="n">
+        <v>6502.91</v>
+      </c>
+      <c r="I19" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="16" t="n">
+      <c r="J19" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="16" t="n">
         <v>-550</v>
       </c>
     </row>
@@ -4355,22 +4427,31 @@
       <c r="C20" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
+        <v>25367</v>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="F20" s="16" t="n">
+        <v>30643</v>
+      </c>
+      <c r="G20" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="H20" s="16" t="n">
+        <v>7517</v>
+      </c>
+      <c r="I20" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="16" t="n">
+      <c r="J20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -4388,22 +4469,31 @@
       <c r="C21" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="F21" s="16" t="n">
+        <v>85544.60000000001</v>
+      </c>
+      <c r="G21" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="H21" s="16" t="n">
+        <v>11629.68</v>
+      </c>
+      <c r="I21" s="16" t="n">
         <v>740</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>362.5</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="16" t="n">
+      <c r="J21" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16" t="n">
         <v>-740</v>
       </c>
     </row>
@@ -4421,22 +4511,31 @@
       <c r="C22" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
+        <v>7659.5</v>
+      </c>
+      <c r="E22" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="F22" s="16" t="n">
+        <v>49990.7</v>
+      </c>
+      <c r="G22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="H22" s="16" t="n">
+        <v>1063</v>
+      </c>
+      <c r="I22" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="G22" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="16" t="n">
+      <c r="J22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
         <v>-450</v>
       </c>
     </row>
@@ -4454,22 +4553,31 @@
       <c r="C23" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
+        <v>22247.7</v>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="F23" s="16" t="n">
+        <v>43687.45</v>
+      </c>
+      <c r="G23" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="H23" s="16" t="n">
+        <v>2099</v>
+      </c>
+      <c r="I23" s="16" t="n">
         <v>600</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="16" t="n">
+      <c r="J23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="16" t="n">
         <v>-600</v>
       </c>
     </row>
@@ -4487,22 +4595,31 @@
       <c r="C24" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
+        <v>19414.25</v>
+      </c>
+      <c r="E24" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="F24" s="16" t="n">
+        <v>28298.16</v>
+      </c>
+      <c r="G24" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="H24" s="16" t="n">
+        <v>7446</v>
+      </c>
+      <c r="I24" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="16" t="n">
+      <c r="J24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4520,22 +4637,31 @@
       <c r="C25" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="E25" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="F25" s="16" t="n">
+        <v>47228.18</v>
+      </c>
+      <c r="G25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="H25" s="16" t="n">
+        <v>3092</v>
+      </c>
+      <c r="I25" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>125</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="16" t="n">
+      <c r="J25" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="16" t="n">
         <v>-450</v>
       </c>
     </row>
@@ -4553,22 +4679,31 @@
       <c r="C26" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
+        <v>46523.37</v>
+      </c>
+      <c r="E26" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="F26" s="16" t="n">
+        <v>25227.6</v>
+      </c>
+      <c r="G26" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="H26" s="16" t="n">
+        <v>3901</v>
+      </c>
+      <c r="I26" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>250</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="K26" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="I26" s="16" t="n">
+      <c r="L26" s="16" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4586,23 +4721,32 @@
       <c r="C27" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
+        <v>52434.9</v>
+      </c>
+      <c r="E27" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="F27" s="16" t="n">
+        <v>96228.35000000001</v>
+      </c>
+      <c r="G27" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="H27" s="16" t="n">
+        <v>5962.5</v>
+      </c>
+      <c r="I27" s="16" t="n">
         <v>1020</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="I27" s="16" t="n">
-        <v>-407.5</v>
+      <c r="J27" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <v>-420</v>
       </c>
     </row>
     <row r="28">
@@ -4619,22 +4763,31 @@
       <c r="C28" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="F28" s="16" t="n">
+        <v>56860.6</v>
+      </c>
+      <c r="G28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="H28" s="16" t="n">
+        <v>1034</v>
+      </c>
+      <c r="I28" s="16" t="n">
         <v>710</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="16" t="n">
+      <c r="J28" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
         <v>-710</v>
       </c>
     </row>
@@ -4652,22 +4805,31 @@
       <c r="C29" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="16" t="n">
+        <v>31269</v>
+      </c>
+      <c r="E29" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="E29" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" s="16" t="n">
+        <v>23526.7</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="16" t="n">
+      <c r="J29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="16" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -4685,22 +4847,31 @@
       <c r="C30" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
+        <v>17843.69</v>
+      </c>
+      <c r="E30" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="F30" s="16" t="n">
+        <v>19840.85</v>
+      </c>
+      <c r="G30" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="H30" s="16" t="n">
+        <v>5643.9</v>
+      </c>
+      <c r="I30" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="16" t="n">
+      <c r="J30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4718,22 +4889,31 @@
       <c r="C31" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
+        <v>68546.22</v>
+      </c>
+      <c r="E31" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E31" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" s="16" t="n">
+        <v>39254.65</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="16" t="n">
         <v>590</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="J31" s="11" t="n">
         <v>375</v>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="K31" s="17" t="n">
         <v>375</v>
       </c>
-      <c r="I31" s="16" t="n">
+      <c r="L31" s="16" t="n">
         <v>-215</v>
       </c>
     </row>
@@ -4751,22 +4931,31 @@
       <c r="C32" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
+        <v>37825.93</v>
+      </c>
+      <c r="E32" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="F32" s="16" t="n">
+        <v>15361.95</v>
+      </c>
+      <c r="G32" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="H32" s="16" t="n">
+        <v>10935.99</v>
+      </c>
+      <c r="I32" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="16" t="n">
+      <c r="J32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4784,23 +4973,32 @@
       <c r="C33" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="16" t="n">
+        <v>49689.35</v>
+      </c>
+      <c r="E33" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="F33" s="16" t="n">
+        <v>64165.43</v>
+      </c>
+      <c r="G33" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="H33" s="16" t="n">
+        <v>19575</v>
+      </c>
+      <c r="I33" s="16" t="n">
         <v>720</v>
       </c>
-      <c r="G33" s="11" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="H33" s="17" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>-282.5</v>
+      <c r="J33" s="11" t="n">
+        <v>450</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="L33" s="16" t="n">
+        <v>-270</v>
       </c>
     </row>
     <row r="34">
@@ -4817,22 +5015,31 @@
       <c r="C34" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
+        <v>19288.35</v>
+      </c>
+      <c r="E34" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="E34" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="F34" s="16" t="n">
+        <v>43396.2</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="16" t="n">
         <v>470</v>
       </c>
-      <c r="G34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="16" t="n">
+      <c r="J34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="n">
         <v>-470</v>
       </c>
     </row>
@@ -4850,22 +5057,31 @@
       <c r="C35" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
+        <v>29581.05</v>
+      </c>
+      <c r="E35" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="F35" s="16" t="n">
+        <v>30832.76</v>
+      </c>
+      <c r="G35" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="H35" s="16" t="n">
+        <v>885</v>
+      </c>
+      <c r="I35" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="G35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="16" t="n">
+      <c r="J35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="16" t="n">
         <v>-490</v>
       </c>
     </row>
@@ -4883,22 +5099,31 @@
       <c r="C36" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
+        <v>14099</v>
+      </c>
+      <c r="E36" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="E36" s="15" t="n">
+      <c r="F36" s="16" t="n">
+        <v>39794.4</v>
+      </c>
+      <c r="G36" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="H36" s="16" t="n">
+        <v>3617</v>
+      </c>
+      <c r="I36" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="16" t="n">
+      <c r="J36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4916,22 +5141,31 @@
       <c r="C37" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
+        <v>29755.49</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="F37" s="16" t="n">
+        <v>35279.9</v>
+      </c>
+      <c r="G37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="H37" s="16" t="n">
+        <v>2514</v>
+      </c>
+      <c r="I37" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="16" t="n">
+      <c r="J37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -4941,16 +5175,16 @@
           <t>REAL 4-MONTH TOTAL (6 agents)</t>
         </is>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="I38" s="19" t="n">
         <v>12220</v>
       </c>
-      <c r="G38" s="19" t="n">
-        <v>2975</v>
-      </c>
-      <c r="H38" s="19" t="n">
+      <c r="J38" s="19" t="n">
+        <v>2925</v>
+      </c>
+      <c r="K38" s="19" t="n">
         <v>1675</v>
       </c>
-      <c r="I38" s="19" t="n">
+      <c r="L38" s="19" t="n">
         <v>-10545</v>
       </c>
     </row>
@@ -4974,35 +5208,50 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>NB #</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>RWR</t>
+          <t>NB $</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RWR #</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
+          <t>RWR $</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>REN #</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>REN $</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>Plan no-min</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>Plan WITH MIN</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>vs Current</t>
         </is>
@@ -5022,22 +5271,31 @@
       <c r="C42" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
+        <v>38611.42</v>
+      </c>
+      <c r="E42" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E42" s="15" t="n">
+      <c r="F42" s="16" t="n">
+        <v>13759.25</v>
+      </c>
+      <c r="G42" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="H42" s="16" t="n">
+        <v>21364.25</v>
+      </c>
+      <c r="I42" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="16" t="n">
+      <c r="J42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -5055,23 +5313,32 @@
       <c r="C43" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
+        <v>40249.26</v>
+      </c>
+      <c r="E43" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E43" s="15" t="n">
+      <c r="F43" s="16" t="n">
+        <v>32837.69</v>
+      </c>
+      <c r="G43" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="H43" s="16" t="n">
+        <v>45368.16</v>
+      </c>
+      <c r="I43" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G43" s="11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H43" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>-50</v>
+      <c r="J43" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="L43" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5088,23 +5355,32 @@
       <c r="C44" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="D44" s="15" t="n">
-        <v>24</v>
+      <c r="D44" s="16" t="n">
+        <v>37039</v>
       </c>
       <c r="E44" s="15" t="n">
         <v>24</v>
       </c>
       <c r="F44" s="16" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>31687.25</v>
+      </c>
+      <c r="I44" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="G44" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H44" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I44" s="16" t="n">
-        <v>-300</v>
+      <c r="J44" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>-250</v>
       </c>
     </row>
     <row r="45">
@@ -5121,22 +5397,31 @@
       <c r="C45" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
+        <v>28525.05</v>
+      </c>
+      <c r="E45" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="F45" s="16" t="n">
+        <v>19779.025</v>
+      </c>
+      <c r="G45" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="H45" s="16" t="n">
+        <v>21243.375</v>
+      </c>
+      <c r="I45" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="16" t="n">
+      <c r="J45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -5154,22 +5439,31 @@
       <c r="C46" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
+        <v>15503.9</v>
+      </c>
+      <c r="E46" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="F46" s="16" t="n">
+        <v>16541.965</v>
+      </c>
+      <c r="G46" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="F46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="17" t="n">
-        <v>0</v>
+      <c r="H46" s="16" t="n">
+        <v>20231.965</v>
       </c>
       <c r="I46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5187,23 +5481,32 @@
       <c r="C47" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
+        <v>28605.29</v>
+      </c>
+      <c r="E47" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E47" s="15" t="n">
+      <c r="F47" s="16" t="n">
+        <v>24306.48</v>
+      </c>
+      <c r="G47" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="H47" s="16" t="n">
+        <v>30809.39</v>
+      </c>
+      <c r="I47" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G47" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H47" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I47" s="16" t="n">
-        <v>-150</v>
+      <c r="J47" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="48">
@@ -5220,22 +5523,31 @@
       <c r="C48" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
+        <v>25367</v>
+      </c>
+      <c r="E48" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E48" s="15" t="n">
+      <c r="F48" s="16" t="n">
+        <v>15321.5</v>
+      </c>
+      <c r="G48" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="17" t="n">
-        <v>0</v>
+      <c r="H48" s="16" t="n">
+        <v>22838.5</v>
       </c>
       <c r="I48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5253,23 +5565,32 @@
       <c r="C49" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
+        <v>30057.89</v>
+      </c>
+      <c r="E49" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E49" s="15" t="n">
+      <c r="F49" s="16" t="n">
+        <v>42772.3</v>
+      </c>
+      <c r="G49" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="H49" s="16" t="n">
+        <v>54401.98</v>
+      </c>
+      <c r="I49" s="16" t="n">
         <v>460</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H49" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="I49" s="16" t="n">
-        <v>-160</v>
+      <c r="J49" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="L49" s="16" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="50">
@@ -5286,23 +5607,32 @@
       <c r="C50" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="D50" s="15" t="n">
-        <v>19</v>
+      <c r="D50" s="16" t="n">
+        <v>7659.5</v>
       </c>
       <c r="E50" s="15" t="n">
         <v>19</v>
       </c>
       <c r="F50" s="16" t="n">
+        <v>24995.35</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>26058.35</v>
+      </c>
+      <c r="I50" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G50" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H50" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I50" s="16" t="n">
-        <v>-50</v>
+      <c r="J50" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5319,22 +5649,31 @@
       <c r="C51" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
+        <v>22247.7</v>
+      </c>
+      <c r="E51" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="F51" s="16" t="n">
+        <v>21843.725</v>
+      </c>
+      <c r="G51" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="H51" s="16" t="n">
+        <v>23942.725</v>
+      </c>
+      <c r="I51" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="16" t="n">
+      <c r="J51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -5352,22 +5691,31 @@
       <c r="C52" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
+        <v>19414.25</v>
+      </c>
+      <c r="E52" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="E52" s="15" t="n">
+      <c r="F52" s="16" t="n">
+        <v>14149.08</v>
+      </c>
+      <c r="G52" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="17" t="n">
-        <v>0</v>
+      <c r="H52" s="16" t="n">
+        <v>21595.08</v>
       </c>
       <c r="I52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5385,23 +5733,32 @@
       <c r="C53" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
+        <v>31516.95</v>
+      </c>
+      <c r="E53" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="F53" s="16" t="n">
+        <v>23614.09</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="H53" s="16" t="n">
+        <v>26706.09</v>
+      </c>
+      <c r="I53" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G53" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H53" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I53" s="16" t="n">
-        <v>-150</v>
+      <c r="J53" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K53" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="54">
@@ -5418,22 +5775,31 @@
       <c r="C54" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
+        <v>46523.37</v>
+      </c>
+      <c r="E54" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E54" s="15" t="n">
+      <c r="F54" s="16" t="n">
+        <v>12613.8</v>
+      </c>
+      <c r="G54" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="H54" s="16" t="n">
+        <v>16514.8</v>
+      </c>
+      <c r="I54" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G54" s="11" t="n">
+      <c r="J54" s="11" t="n">
         <v>250</v>
       </c>
-      <c r="H54" s="17" t="n">
+      <c r="K54" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="I54" s="16" t="n">
+      <c r="L54" s="16" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5451,23 +5817,32 @@
       <c r="C55" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
+        <v>52434.9</v>
+      </c>
+      <c r="E55" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="E55" s="15" t="n">
+      <c r="F55" s="16" t="n">
+        <v>48114.175</v>
+      </c>
+      <c r="G55" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="H55" s="16" t="n">
+        <v>54076.675</v>
+      </c>
+      <c r="I55" s="16" t="n">
         <v>680</v>
       </c>
-      <c r="G55" s="11" t="n">
-        <v>675</v>
-      </c>
-      <c r="H55" s="17" t="n">
-        <v>675</v>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>-5</v>
+      <c r="J55" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="L55" s="16" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -5484,23 +5859,32 @@
       <c r="C56" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
+        <v>39759.7</v>
+      </c>
+      <c r="E56" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E56" s="15" t="n">
+      <c r="F56" s="16" t="n">
+        <v>28430.3</v>
+      </c>
+      <c r="G56" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="H56" s="16" t="n">
+        <v>29464.3</v>
+      </c>
+      <c r="I56" s="16" t="n">
         <v>470</v>
       </c>
-      <c r="G56" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="H56" s="17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I56" s="16" t="n">
-        <v>-270</v>
+      <c r="J56" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>-220</v>
       </c>
     </row>
     <row r="57">
@@ -5517,22 +5901,31 @@
       <c r="C57" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
+        <v>31269</v>
+      </c>
+      <c r="E57" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="E57" s="15" t="n">
+      <c r="F57" s="16" t="n">
+        <v>11763.35</v>
+      </c>
+      <c r="G57" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="H57" s="16" t="n">
+        <v>11763.35</v>
+      </c>
+      <c r="I57" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="16" t="n">
+      <c r="J57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -5550,22 +5943,31 @@
       <c r="C58" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
+        <v>17843.69</v>
+      </c>
+      <c r="E58" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E58" s="15" t="n">
+      <c r="F58" s="16" t="n">
+        <v>9920.424999999999</v>
+      </c>
+      <c r="G58" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="F58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="17" t="n">
-        <v>0</v>
+      <c r="H58" s="16" t="n">
+        <v>15564.325</v>
       </c>
       <c r="I58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5583,22 +5985,31 @@
       <c r="C59" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="D59" s="15" t="n">
-        <v>14</v>
+      <c r="D59" s="16" t="n">
+        <v>68546.22</v>
       </c>
       <c r="E59" s="15" t="n">
         <v>14</v>
       </c>
       <c r="F59" s="16" t="n">
+        <v>19627.325</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H59" s="16" t="n">
+        <v>19627.325</v>
+      </c>
+      <c r="I59" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="G59" s="11" t="n">
+      <c r="J59" s="11" t="n">
         <v>375</v>
       </c>
-      <c r="H59" s="17" t="n">
+      <c r="K59" s="17" t="n">
         <v>375</v>
       </c>
-      <c r="I59" s="16" t="n">
+      <c r="L59" s="16" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -5616,22 +6027,31 @@
       <c r="C60" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
+        <v>37825.93</v>
+      </c>
+      <c r="E60" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E60" s="15" t="n">
+      <c r="F60" s="16" t="n">
+        <v>7680.975</v>
+      </c>
+      <c r="G60" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="F60" s="16" t="n">
+      <c r="H60" s="16" t="n">
+        <v>18616.965</v>
+      </c>
+      <c r="I60" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="16" t="n">
+      <c r="J60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="16" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -5649,23 +6069,32 @@
       <c r="C61" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
+        <v>49689.35</v>
+      </c>
+      <c r="E61" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="E61" s="15" t="n">
+      <c r="F61" s="16" t="n">
+        <v>32082.715</v>
+      </c>
+      <c r="G61" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="F61" s="16" t="n">
+      <c r="H61" s="16" t="n">
+        <v>51657.715</v>
+      </c>
+      <c r="I61" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="G61" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="H61" s="17" t="n">
-        <v>550</v>
-      </c>
-      <c r="I61" s="16" t="n">
-        <v>50</v>
+      <c r="J61" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="K61" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -5682,22 +6111,31 @@
       <c r="C62" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
+        <v>19288.35</v>
+      </c>
+      <c r="E62" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E62" s="15" t="n">
+      <c r="F62" s="16" t="n">
+        <v>21698.1</v>
+      </c>
+      <c r="G62" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="F62" s="16" t="n">
+      <c r="H62" s="16" t="n">
+        <v>21698.1</v>
+      </c>
+      <c r="I62" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="16" t="n">
+      <c r="J62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="16" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -5715,22 +6153,31 @@
       <c r="C63" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="16" t="n">
+        <v>29581.05</v>
+      </c>
+      <c r="E63" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="E63" s="15" t="n">
+      <c r="F63" s="16" t="n">
+        <v>15416.38</v>
+      </c>
+      <c r="G63" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F63" s="16" t="n">
+      <c r="H63" s="16" t="n">
+        <v>16301.38</v>
+      </c>
+      <c r="I63" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="G63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="16" t="n">
+      <c r="J63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="16" t="n">
         <v>-350</v>
       </c>
     </row>
@@ -5748,22 +6195,31 @@
       <c r="C64" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D64" s="16" t="n">
+        <v>14099</v>
+      </c>
+      <c r="E64" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="E64" s="15" t="n">
+      <c r="F64" s="16" t="n">
+        <v>19897.2</v>
+      </c>
+      <c r="G64" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="17" t="n">
-        <v>0</v>
+      <c r="H64" s="16" t="n">
+        <v>23514.2</v>
       </c>
       <c r="I64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5781,22 +6237,31 @@
       <c r="C65" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D65" s="16" t="n">
+        <v>29755.49</v>
+      </c>
+      <c r="E65" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E65" s="15" t="n">
+      <c r="F65" s="16" t="n">
+        <v>17639.95</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="F65" s="16" t="n">
+      <c r="H65" s="16" t="n">
+        <v>20153.95</v>
+      </c>
+      <c r="I65" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="G65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="16" t="n">
+      <c r="J65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="16" t="n">
         <v>-250</v>
       </c>
     </row>
@@ -5806,17 +6271,17 @@
           <t>SWAP 4-MONTH TOTAL (6 agents)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="n">
+      <c r="I66" s="19" t="n">
         <v>7110</v>
       </c>
-      <c r="G66" s="19" t="n">
-        <v>3450</v>
-      </c>
-      <c r="H66" s="19" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I66" s="19" t="n">
-        <v>-3660</v>
+      <c r="J66" s="19" t="n">
+        <v>3875</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>3875</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>-3235</v>
       </c>
     </row>
     <row r="69">
@@ -5836,7 +6301,7 @@
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $6,905 (57% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
+          <t>100% FLIP - 'if you had been renewing instead of rewriting': The Bonus Plan WITH MIN pays $7,975 (65% of today's $12,220 current). Agent earns close to today for doing the RIGHT behavior.</t>
         </is>
       </c>
     </row>
@@ -5864,16 +6329,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A40:L40"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A69:L69"/>
+    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A72:I72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6199,12 +6664,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>$125</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Entry. Half of NB T1.</t>
+          <t>Entry.</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6686,12 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>$187.50</t>
+          <t>$200</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Half of NB T2.</t>
+          <t>+$100 for the next $10k.</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6708,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>$262.50</t>
+          <t>$275</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Half of NB T3.</t>
+          <t>+$75 for the next $15k.</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6730,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$362.50</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Half of NB T4.</t>
+          <t>+$75 for the next $15k.</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6757,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Top tier. Half of NB top.</t>
+          <t>Top tier. +$150 for the final $15k.</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6865,12 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>$200</t>
+          <t>$250</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Entry - low bar to acknowledge renewals are smaller books today. Pays ~0.80 of NB T1.</t>
+          <t>Entry - low bar to acknowledge renewals are smaller books today.</t>
         </is>
       </c>
     </row>
@@ -6417,17 +6882,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>$45,000</t>
+          <t>$40,000</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>0.80 of NB T2.</t>
+          <t>+$100 for the next $15k.</t>
         </is>
       </c>
     </row>
@@ -6444,12 +6909,12 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>$420</t>
+          <t>$450</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0.80 of NB T3.</t>
+          <t>+$100 for the next $25k.</t>
         </is>
       </c>
     </row>
@@ -6461,17 +6926,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>$85,000</t>
+          <t>$80,000</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>$580</t>
+          <t>$550</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>0.80 of NB T4.</t>
+          <t>+$100 for the next $15k.</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6958,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Top tier. 0.80 of NB top.</t>
+          <t>Top tier. +$250 for the final $20k - biggest jump at the top.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +7221,7 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>$362</t>
+          <t>$350</t>
         </is>
       </c>
     </row>
@@ -6790,7 +7255,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>$612</t>
+          <t>$600</t>
         </is>
       </c>
     </row>
@@ -6858,7 +7323,7 @@
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>$612.50</t>
+          <t>$600.00</t>
         </is>
       </c>
     </row>
@@ -7635,7 +8100,7 @@
         </is>
       </c>
       <c r="H36" s="16" t="n">
-        <v>612.5</v>
+        <v>600</v>
       </c>
       <c r="I36" s="16" t="n">
         <v>765.74</v>
@@ -7677,7 +8142,7 @@
         </is>
       </c>
       <c r="H37" s="16" t="n">
-        <v>437.5</v>
+        <v>450</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>594.11</v>
@@ -8618,7 +9083,7 @@
         </is>
       </c>
       <c r="H62" s="16" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I62" s="16" t="n">
         <v>304.15</v>
@@ -8660,7 +9125,7 @@
         </is>
       </c>
       <c r="H63" s="16" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I63" s="16" t="n">
         <v>321.53</v>
@@ -8702,7 +9167,7 @@
         </is>
       </c>
       <c r="H64" s="16" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="I64" s="16" t="n">
         <v>980.8700000000001</v>
@@ -8744,7 +9209,7 @@
         </is>
       </c>
       <c r="H65" s="16" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="I65" s="16" t="n">
         <v>734.6900000000001</v>
@@ -8786,7 +9251,7 @@
         </is>
       </c>
       <c r="H66" s="16" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I66" s="16" t="n">
         <v>208.56</v>
@@ -8828,7 +9293,7 @@
         </is>
       </c>
       <c r="H67" s="16" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I67" s="16" t="n">
         <v>150.1</v>
@@ -8870,7 +9335,7 @@
         </is>
       </c>
       <c r="H68" s="16" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I68" s="16" t="n">
         <v>217.25</v>
@@ -9290,7 +9755,7 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I78" s="16" t="n">
         <v>208.56</v>
@@ -9332,7 +9797,7 @@
         </is>
       </c>
       <c r="H79" s="16" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I79" s="16" t="n">
         <v>126.4</v>
@@ -9919,7 +10384,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>$362</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -9929,12 +10394,12 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>$612</t>
+          <t>$600</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>$612</t>
+          <t>$600</t>
         </is>
       </c>
     </row>
@@ -9951,22 +10416,22 @@
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>$125</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>$300</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>$675</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>$675</t>
+          <t>$700</t>
         </is>
       </c>
     </row>
@@ -9979,22 +10444,22 @@
       <c r="B21" s="28" t="inlineStr"/>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>-$238</t>
+          <t>-$250</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>+$300</t>
+          <t>+$350</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>+$62</t>
+          <t>+$100</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>+$62</t>
+          <t>+$100</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11511,7 @@
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>12530.47</v>
@@ -11060,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="L29" s="17" t="n">
         <v>0</v>
@@ -11100,7 +11565,7 @@
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>362.5</v>
+        <v>350</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>11629.68</v>
@@ -11114,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>362.5</v>
+        <v>350</v>
       </c>
       <c r="L30" s="17" t="n">
         <v>0</v>
@@ -11154,7 +11619,7 @@
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>362.5</v>
+        <v>350</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>5962.5</v>
@@ -11168,10 +11633,10 @@
         <v>0</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>612.5</v>
+        <v>600</v>
       </c>
       <c r="L31" s="17" t="n">
-        <v>612.5</v>
+        <v>600</v>
       </c>
       <c r="M31" s="23" t="inlineStr">
         <is>
@@ -11179,7 +11644,7 @@
         </is>
       </c>
       <c r="N31" s="11" t="n">
-        <v>-407.5</v>
+        <v>-420</v>
       </c>
     </row>
     <row r="32">
@@ -11208,7 +11673,7 @@
         </is>
       </c>
       <c r="G32" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>19575</v>
@@ -11222,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>437.5</v>
+        <v>450</v>
       </c>
       <c r="L32" s="17" t="n">
-        <v>437.5</v>
+        <v>450</v>
       </c>
       <c r="M32" s="23" t="inlineStr">
         <is>
@@ -11233,7 +11698,7 @@
         </is>
       </c>
       <c r="N32" s="11" t="n">
-        <v>-282.5</v>
+        <v>-270</v>
       </c>
     </row>
     <row r="33">
@@ -11630,7 +12095,7 @@
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>0</v>
@@ -11644,7 +12109,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="L45" s="17" t="n">
         <v>0</v>
@@ -11684,7 +12149,7 @@
         </is>
       </c>
       <c r="G46" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>1063</v>
@@ -11698,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L46" s="17" t="n">
         <v>0</v>
@@ -11738,7 +12203,7 @@
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>1034</v>
@@ -11752,7 +12217,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>187.5</v>
+        <v>200</v>
       </c>
       <c r="L47" s="17" t="n">
         <v>0</v>
@@ -13382,7 +13847,7 @@
         </is>
       </c>
       <c r="G93" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>6502.91</v>
@@ -13396,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L93" s="17" t="n">
         <v>0</v>
@@ -13436,7 +13901,7 @@
         </is>
       </c>
       <c r="G94" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H94" s="11" t="n">
         <v>3092</v>
@@ -13450,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L94" s="17" t="n">
         <v>0</v>
@@ -13588,7 +14053,7 @@
       <c r="I97" s="34" t="n"/>
       <c r="J97" s="34" t="n"/>
       <c r="K97" s="19" t="n">
-        <v>625</v>
+        <v>575</v>
       </c>
       <c r="L97" s="19" t="n">
         <v>375</v>
@@ -14617,17 +15082,17 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L29" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M29" s="33" t="inlineStr">
         <is>
@@ -14635,7 +15100,7 @@
         </is>
       </c>
       <c r="N29" s="11" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -14671,17 +15136,17 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J30" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L30" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M30" s="33" t="inlineStr">
         <is>
@@ -14689,7 +15154,7 @@
         </is>
       </c>
       <c r="N30" s="11" t="n">
-        <v>-160</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="31">
@@ -14718,24 +15183,24 @@
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>54076.675</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="L31" s="17" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="M31" s="23" t="inlineStr">
         <is>
@@ -14743,7 +15208,7 @@
         </is>
       </c>
       <c r="N31" s="11" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -14779,17 +15244,17 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J32" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="L32" s="17" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="M32" s="23" t="inlineStr">
         <is>
@@ -14797,7 +15262,7 @@
         </is>
       </c>
       <c r="N32" s="11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -14816,14 +15281,14 @@
       <c r="I33" s="34" t="n"/>
       <c r="J33" s="34" t="n"/>
       <c r="K33" s="19" t="n">
-        <v>1825</v>
+        <v>2000</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>1825</v>
+        <v>2000</v>
       </c>
       <c r="M33" s="34" t="n"/>
       <c r="N33" s="19" t="n">
-        <v>-165</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -15205,13 +15670,13 @@
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L45" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M45" s="33" t="inlineStr">
         <is>
@@ -15219,7 +15684,7 @@
         </is>
       </c>
       <c r="N45" s="11" t="n">
-        <v>-300</v>
+        <v>-250</v>
       </c>
     </row>
     <row r="46">
@@ -15259,13 +15724,13 @@
         </is>
       </c>
       <c r="J46" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L46" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M46" s="33" t="inlineStr">
         <is>
@@ -15273,7 +15738,7 @@
         </is>
       </c>
       <c r="N46" s="11" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -15313,13 +15778,13 @@
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L47" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M47" s="33" t="inlineStr">
         <is>
@@ -15327,7 +15792,7 @@
         </is>
       </c>
       <c r="N47" s="11" t="n">
-        <v>-270</v>
+        <v>-220</v>
       </c>
     </row>
     <row r="48">
@@ -15400,14 +15865,14 @@
       <c r="I49" s="34" t="n"/>
       <c r="J49" s="34" t="n"/>
       <c r="K49" s="19" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="M49" s="34" t="n"/>
       <c r="N49" s="19" t="n">
-        <v>-870</v>
+        <v>-720</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
@@ -16957,13 +17422,13 @@
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L93" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M93" s="33" t="inlineStr">
         <is>
@@ -16971,7 +17436,7 @@
         </is>
       </c>
       <c r="N93" s="11" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="94">
@@ -17011,13 +17476,13 @@
         </is>
       </c>
       <c r="J94" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L94" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M94" s="33" t="inlineStr">
         <is>
@@ -17025,7 +17490,7 @@
         </is>
       </c>
       <c r="N94" s="11" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="95">
@@ -17152,14 +17617,14 @@
       <c r="I97" s="34" t="n"/>
       <c r="J97" s="34" t="n"/>
       <c r="K97" s="19" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="M97" s="34" t="n"/>
       <c r="N97" s="19" t="n">
-        <v>-625</v>
+        <v>-525</v>
       </c>
     </row>
   </sheetData>
@@ -17584,13 +18049,13 @@
         </is>
       </c>
       <c r="J13" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M13" s="33" t="inlineStr">
         <is>
@@ -17598,7 +18063,7 @@
         </is>
       </c>
       <c r="N13" s="11" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -17638,13 +18103,13 @@
         </is>
       </c>
       <c r="J14" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L14" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M14" s="33" t="inlineStr">
         <is>
@@ -17652,7 +18117,7 @@
         </is>
       </c>
       <c r="N14" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15">
@@ -17692,13 +18157,13 @@
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="L15" s="17" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="M15" s="23" t="inlineStr">
         <is>
@@ -17706,7 +18171,7 @@
         </is>
       </c>
       <c r="N15" s="11" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -17780,11 +18245,11 @@
       <c r="J17" s="34" t="n"/>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="19" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="M17" s="34" t="n"/>
       <c r="N17" s="19" t="n">
-        <v>-100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -18149,13 +18614,13 @@
         </is>
       </c>
       <c r="J28" s="11" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="L28" s="17" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="M28" s="33" t="inlineStr">
         <is>
@@ -18163,7 +18628,7 @@
         </is>
       </c>
       <c r="N28" s="11" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -18199,17 +18664,17 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>T4 $85k</t>
+          <t>T4 $80k</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="L29" s="17" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="M29" s="33" t="inlineStr">
         <is>
@@ -18217,7 +18682,7 @@
         </is>
       </c>
       <c r="N29" s="11" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -18253,17 +18718,17 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>T4 $85k</t>
+          <t>T4 $80k</t>
         </is>
       </c>
       <c r="J30" s="11" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>830</v>
+        <v>800</v>
       </c>
       <c r="L30" s="17" t="n">
-        <v>830</v>
+        <v>800</v>
       </c>
       <c r="M30" s="23" t="inlineStr">
         <is>
@@ -18271,7 +18736,7 @@
         </is>
       </c>
       <c r="N30" s="11" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31">
@@ -18307,17 +18772,17 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="L31" s="17" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="M31" s="23" t="inlineStr">
         <is>
@@ -18325,7 +18790,7 @@
         </is>
       </c>
       <c r="N31" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32">
@@ -18345,11 +18810,11 @@
       <c r="J32" s="34" t="n"/>
       <c r="K32" s="34" t="n"/>
       <c r="L32" s="19" t="n">
-        <v>2380</v>
+        <v>2400</v>
       </c>
       <c r="M32" s="34" t="n"/>
       <c r="N32" s="19" t="n">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="34">
@@ -18710,17 +19175,17 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L43" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M43" s="33" t="inlineStr">
         <is>
@@ -18728,7 +19193,7 @@
         </is>
       </c>
       <c r="N43" s="11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -18764,17 +19229,17 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J44" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L44" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M44" s="33" t="inlineStr">
         <is>
@@ -18782,7 +19247,7 @@
         </is>
       </c>
       <c r="N44" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45">
@@ -18818,17 +19283,17 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L45" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M45" s="33" t="inlineStr">
         <is>
@@ -18836,7 +19301,7 @@
         </is>
       </c>
       <c r="N45" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -18872,17 +19337,17 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>T1 $25k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J46" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="L46" s="17" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="M46" s="33" t="inlineStr">
         <is>
@@ -18890,7 +19355,7 @@
         </is>
       </c>
       <c r="N46" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47">
@@ -18910,11 +19375,11 @@
       <c r="J47" s="34" t="n"/>
       <c r="K47" s="34" t="n"/>
       <c r="L47" s="19" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="M47" s="34" t="n"/>
       <c r="N47" s="19" t="n">
-        <v>850</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="49">
@@ -19279,13 +19744,13 @@
         </is>
       </c>
       <c r="J58" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L58" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M58" s="33" t="inlineStr">
         <is>
@@ -19293,7 +19758,7 @@
         </is>
       </c>
       <c r="N58" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59">
@@ -19329,17 +19794,17 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>T1 $25k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="L59" s="17" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="M59" s="33" t="inlineStr">
         <is>
@@ -19347,7 +19812,7 @@
         </is>
       </c>
       <c r="N59" s="11" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60">
@@ -19441,13 +19906,13 @@
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L61" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M61" s="33" t="inlineStr">
         <is>
@@ -19455,7 +19920,7 @@
         </is>
       </c>
       <c r="N61" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
@@ -19475,11 +19940,11 @@
       <c r="J62" s="34" t="n"/>
       <c r="K62" s="34" t="n"/>
       <c r="L62" s="19" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="M62" s="34" t="n"/>
       <c r="N62" s="19" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row r="64">
@@ -19844,13 +20309,13 @@
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L73" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
@@ -19858,7 +20323,7 @@
         </is>
       </c>
       <c r="N73" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74">
@@ -19898,13 +20363,13 @@
         </is>
       </c>
       <c r="J74" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L74" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M74" s="33" t="inlineStr">
         <is>
@@ -19912,7 +20377,7 @@
         </is>
       </c>
       <c r="N74" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75">
@@ -20006,13 +20471,13 @@
         </is>
       </c>
       <c r="J76" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L76" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M76" s="33" t="inlineStr">
         <is>
@@ -20020,7 +20485,7 @@
         </is>
       </c>
       <c r="N76" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77">
@@ -20040,11 +20505,11 @@
       <c r="J77" s="34" t="n"/>
       <c r="K77" s="34" t="n"/>
       <c r="L77" s="19" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="M77" s="34" t="n"/>
       <c r="N77" s="19" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="79">
@@ -20405,17 +20870,17 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J88" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L88" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M88" s="33" t="inlineStr">
         <is>
@@ -20423,7 +20888,7 @@
         </is>
       </c>
       <c r="N88" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89">
@@ -20459,17 +20924,17 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>T2 $45k</t>
+          <t>T2 $40k</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L89" s="17" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M89" s="33" t="inlineStr">
         <is>
@@ -20477,7 +20942,7 @@
         </is>
       </c>
       <c r="N89" s="11" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90">
@@ -20517,13 +20982,13 @@
         </is>
       </c>
       <c r="J90" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>575</v>
+        <v>625</v>
       </c>
       <c r="L90" s="17" t="n">
-        <v>575</v>
+        <v>625</v>
       </c>
       <c r="M90" s="23" t="inlineStr">
         <is>
@@ -20531,7 +20996,7 @@
         </is>
       </c>
       <c r="N90" s="11" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91">
@@ -20571,13 +21036,13 @@
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L91" s="17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
@@ -20585,7 +21050,7 @@
         </is>
       </c>
       <c r="N91" s="11" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92">
@@ -20605,11 +21070,11 @@
       <c r="J92" s="34" t="n"/>
       <c r="K92" s="34" t="n"/>
       <c r="L92" s="19" t="n">
-        <v>1375</v>
+        <v>1575</v>
       </c>
       <c r="M92" s="34" t="n"/>
       <c r="N92" s="19" t="n">
-        <v>1025</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
